--- a/Results/Hydrogen/hydrogen eutrophication marine results.xlsx
+++ b/Results/Hydrogen/hydrogen eutrophication marine results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02888116415279556</v>
+        <v>0.02888116415279566</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01513942999642761</v>
+        <v>0.01513942999642756</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05865733979347301</v>
+        <v>0.05865733979347293</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01513942999642761</v>
+        <v>0.01513942999642756</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01513942999642761</v>
+        <v>0.01513942999642756</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03813631489947283</v>
+        <v>0.03813631489947275</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07880398026956531</v>
+        <v>0.07880398026956502</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01513942999642761</v>
+        <v>0.01513942999642756</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03604030525438003</v>
+        <v>0.0360403052543799</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01574380501930678</v>
+        <v>0.01574380501930671</v>
       </c>
       <c r="L2" t="n">
-        <v>0.122396411547298</v>
+        <v>0.03212267781495749</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.0007123338257491606</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006553626560496907</v>
+        <v>0.0006553626560496922</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.0007123338257491606</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0006744875365914058</v>
+        <v>0.000674487536591408</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0006744875365914057</v>
+        <v>0.0006744875365914066</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007101619255812736</v>
+        <v>0.0007101619255812688</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.0007123338257491606</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006984535555144521</v>
+        <v>0.0006984535555144519</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.0007123338257491606</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.0007123338257491606</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.0007123338257491606</v>
       </c>
     </row>
     <row r="4">
@@ -595,31 +595,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002568339442016162</v>
+        <v>0.001650054115013734</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001598271453166547</v>
+        <v>0.001598271453166542</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001710306255858641</v>
+        <v>0.001710300415302096</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001504742499186777</v>
+        <v>0.001504742499186781</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00163454295157516</v>
+        <v>0.001634542951575161</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002566167541848274</v>
+        <v>0.002566167541848276</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002625352167206045</v>
+        <v>0.002625352167206037</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002554459171781454</v>
+        <v>0.001636173844779027</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001721755508722797</v>
+        <v>0.001721755508722815</v>
       </c>
       <c r="K4" t="n">
         <v>0.001624144813699047</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00137531401556985</v>
+        <v>0.001375314015569849</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001361433745335145</v>
+        <v>0.001361433745335146</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001375254005885967</v>
+        <v>0.001375254005885969</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001360557110117741</v>
+        <v>0.001360557110117743</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001360557110117741</v>
+        <v>0.001360557110117743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001373142115401965</v>
+        <v>0.001373142115401966</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00137531401556985</v>
+        <v>0.001375314015569849</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001361433745335145</v>
+        <v>0.001361433745335146</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00137531401556985</v>
+        <v>0.001375314015569849</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00137531401556985</v>
+        <v>0.001375314015569849</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00137531401556985</v>
+        <v>0.001375314015569849</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001948890565030784</v>
+        <v>0.001948890565030777</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002932759860549482</v>
+        <v>0.002932759860549492</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00315421486536906</v>
+        <v>0.003154214865369068</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002659774034264545</v>
+        <v>0.002659774034264548</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001966168239391154</v>
+        <v>0.00196616823939116</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002945035471852987</v>
+        <v>0.002945035471852977</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002947207372020895</v>
+        <v>0.002947207372020927</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002933327101786167</v>
+        <v>0.002933327101786153</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002947403569729817</v>
+        <v>0.002947403569729818</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001930346317815961</v>
+        <v>0.001930346317815959</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003990032754678967</v>
+        <v>0.003990032754678948</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003521769701192664</v>
+        <v>0.003521769701192665</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004377397803454512</v>
+        <v>0.004377397803454514</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004391278352882414</v>
+        <v>0.004391278352882413</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005380790948326928</v>
+        <v>0.00538079094832693</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004377396737198246</v>
+        <v>0.004377396737198234</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00438910617352133</v>
+        <v>0.004389106173521334</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004391278073689216</v>
+        <v>0.004391278073689225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004377397803454512</v>
+        <v>0.004377397803454514</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004391278073689216</v>
+        <v>0.004391278073689225</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003296411753660712</v>
+        <v>0.003887481625270313</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004391278073689216</v>
+        <v>0.004391278073689225</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00113572896960069</v>
+        <v>0.001135728969600711</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001446042362253147</v>
+        <v>0.001446042362253146</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005146423656717448</v>
+        <v>0.0005146423656717438</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001446042362253147</v>
+        <v>0.001446042362253146</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001446042362253147</v>
+        <v>0.001446042362253146</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009694298668947907</v>
+        <v>0.0009694298668947922</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0002738010818122738</v>
+        <v>0.0002738010818122727</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001446042362253147</v>
+        <v>0.001446042362253146</v>
       </c>
       <c r="J8" t="n">
         <v>0.00104028573292882</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001435152206400079</v>
+        <v>0.00143515220640008</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001152487928766265</v>
+        <v>0.001152487928766264</v>
       </c>
     </row>
     <row r="9">
@@ -801,7 +801,7 @@
         <v>0.001593251791687278</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001212513826184299</v>
+        <v>0.0012125138261843</v>
       </c>
       <c r="E9" t="n">
         <v>0.001593251791687278</v>
@@ -810,10 +810,10 @@
         <v>0.001593251791687278</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00139541095950308</v>
+        <v>0.001395410959503081</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001115768847512964</v>
+        <v>0.001115768847512963</v>
       </c>
       <c r="I9" t="n">
         <v>0.001593251791687278</v>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002357454088996901</v>
+        <v>0.002357454088996893</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00579671585439441</v>
+        <v>0.005796715854394399</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004825673873168724</v>
+        <v>0.004825673873168733</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00579671585439441</v>
+        <v>0.005796715854394399</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00579671585439441</v>
+        <v>0.005796715854394399</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006819852019234309</v>
+        <v>0.006819852019234226</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005053068363022811</v>
+        <v>0.005053068363022807</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00579671585439441</v>
+        <v>0.005796715854394399</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009411506195027175</v>
+        <v>0.009411506195027184</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004556896355457275</v>
+        <v>0.004556896355457294</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004292278882670871</v>
+        <v>0.00344654496494164</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005549807825525952</v>
+        <v>0.0005549807825525946</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005061597788830215</v>
+        <v>0.0005061597788830196</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005549807825525952</v>
+        <v>0.0005549807825525946</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005200852085627896</v>
+        <v>0.0005200852085627869</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005200852085627896</v>
+        <v>0.000520085208562787</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005532790478318264</v>
+        <v>0.000553279047831826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005549807825525952</v>
+        <v>0.0005549807825525946</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005439883413838714</v>
+        <v>0.0005439883413838689</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005549807825525952</v>
+        <v>0.0005549807825525946</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005549807825525952</v>
+        <v>0.0005549807825525946</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005549807825525952</v>
+        <v>0.0005549807825525946</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001924077701727949</v>
+        <v>0.001924077701727948</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001293893579470999</v>
+        <v>0.001293893579470991</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001309802756342614</v>
+        <v>0.001934975575615246</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001214620874693914</v>
+        <v>0.001214620874693912</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001302409852743483</v>
+        <v>0.001302409852743481</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001922375967007179</v>
+        <v>0.001312144007688663</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00195940920931378</v>
+        <v>0.001959409209313777</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001302853301240706</v>
+        <v>0.001302853301240704</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001936794194889609</v>
+        <v>0.001936794194889608</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001314042285451014</v>
+        <v>0.001314042285451027</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001313875967113682</v>
+        <v>0.001313875967113681</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001001775188947015</v>
+        <v>0.001001775188947014</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009907827477782941</v>
+        <v>0.0009907827477782891</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001001724689642438</v>
+        <v>0.001001724689642436</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009900888870349902</v>
+        <v>0.0009900888870349866</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009900888870349902</v>
+        <v>0.0009900888870349866</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001000073454226249</v>
+        <v>0.001000073454226247</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001001775188947015</v>
+        <v>0.001001775188947014</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009907827477782941</v>
+        <v>0.0009907827477782891</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001001775188947015</v>
+        <v>0.001001775188947014</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001001775188947015</v>
+        <v>0.001001775188947014</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001001775188947015</v>
+        <v>0.001001775188947014</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001380554690560406</v>
+        <v>0.0013805546905604</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002051170782959383</v>
+        <v>0.002051170782959375</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002204062679890804</v>
+        <v>0.002204062679890799</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0018646661153892</v>
+        <v>0.001864666115389193</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00139079918515911</v>
+        <v>0.001390799185159106</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002060928199993602</v>
+        <v>0.002060928199993595</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002062629934714338</v>
+        <v>0.002062629934714335</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002051637493545643</v>
+        <v>0.002051637493545636</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002062763981959421</v>
+        <v>0.002062763981959416</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001367884792728547</v>
+        <v>0.001367884792728543</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002775114561360673</v>
+        <v>0.002775114561360664</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001698221192128132</v>
+        <v>0.001698221192128122</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002071956389665975</v>
+        <v>0.002071956389665965</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002082949152179945</v>
+        <v>0.002082949152179933</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002515924135190011</v>
+        <v>0.002515924135190005</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002071956323672986</v>
+        <v>0.002071956323672976</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00208124709611393</v>
+        <v>0.002081247096113922</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002082948830834695</v>
+        <v>0.002082948830834691</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002071956389665975</v>
+        <v>0.002071956389665965</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002082948830834695</v>
+        <v>0.002082948830834691</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001860036261183422</v>
+        <v>0.001860036261183412</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002082948830834695</v>
+        <v>0.002082948830834691</v>
       </c>
     </row>
     <row r="8">
@@ -1169,19 +1169,19 @@
         <v>0.001391579940483863</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001448778162187331</v>
+        <v>0.00144877816218733</v>
       </c>
       <c r="I8" t="n">
         <v>0.001352397473257019</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001342484530835189</v>
+        <v>0.001342484530835188</v>
       </c>
       <c r="K8" t="n">
         <v>0.001443386705515912</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001464560242205021</v>
+        <v>0.001488746779492833</v>
       </c>
     </row>
     <row r="9">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001495494150955801</v>
+        <v>0.0014954941509558</v>
       </c>
       <c r="C9" t="n">
         <v>0.001397368461479902</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001468861939765744</v>
+        <v>0.001468861939765742</v>
       </c>
       <c r="E9" t="n">
         <v>0.001397368461479902</v>
@@ -1206,7 +1206,7 @@
         <v>0.001397368461479902</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001448784785749156</v>
+        <v>0.001448784785749155</v>
       </c>
       <c r="H9" t="n">
         <v>0.001472667724144988</v>
@@ -1215,13 +1215,13 @@
         <v>0.001397368461479902</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001429359916485233</v>
+        <v>0.001429359916485231</v>
       </c>
       <c r="K9" t="n">
         <v>0.001470383187831555</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001479065193755787</v>
+        <v>0.001479065193755786</v>
       </c>
     </row>
   </sheetData>
@@ -1307,34 +1307,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006302078885303043</v>
+        <v>0.006302078885303057</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009594410728319793</v>
+        <v>0.009594410728319796</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01671249283341016</v>
+        <v>0.01671249283341017</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007963301996171528</v>
+        <v>0.007963301996171559</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007963301996171528</v>
+        <v>0.007963301996171559</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01493075912742126</v>
+        <v>0.0149307591274212</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03433290738343972</v>
+        <v>0.03433290738343973</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007963301996171528</v>
+        <v>0.007963301996171559</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02830406137785923</v>
+        <v>0.02830406137785924</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007467634140212322</v>
+        <v>0.007467634140212324</v>
       </c>
       <c r="L2" t="n">
         <v>0.02427979573568995</v>
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005642020218236039</v>
+        <v>0.0005642020218236115</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004853117457798649</v>
+        <v>0.0004853117457798577</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005642020218236039</v>
+        <v>0.0005642020218236117</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005339936364825229</v>
+        <v>0.0005339936364825223</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005339936364825211</v>
+        <v>0.0005339936364825224</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005620359132407812</v>
+        <v>0.0005620359132407758</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005642020218236039</v>
+        <v>0.0005642020218236117</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005501937874740927</v>
+        <v>0.0005501937874740909</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000564202021823604</v>
+        <v>0.0005642020218236117</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005642020218236039</v>
+        <v>0.0005642020218236117</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005642020218236039</v>
+        <v>0.0005642020218236117</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002056374876000488</v>
+        <v>0.001362329657635273</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001340654221208007</v>
+        <v>0.001340654221207997</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001372050294837997</v>
+        <v>0.001372045928070306</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001248990640132062</v>
+        <v>0.001248990640132056</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001347374040110536</v>
+        <v>0.001347374040110531</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002054208767417663</v>
+        <v>0.00205420876741766</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002110381362945673</v>
+        <v>0.002110381362945668</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002042366641650967</v>
+        <v>0.002042366641650975</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002065593364019779</v>
+        <v>0.002065593364019784</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001347302299137553</v>
+        <v>0.001347302299137546</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001365562165139723</v>
+        <v>0.001365562165139729</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001084506150114598</v>
+        <v>0.001084506150114603</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001083439116145953</v>
+        <v>0.001083439116145951</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001084457028350446</v>
+        <v>0.001084457028350448</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001071867099246337</v>
+        <v>0.00107186709924634</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001071867099246337</v>
+        <v>0.00107186709924634</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001082340041531772</v>
+        <v>0.001082340041531767</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001084506150114598</v>
+        <v>0.001084506150114603</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00107049791576508</v>
+        <v>0.001070497915765081</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001084506150114598</v>
+        <v>0.001084506150114603</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001084506150114598</v>
+        <v>0.001084506150114603</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001084506150114598</v>
+        <v>0.001084506150114603</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001531553942445149</v>
+        <v>0.001531553942445148</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002324725415097838</v>
+        <v>0.002324725415103292</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002488642830457256</v>
+        <v>0.002488642830457247</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002094811637885228</v>
+        <v>0.002094811637885224</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001543519618358416</v>
+        <v>0.001543519618358413</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002322102228167563</v>
+        <v>0.002322102228167564</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002324268336751326</v>
+        <v>0.002324268336751324</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002310260102400882</v>
+        <v>0.00231026010240088</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002324424127711077</v>
+        <v>0.002324424127711076</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001516828865600365</v>
+        <v>0.001516828865600368</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003152324807186037</v>
+        <v>0.003152324807186031</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002169631037683369</v>
+        <v>0.002169631037683374</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002690058993282544</v>
+        <v>0.002690058993282532</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002691126257723178</v>
+        <v>0.002691126257723182</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00327891163899519</v>
+        <v>0.003278911638995189</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002677117374716074</v>
+        <v>0.002677117374716063</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00268895991866835</v>
+        <v>0.002688959918668345</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002691126027251189</v>
+        <v>0.002691126027251176</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00267711779290167</v>
+        <v>0.002677117792901666</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002691126027251189</v>
+        <v>0.002691126027251176</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002034470689126509</v>
+        <v>0.002388969879163186</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002691126027251189</v>
+        <v>0.002691126027251176</v>
       </c>
     </row>
     <row r="8">
@@ -1550,10 +1550,10 @@
         <v>0.003082045433884202</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009477450194473527</v>
+        <v>0.0009477450194473534</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001343981051833635</v>
+        <v>0.001343981051833632</v>
       </c>
       <c r="E8" t="n">
         <v>0.001233935975189953</v>
@@ -1562,19 +1562,19 @@
         <v>0.001233935975189953</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001132663394450968</v>
+        <v>0.001132663394450969</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001029349980645343</v>
+        <v>0.001029349980645344</v>
       </c>
       <c r="I8" t="n">
         <v>0.001233935975189953</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001251847987635942</v>
+        <v>0.00125184798763594</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001770955691116301</v>
+        <v>0.001770955691116302</v>
       </c>
       <c r="L8" t="n">
         <v>0.00138026323349421</v>
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003098473435151387</v>
+        <v>0.003098473435151388</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00103863776815088</v>
+        <v>0.001038637768150878</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001526889190430714</v>
+        <v>0.001526889190430715</v>
       </c>
       <c r="E9" t="n">
         <v>0.001300954711764521</v>
@@ -1602,19 +1602,19 @@
         <v>0.001300954711764521</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001289524235522642</v>
+        <v>0.001289524235522643</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001399373925416271</v>
+        <v>0.001399373925416272</v>
       </c>
       <c r="I9" t="n">
         <v>0.001300954711764521</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001572181268011262</v>
+        <v>0.001572181268011264</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001823495055521821</v>
+        <v>0.001823495055521824</v>
       </c>
       <c r="L9" t="n">
         <v>0.001620728519570582</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003277360994062628</v>
+        <v>0.003277360994062617</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006663008402527826</v>
+        <v>0.006663008402527799</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01156592188711921</v>
+        <v>0.0115659218871192</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005036409147328627</v>
+        <v>0.005036409147328611</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005036409147328627</v>
+        <v>0.005036409147328611</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00915923072723779</v>
+        <v>0.009159230727237712</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01746641939187345</v>
+        <v>0.01746641939187344</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005036409147328627</v>
+        <v>0.005036409147328611</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01818707070270403</v>
+        <v>0.01818707070270402</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003812813518921449</v>
+        <v>0.003812813518921434</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008249532478640515</v>
+        <v>0.008249532478640499</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005390954554493612</v>
+        <v>0.0005390954554493518</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004734029366716139</v>
+        <v>0.0004734029366716137</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005390954554493612</v>
+        <v>0.0005390954554493518</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005804080451127618</v>
+        <v>0.0005804080451127597</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005804080451127615</v>
+        <v>0.0005804080451127609</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005371670885479868</v>
+        <v>0.0005371670885479839</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005390954554493612</v>
+        <v>0.0005390954554493518</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000526612891780915</v>
+        <v>0.0005266128917809148</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005390954554493612</v>
+        <v>0.0005390954554493517</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005390954554493612</v>
+        <v>0.0005390954554493518</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005390954554493612</v>
+        <v>0.0005390954554493518</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001943217746280058</v>
+        <v>0.00194321774628004</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001285817826480029</v>
+        <v>0.001285817826480011</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001310266753564826</v>
+        <v>0.001950979976802378</v>
       </c>
       <c r="E4" t="n">
         <v>0.00120833424359802</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001294616247367693</v>
+        <v>0.001294616247367691</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001300537790807078</v>
+        <v>0.001300537790807071</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001989411158193296</v>
+        <v>0.001989411158193291</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001289983594040006</v>
+        <v>0.001289983594040004</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001361668538451264</v>
+        <v>0.001361668538451257</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001294369195784951</v>
+        <v>0.00129436919578495</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001300151551918287</v>
+        <v>0.001300151551918274</v>
       </c>
     </row>
     <row r="5">
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001020837710383891</v>
+        <v>0.001020837710383893</v>
       </c>
       <c r="C5" t="n">
         <v>0.001019951454724185</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001020791584666492</v>
+        <v>0.001020791584666499</v>
       </c>
       <c r="E5" t="n">
         <v>0.001017161175269407</v>
@@ -1838,22 +1838,22 @@
         <v>0.001017161175269407</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001018909343482519</v>
+        <v>0.001018909343482523</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001020837710383891</v>
+        <v>0.001020837710383893</v>
       </c>
       <c r="I5" t="n">
         <v>0.001008355146715451</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001020837710383891</v>
+        <v>0.001020837710383893</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001020837710383891</v>
+        <v>0.001020837710383893</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001020837710383891</v>
+        <v>0.001020837710383893</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001431999535669107</v>
+        <v>0.001431999535669093</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00217536311641451</v>
+        <v>0.002175363116420028</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002320171274693164</v>
+        <v>0.002320171274693159</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001961657250707789</v>
+        <v>0.001961657250707786</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001448116153681701</v>
+        <v>0.001448116153681698</v>
       </c>
       <c r="G6" t="n">
         <v>0.002165704536747719</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002167632903650912</v>
+        <v>0.002167632903650903</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002155150339980648</v>
+        <v>0.002155150339980646</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002167777476489444</v>
+        <v>0.002167777476489441</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001418334768199598</v>
+        <v>0.00141833476819958</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002936063468991348</v>
+        <v>0.002936063468991334</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001833251615038102</v>
+        <v>0.001833251615038094</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002263520418292129</v>
+        <v>0.002263520418292128</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002264406954877068</v>
+        <v>0.002264406954877062</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002749467910374929</v>
+        <v>0.002749467910374928</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002251923910376463</v>
+        <v>0.002251923910376459</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002262478307050471</v>
+        <v>0.002262478307050463</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00226440667395184</v>
+        <v>0.00226440667395183</v>
       </c>
       <c r="I7" t="n">
         <v>0.002251924110283395</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00226440667395184</v>
+        <v>0.00226440667395183</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00201459385769749</v>
+        <v>0.002014593857697482</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00226440667395184</v>
+        <v>0.00226440667395183</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003133458442330859</v>
+        <v>0.003133458442330862</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009890241507717332</v>
+        <v>0.0009890241507717341</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001433751047898145</v>
+        <v>0.001433751047898147</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001292068866998125</v>
+        <v>0.001292068866998126</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001292068866998125</v>
+        <v>0.001292068866998126</v>
       </c>
       <c r="G8" t="n">
         <v>0.001242352177603974</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001338982945092809</v>
+        <v>0.001338982945092805</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001292068866998125</v>
+        <v>0.001292068866998126</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001473789359083566</v>
+        <v>0.001473789359083561</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00185171858621509</v>
+        <v>0.001851718586215084</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001460133349035873</v>
+        <v>0.001460133349035869</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003112442755886063</v>
+        <v>0.003112442755886059</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001046182136740867</v>
+        <v>0.001046182136740868</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001555346579453643</v>
+        <v>0.001555346579453641</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001323392874236854</v>
+        <v>0.001323392874236855</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001323392874236854</v>
+        <v>0.001323392874236855</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001329510211072303</v>
+        <v>0.001329510211072298</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001517081018623584</v>
+        <v>0.001517081018623576</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001323392874236854</v>
+        <v>0.001323392874236855</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001675452190832488</v>
+        <v>0.001675452190832486</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001857405400065836</v>
+        <v>0.001857405400065835</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001519737843200104</v>
+        <v>0.0015197378432001</v>
       </c>
     </row>
   </sheetData>
@@ -2102,34 +2102,34 @@
         <v>0.001640608874312366</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004985534879649692</v>
+        <v>0.004985534879649704</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007500878151977646</v>
+        <v>0.007500878151977627</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002166627070394702</v>
+        <v>0.002166627070394684</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002166627070394702</v>
+        <v>0.002166627070394684</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005462935018253484</v>
+        <v>0.005462935018253366</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008785205825380605</v>
+        <v>0.008785205825380586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002166627070394702</v>
+        <v>0.002166627070394684</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008765832536700066</v>
+        <v>0.008765832536700052</v>
       </c>
       <c r="K2" t="n">
         <v>0.002094120116096857</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003357987184563702</v>
+        <v>0.0033579871845637</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005214368868232698</v>
+        <v>0.00052143688682327</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004631199147401384</v>
+        <v>0.0004631199147401385</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005214368868232698</v>
+        <v>0.00052143688682327</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005604762271465099</v>
+        <v>0.0005604762271465074</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005604762271465098</v>
+        <v>0.0005604762271465074</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005196553938146281</v>
+        <v>0.0005196553938146283</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005214368868232698</v>
+        <v>0.00052143688682327</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005099279131727974</v>
+        <v>0.0005099279131728008</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005214368868232698</v>
+        <v>0.00052143688682327</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005214368868232698</v>
+        <v>0.00052143688682327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005214368868232698</v>
+        <v>0.00052143688682327</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001901955588209049</v>
+        <v>0.001277818392991215</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001265452828245026</v>
+        <v>0.001265452828244958</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001280205010503352</v>
+        <v>0.001280205010503246</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001184649191405628</v>
+        <v>0.001184649191405633</v>
       </c>
       <c r="F4" t="n">
         <v>0.001270296954005983</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001276036899982573</v>
+        <v>0.001900174095200409</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001942632827647637</v>
+        <v>0.001942632827647639</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001266309419340743</v>
+        <v>0.001890446614558581</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001333952626861887</v>
+        <v>0.001907531825042422</v>
       </c>
       <c r="K4" t="n">
         <v>0.001274521514247264</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001273782065207833</v>
+        <v>0.001273782065207892</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009850358955308626</v>
+        <v>0.0009850358955308636</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009842629829125604</v>
+        <v>0.0009842629829125585</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009849894313116586</v>
+        <v>0.0009849894313116571</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009839702793890482</v>
+        <v>0.0009839702793890464</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009839702793890482</v>
+        <v>0.0009839702793890464</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009832544025222267</v>
+        <v>0.000983254402522223</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009850358955308626</v>
+        <v>0.0009850358955308636</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009735269218803988</v>
+        <v>0.0009735269218803951</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009850358955308626</v>
+        <v>0.0009850358955308636</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009850358955308626</v>
+        <v>0.0009850358955308636</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009850358955308626</v>
+        <v>0.0009850358955308636</v>
       </c>
     </row>
     <row r="6">
@@ -2259,34 +2259,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001381622363800134</v>
+        <v>0.001381622363800129</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002102694057646358</v>
+        <v>0.002102694057640708</v>
       </c>
       <c r="D6" t="n">
         <v>0.002240855403228209</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001896235853578204</v>
+        <v>0.001896235853578206</v>
       </c>
       <c r="F6" t="n">
         <v>0.001398929750932922</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002091505593843563</v>
+        <v>0.002091505593843559</v>
       </c>
       <c r="H6" t="n">
         <v>0.002093287086853995</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002081778113201732</v>
+        <v>0.002081778113201731</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002093426949152444</v>
+        <v>0.002093426949152446</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001368402826216735</v>
+        <v>0.001368402826216734</v>
       </c>
       <c r="L6" t="n">
         <v>0.002836680398327907</v>
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001623389797811534</v>
+        <v>0.001623389797811533</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001999233220623277</v>
+        <v>0.001999233220623275</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00200000641134853</v>
+        <v>0.002000006411348526</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002423104529675018</v>
+        <v>0.002423104529675014</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00198849704211017</v>
+        <v>0.001988497042110168</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001998224640232945</v>
+        <v>0.00199822464023294</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00200000613324158</v>
+        <v>0.002000006133241578</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001988497159591114</v>
+        <v>0.001988497159591113</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00200000613324158</v>
+        <v>0.002000006133241578</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001772940083441778</v>
+        <v>0.001525778869078643</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00200000613324158</v>
+        <v>0.002000006133241578</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003158151083911235</v>
+        <v>0.003158151083911238</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001003053942079239</v>
+        <v>0.001003053942079238</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001507862694660611</v>
+        <v>0.001507862694660612</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00126007265526358</v>
+        <v>0.001260072655263581</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00126007265526358</v>
+        <v>0.001260072655263581</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001269463582284926</v>
+        <v>0.001269463582284925</v>
       </c>
       <c r="H8" t="n">
         <v>0.00150075375687253</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00126007265526358</v>
+        <v>0.001260072655263581</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001387889472733904</v>
+        <v>0.001387889472733906</v>
       </c>
       <c r="K8" t="n">
         <v>0.001872693809971352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001528843405384197</v>
+        <v>0.001528843405384198</v>
       </c>
     </row>
     <row r="9">
@@ -2379,16 +2379,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003114526341833952</v>
+        <v>0.003114526341833947</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00103712990321982</v>
+        <v>0.001037129903219819</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001571187723754935</v>
+        <v>0.001571187723754936</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001252014208560741</v>
+        <v>0.001252014208560742</v>
       </c>
       <c r="F9" t="n">
         <v>0.001252014208560742</v>
@@ -2397,19 +2397,19 @@
         <v>0.001305784292150731</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001568453982102123</v>
+        <v>0.001568453982102122</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001252014208560741</v>
+        <v>0.001252014208560742</v>
       </c>
       <c r="J9" t="n">
         <v>0.001464994887074983</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001854078758692988</v>
+        <v>0.001854078758692989</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001527852803597039</v>
+        <v>0.001527852803597038</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002295362818849301</v>
+        <v>0.0022953628188493</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001806206675995393</v>
+        <v>0.001806206675995396</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009362671141319131</v>
+        <v>0.009362671141319152</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004638717644930786</v>
+        <v>0.004638717644930795</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004638717644930786</v>
+        <v>0.004638717644930795</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009790515569171028</v>
+        <v>0.009790515569171007</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02706358641093285</v>
+        <v>0.0270635864109329</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004638717644930786</v>
+        <v>0.004638717644930795</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02671771821334063</v>
+        <v>0.02671771821334061</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005305409492797769</v>
+        <v>0.005305409492797756</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02273987961328348</v>
+        <v>0.02273987961328349</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005445549919631973</v>
+        <v>0.0005445549919631974</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004592496206228292</v>
+        <v>0.0004592496206228296</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005445549919631973</v>
+        <v>0.0005445549919631974</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005576403716071065</v>
+        <v>0.000557640371607105</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005576403716071056</v>
+        <v>0.0005576403716071052</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005425071956086767</v>
+        <v>0.0005425071956086765</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005445549919631973</v>
+        <v>0.0005445549919631974</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005312738395232919</v>
+        <v>0.0005312738395232916</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005445549919631973</v>
+        <v>0.0005445549919631974</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005445549919631973</v>
+        <v>0.0005445549919631974</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005445549919631973</v>
+        <v>0.0005445549919631974</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001997533889781902</v>
+        <v>0.001325042088928075</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001296289512232399</v>
+        <v>0.001296289512232392</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001327729209839713</v>
+        <v>0.001327729209839674</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00122117658125618</v>
+        <v>0.00122117658125619</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001313782488822856</v>
+        <v>0.001313782488822855</v>
       </c>
       <c r="G4" t="n">
         <v>0.001322994292573554</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002048697620225629</v>
+        <v>0.002048697620225627</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001984252737341995</v>
+        <v>0.001311760936488169</v>
       </c>
       <c r="J4" t="n">
         <v>0.002008106504388938</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001313967924239291</v>
+        <v>0.00131396792423929</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001328899858824941</v>
+        <v>0.001328899858824942</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001055702661523208</v>
+        <v>0.001055702661523207</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00105468303970181</v>
+        <v>0.001054683039701809</v>
       </c>
       <c r="D5" t="n">
         <v>0.001055654984584607</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00105541772139096</v>
+        <v>0.001055417721390958</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00105541772139096</v>
+        <v>0.001055417721390958</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001053654865168688</v>
+        <v>0.001053654865168687</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001055702661523208</v>
+        <v>0.001055702661523207</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001042421509083303</v>
+        <v>0.001042421509083302</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001055702661523208</v>
+        <v>0.001055702661523207</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001055702661523208</v>
+        <v>0.001055702661523207</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001055702661523208</v>
+        <v>0.001055702661523207</v>
       </c>
     </row>
     <row r="6">
@@ -2658,34 +2658,34 @@
         <v>0.001489973541824262</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002280506568280743</v>
+        <v>0.002280506568280739</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002430411032004242</v>
+        <v>0.002430411032004238</v>
       </c>
       <c r="E6" t="n">
         <v>0.002053873420881279</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001509164351905485</v>
+        <v>0.001509164351905483</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002266848523441019</v>
+        <v>0.002266848523441017</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002268896319795137</v>
+        <v>0.002268896319795131</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002255615167355634</v>
+        <v>0.00225561516735563</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002269049400229264</v>
+        <v>0.002269049400229262</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001475504651341687</v>
+        <v>0.001475504651341686</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003082546293657104</v>
+        <v>0.003082546293657097</v>
       </c>
     </row>
     <row r="7">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002028786412423402</v>
+        <v>0.002028786412423403</v>
       </c>
       <c r="C7" t="n">
         <v>0.002515806921196448</v>
@@ -2707,25 +2707,25 @@
         <v>0.003066733155641059</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002503545077721771</v>
+        <v>0.002503545077721769</v>
       </c>
       <c r="G7" t="n">
         <v>0.002514778746663322</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002516826543017847</v>
+        <v>0.002516826543017846</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002503545390577939</v>
+        <v>0.002503545390577937</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002516826543017847</v>
+        <v>0.002516826543017846</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001902296848253563</v>
+        <v>0.001902296848253564</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002516826543017847</v>
+        <v>0.002516826543017846</v>
       </c>
     </row>
     <row r="8">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00309848775368726</v>
+        <v>0.003098487753687259</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001099471853667181</v>
+        <v>0.00109947185366718</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001494520100930839</v>
+        <v>0.001494520100930838</v>
       </c>
       <c r="E8" t="n">
         <v>0.001308222657391522</v>
@@ -2750,22 +2750,22 @@
         <v>0.001308222657391522</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001234738446408814</v>
+        <v>0.001234738446408813</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001158248357871041</v>
+        <v>0.00115824835787104</v>
       </c>
       <c r="I8" t="n">
         <v>0.001308222657391522</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001292818306763072</v>
+        <v>0.001292818306763071</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001832886177719394</v>
+        <v>0.00183288617771939</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001411749793996181</v>
+        <v>0.00141174979399618</v>
       </c>
     </row>
     <row r="9">
@@ -2775,19 +2775,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003063198054793013</v>
+        <v>0.003063198054793014</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001087275058211181</v>
+        <v>0.00108727505821118</v>
       </c>
       <c r="D9" t="n">
         <v>0.001577402814152955</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001330548531964355</v>
+        <v>0.001330548531964356</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001330548531964355</v>
+        <v>0.001330548531964356</v>
       </c>
       <c r="G9" t="n">
         <v>0.001323787858349058</v>
@@ -2796,16 +2796,16 @@
         <v>0.001440940000333455</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001330548531964355</v>
+        <v>0.001330548531964356</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001592749398963823</v>
+        <v>0.001592749398963822</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001856090076907899</v>
+        <v>0.001856090076907895</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001634257683851955</v>
+        <v>0.001634257683851954</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001426569029939343</v>
+        <v>0.001426569029939341</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001553886617342954</v>
+        <v>0.001553886617342953</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002095198327437073</v>
+        <v>0.002095198327437071</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003188964497113134</v>
+        <v>0.003188964497113143</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003188964497113134</v>
+        <v>0.003188964497113143</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002665098779850052</v>
+        <v>0.002665098779850055</v>
       </c>
       <c r="H2" t="n">
         <v>0.00340218462821194</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003188964497113134</v>
+        <v>0.003188964497113143</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009219380818927996</v>
+        <v>0.009219380818927991</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001829838045788947</v>
+        <v>0.001829838045788946</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004154688373875849</v>
+        <v>0.004154688373875845</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005181644144748776</v>
+        <v>0.0005181644144748779</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004505888937986674</v>
+        <v>0.0004505888937986666</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005181644144748776</v>
+        <v>0.0005181644144748779</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005886490095354317</v>
+        <v>0.0005886490095354308</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005886490095354322</v>
+        <v>0.000588649009535431</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005164444416674775</v>
+        <v>0.0005164444416674763</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005181644144748776</v>
+        <v>0.0005181644144748779</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005069970595917439</v>
+        <v>0.0005069970595917427</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005181644144748776</v>
+        <v>0.0005181644144748779</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005181644144748776</v>
+        <v>0.0005181644144748779</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005181644144748776</v>
+        <v>0.0005181644144748779</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001263822983243038</v>
+        <v>0.001263822983243035</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001246730149436522</v>
+        <v>0.001246730149436528</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00188275912552101</v>
+        <v>0.001261075960073505</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001181608907829616</v>
+        <v>0.001181608907829614</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001259490853542444</v>
+        <v>0.001259490853542441</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001262103010435638</v>
+        <v>0.001876062729579813</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001915207208551613</v>
+        <v>0.001915207208551609</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001252655628359905</v>
+        <v>0.001866615347504079</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00131921153835259</v>
+        <v>0.001319211538352589</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00126107602090233</v>
+        <v>0.001261076020902328</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001260730168669843</v>
+        <v>0.001260730168669836</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009776283896510097</v>
+        <v>0.0009776283896510045</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009769165179371153</v>
+        <v>0.0009769165179371094</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009775831993368979</v>
+        <v>0.0009775831993368929</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009824506638299322</v>
+        <v>0.0009824506638299274</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009824506638299322</v>
+        <v>0.0009824506638299274</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000975908416843611</v>
+        <v>0.0009759084168436056</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009776283896510097</v>
+        <v>0.0009776283896510045</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000966461034767877</v>
+        <v>0.0009664610347678704</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009776283896510097</v>
+        <v>0.0009776283896510045</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009776283896510097</v>
+        <v>0.0009776283896510045</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009776283896510097</v>
+        <v>0.0009776283896510045</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001367951910726789</v>
+        <v>0.001367951910726788</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002087835151530401</v>
+        <v>0.002087835151530399</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002219283818771935</v>
+        <v>0.002219283818771931</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001882891205267872</v>
+        <v>0.001882891205267867</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001388701337206241</v>
+        <v>0.001388701337206239</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002071352503314101</v>
+        <v>0.002071352503314097</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002073072476121843</v>
+        <v>0.00207307247612184</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002061905121238366</v>
+        <v>0.002061905121238363</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002073211052267091</v>
+        <v>0.002073211052267088</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001354853934236648</v>
+        <v>0.001354853934236645</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002809629867671079</v>
+        <v>0.002809629867671072</v>
       </c>
     </row>
     <row r="7">
@@ -3091,34 +3091,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001675319817560084</v>
+        <v>0.001675319817560083</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002066518053629432</v>
+        <v>0.002066518053629431</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002067230206986743</v>
+        <v>0.002067230206986742</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002508318761175402</v>
+        <v>0.002508318761175401</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002056062555714607</v>
+        <v>0.002056062555714606</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002065509952535928</v>
+        <v>0.002065509952535927</v>
       </c>
       <c r="H7" t="n">
         <v>0.002067229925343326</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002056062570460195</v>
+        <v>0.002056062570460193</v>
       </c>
       <c r="J7" t="n">
         <v>0.002067229925343326</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001840155788202853</v>
+        <v>0.00157374507094243</v>
       </c>
       <c r="L7" t="n">
         <v>0.002067229925343326</v>
@@ -3131,19 +3131,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003080893018728328</v>
+        <v>0.003080893018728332</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00108648067223479</v>
+        <v>0.001086480672234789</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001641740777196004</v>
+        <v>0.001641740777196003</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001325506947614027</v>
+        <v>0.001325506947614026</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001325506947614027</v>
+        <v>0.001325506947614026</v>
       </c>
       <c r="G8" t="n">
         <v>0.001370923561656327</v>
@@ -3152,16 +3152,16 @@
         <v>0.001618579994172915</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001325506947614027</v>
+        <v>0.001325506947614026</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001663138323152336</v>
+        <v>0.001663138323152335</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001894102076021647</v>
+        <v>0.001894102076021651</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00153548695666939</v>
+        <v>0.001535486956669389</v>
       </c>
     </row>
     <row r="9">
@@ -3171,13 +3171,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003035642613446462</v>
+        <v>0.003035642613446464</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001072378385128023</v>
+        <v>0.001072378385128024</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001626994768351344</v>
+        <v>0.001626994768351343</v>
       </c>
       <c r="E9" t="n">
         <v>0.001330844064627701</v>
@@ -3198,7 +3198,7 @@
         <v>0.001742136570759756</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001871583980137915</v>
+        <v>0.001871583980137918</v>
       </c>
       <c r="L9" t="n">
         <v>0.001544232228649839</v>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001272671048087207</v>
+        <v>0.001272671048087206</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001504489438004672</v>
+        <v>0.001504489438004688</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001865272314112858</v>
+        <v>0.001865272314112856</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00220636059353065</v>
+        <v>0.002206360593530636</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00220636059353065</v>
+        <v>0.002206360593530636</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00183285484361042</v>
+        <v>0.001832854843610402</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00227153158694553</v>
+        <v>0.002271531586945525</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00220636059353065</v>
+        <v>0.002206360593530636</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003009133444787351</v>
+        <v>0.003009133444787356</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001368196355616886</v>
+        <v>0.001368196355616881</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001834435347385609</v>
+        <v>0.001834435347385608</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005082721716442732</v>
+        <v>0.0005082721716442728</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004493174276809609</v>
+        <v>0.0004493174276809611</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005082721716442732</v>
+        <v>0.0005082721716442728</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000558709123968836</v>
+        <v>0.0005587091239688333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005587091239688357</v>
+        <v>0.0005587091239688334</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005066415237221082</v>
+        <v>0.0005066415237221259</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005082721716442732</v>
+        <v>0.0005082721716442728</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000497723217869782</v>
+        <v>0.0004977232178698127</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005082721716442732</v>
+        <v>0.0005082721716442728</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005082721716442732</v>
+        <v>0.0005082721716442728</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005082721716442732</v>
+        <v>0.0005082721716442728</v>
       </c>
     </row>
     <row r="4">
@@ -3367,34 +3367,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001862801908050732</v>
+        <v>0.001862801908050731</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001241536308857211</v>
+        <v>0.001241536308857209</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001250822273255127</v>
+        <v>0.001250822273255128</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001170344724222022</v>
+        <v>0.001170344724222024</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001250221039470806</v>
+        <v>0.001250221039470805</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001861171260128566</v>
+        <v>0.001861171260128564</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001897439485169133</v>
+        <v>0.001897439485169131</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001245050663271734</v>
+        <v>0.001245050663271731</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001866459713731549</v>
+        <v>0.001866459713731548</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001255908043146676</v>
+        <v>0.001255908043146664</v>
       </c>
       <c r="L4" t="n">
         <v>0.00125118491161426</v>
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00095405492836403</v>
+        <v>0.0009540549283640297</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009533626686893617</v>
+        <v>0.0009533626686893612</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009540088195846558</v>
+        <v>0.000954008819584655</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000956358929175569</v>
+        <v>0.0009563589291755666</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000956358929175569</v>
+        <v>0.0009563589291755666</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009524242804418656</v>
+        <v>0.0009524242804418649</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00095405492836403</v>
+        <v>0.0009540549283640297</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000943505974589539</v>
+        <v>0.0009435059745895368</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00095405492836403</v>
+        <v>0.0009540549283640297</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00095405492836403</v>
+        <v>0.0009540549283640297</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00095405492836403</v>
+        <v>0.0009540549283640297</v>
       </c>
     </row>
     <row r="6">
@@ -3450,34 +3450,34 @@
         <v>0.001335412697381462</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002034506511810926</v>
+        <v>0.002034506511810925</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002165238815542407</v>
+        <v>0.002165238815542405</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001835346100547018</v>
+        <v>0.001835346100547014</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001354345272054472</v>
+        <v>0.00135434527205447</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002021090320283233</v>
+        <v>0.002021090320283229</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002022720968206405</v>
+        <v>0.002022720968206403</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002012172014430909</v>
+        <v>0.002012172014430907</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002022856043746083</v>
+        <v>0.002022856043746081</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001322645593405325</v>
+        <v>0.001322645593405324</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002740671928656716</v>
+        <v>0.002740671928656714</v>
       </c>
     </row>
     <row r="7">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001538904196167076</v>
+        <v>0.001538904196167075</v>
       </c>
       <c r="C7" t="n">
         <v>0.001893641651344917</v>
@@ -3499,25 +3499,25 @@
         <v>0.002293943528781812</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001883784941305569</v>
+        <v>0.00188378494130557</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001892703263097421</v>
+        <v>0.00189270326309742</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001894333911019585</v>
+        <v>0.001894333911019584</v>
       </c>
       <c r="I7" t="n">
         <v>0.001883784957245096</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001894333911019585</v>
+        <v>0.001894333911019584</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001688396648552633</v>
+        <v>0.001680041503046069</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001894333911019585</v>
+        <v>0.001894333911019584</v>
       </c>
     </row>
     <row r="8">
@@ -3527,34 +3527,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003036952466198932</v>
+        <v>0.003036952466198927</v>
       </c>
       <c r="C8" t="n">
         <v>0.001067016536896037</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001630746323504197</v>
+        <v>0.001630746323504196</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001247656417284948</v>
+        <v>0.001247656417284947</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001247656417284948</v>
+        <v>0.001247656417284947</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001330180178696251</v>
+        <v>0.00133018017869625</v>
       </c>
       <c r="H8" t="n">
         <v>0.00162632149950495</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001247656417284948</v>
+        <v>0.001247656417284947</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001501146130353985</v>
+        <v>0.001501146130353984</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001879789747578684</v>
+        <v>0.001879789747578682</v>
       </c>
       <c r="L8" t="n">
         <v>0.001548719660163809</v>
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002990275981461371</v>
+        <v>0.002990275981461368</v>
       </c>
       <c r="C9" t="n">
         <v>0.001052518926433698</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00161291669864038</v>
+        <v>0.001612916698640379</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001240483230483955</v>
+        <v>0.001240483230483954</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001240483230483955</v>
+        <v>0.001240483230483954</v>
       </c>
       <c r="G9" t="n">
         <v>0.0013160457295685</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001611149212265465</v>
+        <v>0.001611149212265464</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001240483230483955</v>
+        <v>0.001240483230483954</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001499589856004763</v>
+        <v>0.001499589856004761</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001851004012201263</v>
+        <v>0.001851004012201261</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001528949537701134</v>
+        <v>0.001528949537701133</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001989668864084115</v>
+        <v>0.001989668864084132</v>
       </c>
       <c r="C2" t="n">
         <v>0.001654214787601852</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003352436325151243</v>
+        <v>0.003352436325151239</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00424203936262783</v>
+        <v>0.004242039362627853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00424203936262783</v>
+        <v>0.004242039362627853</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005071000989675694</v>
+        <v>0.005071000989675642</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02264136541858735</v>
+        <v>0.02264136541858738</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00424203936262783</v>
+        <v>0.004242039362627853</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006387593371240739</v>
+        <v>0.00638759337124075</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002968793521750254</v>
+        <v>0.002968793521750262</v>
       </c>
       <c r="L2" t="n">
-        <v>0.018514464053591</v>
+        <v>0.01851446405359099</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005373847077771959</v>
+        <v>0.0005373847077772</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004534941410524082</v>
+        <v>0.0004534941410524083</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005373847077771959</v>
+        <v>0.0005373847077772</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005608458666992809</v>
+        <v>0.0005608458666992838</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005608458666992811</v>
+        <v>0.0005608458666992838</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005354929026662407</v>
+        <v>0.0005354929026662447</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005373847077771959</v>
+        <v>0.0005373847077772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005250921776133702</v>
+        <v>0.0005250921776133726</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005373847077771959</v>
+        <v>0.0005373847077772</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005373847077771959</v>
+        <v>0.0005373847077772</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005373847077771959</v>
+        <v>0.0005373847077772</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00196244176393557</v>
+        <v>0.001301848197388178</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001279447417361458</v>
+        <v>0.001279447417361474</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001298430576871006</v>
+        <v>0.001298430576870941</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001206879990465831</v>
+        <v>0.001206879990465834</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001292587532834754</v>
+        <v>0.001292587532834755</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001960549958824613</v>
+        <v>0.001960549958824615</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002009940283754708</v>
+        <v>0.002009940283754718</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001289555667224337</v>
+        <v>0.001950149233771749</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001970718941786625</v>
+        <v>0.001970718941786618</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001291909705385635</v>
+        <v>0.001291909705385648</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00130444443318865</v>
+        <v>0.001304444433188654</v>
       </c>
     </row>
     <row r="5">
@@ -3803,13 +3803,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001031947501813716</v>
+        <v>0.001031947501813706</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001031139944799114</v>
+        <v>0.001031139944799113</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001031900357765497</v>
+        <v>0.001031900357765511</v>
       </c>
       <c r="E5" t="n">
         <v>0.001034608635975759</v>
@@ -3818,22 +3818,22 @@
         <v>0.001034608635975759</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001030055696702758</v>
+        <v>0.001030055696702766</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001031947501813716</v>
+        <v>0.001031947501813706</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001019654971649892</v>
+        <v>0.001019654971649891</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001031947501813716</v>
+        <v>0.001031947501813706</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001031947501813716</v>
+        <v>0.001031947501813706</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001031947501813716</v>
+        <v>0.001031947501813706</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001453897005411123</v>
+        <v>0.001453897005411126</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002226259235418919</v>
+        <v>0.002226259235418916</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002369887183261071</v>
+        <v>0.002369887183261073</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002005743860452014</v>
+        <v>0.002005743860452016</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001474601984809171</v>
+        <v>0.001474601984809176</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002210679350765202</v>
+        <v>0.002210679350765209</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002212571155875324</v>
+        <v>0.002212571155875335</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002200278625712333</v>
+        <v>0.00220027862571234</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002212720256841712</v>
+        <v>0.002212720256841709</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001439804243583444</v>
+        <v>0.001439804243583457</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00300506974511291</v>
+        <v>0.003005069745112931</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001916070147012607</v>
+        <v>0.001916070147012616</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002373294427727725</v>
+        <v>0.002373294427727714</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00237410209842455</v>
+        <v>0.002374102098424548</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002890368251455807</v>
+        <v>0.002890368251455802</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002361809186748315</v>
+        <v>0.002361809186748312</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002372210179631371</v>
+        <v>0.002372210179631369</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002374101984742329</v>
+        <v>0.002374101984742318</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002361809454578507</v>
+        <v>0.0023618094545785</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002374101984742329</v>
+        <v>0.002374101984742318</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002097949561513525</v>
+        <v>0.002108716586947021</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002374101984742329</v>
+        <v>0.002374101984742318</v>
       </c>
     </row>
     <row r="8">
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0030777900700896</v>
+        <v>0.003077790070089602</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001096216890038797</v>
+        <v>0.001096216890038798</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001624835413969981</v>
+        <v>0.001624835413969979</v>
       </c>
       <c r="E8" t="n">
         <v>0.001310101757923876</v>
@@ -3938,22 +3938,22 @@
         <v>0.001310101757923876</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001326920745661856</v>
+        <v>0.001326920745661859</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001239812793858537</v>
+        <v>0.001239812793858536</v>
       </c>
       <c r="I8" t="n">
         <v>0.001310101757923876</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001713481909249917</v>
+        <v>0.001713481909249919</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001873860645366807</v>
+        <v>0.001873860645366799</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001488713541348293</v>
+        <v>0.001488713541348297</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003038876846383629</v>
+        <v>0.003038876846383624</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001082151450179135</v>
+        <v>0.001082151450179136</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001625581923063747</v>
+        <v>0.001625581923063754</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001327241422245636</v>
+        <v>0.001327241422245637</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001327241422245636</v>
+        <v>0.001327241422245637</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001353478515277828</v>
+        <v>0.00135347851527783</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001469182760198421</v>
+        <v>0.001469182760198425</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001327241422245636</v>
+        <v>0.001327241422245637</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001749312522311329</v>
+        <v>0.001749312522311332</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001865449113661578</v>
+        <v>0.001865449113661575</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001661285216650933</v>
+        <v>0.001661285216650935</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001524705120260531</v>
+        <v>0.001524705120260523</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001612729752052667</v>
+        <v>0.001612729752052666</v>
       </c>
       <c r="D2" t="n">
         <v>0.002001222502615638</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003048136734288679</v>
+        <v>0.00304813673428866</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003048136734288679</v>
+        <v>0.00304813673428866</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002083255916133661</v>
+        <v>0.00208325591613363</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002474129315241066</v>
+        <v>0.002474129315241057</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003048136734288679</v>
+        <v>0.00304813673428866</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00352958717440971</v>
+        <v>0.003529587174409709</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001886615949083802</v>
+        <v>0.001886615949083769</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002008448644312245</v>
+        <v>0.002008448644312231</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005193774656857263</v>
+        <v>0.0005193774656857245</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004504955006404736</v>
+        <v>0.0004504955006404731</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005193774656857263</v>
+        <v>0.0005193774656857245</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0006020879298062659</v>
+        <v>0.0006020879298062655</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0006020879298062657</v>
+        <v>0.0006020879298062658</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005176935956037489</v>
+        <v>0.0005176935956037465</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005193774656857263</v>
+        <v>0.0005193774656857245</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005084366207859409</v>
+        <v>0.000508436620785939</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005193774656857263</v>
+        <v>0.0005193774656857245</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005193774656857263</v>
+        <v>0.0005193774656857245</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005193774656857263</v>
+        <v>0.0005193774656857245</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001880208060719216</v>
+        <v>0.001264383476066253</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001247786846619183</v>
+        <v>0.001247786846619196</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001261773330617066</v>
+        <v>0.001261768720280009</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00118442320880708</v>
+        <v>0.001184423208807079</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001260982830474871</v>
+        <v>0.00126098283047487</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001262699605984274</v>
+        <v>0.001262699605984275</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001916503182607731</v>
+        <v>0.00191650318260773</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001253442631166467</v>
+        <v>0.001869267215819427</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001317824356830226</v>
+        <v>0.001885011966615831</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001262540932643151</v>
+        <v>0.001262540932643149</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001260524922964628</v>
+        <v>0.001260524922964626</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009775627956521665</v>
+        <v>0.0009775627956521622</v>
       </c>
       <c r="C5" t="n">
         <v>0.0009768934444054119</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009775180187146654</v>
+        <v>0.0009775180187146645</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009859697406751885</v>
+        <v>0.0009859697406751898</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009859697406751885</v>
+        <v>0.0009859697406751898</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000975878925570183</v>
+        <v>0.0009758789255701832</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009775627956521665</v>
+        <v>0.0009775627956521622</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009666219507523752</v>
+        <v>0.0009666219507523763</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009775627956521665</v>
+        <v>0.0009775627956521622</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009775627956521665</v>
+        <v>0.0009775627956521622</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009775627956521665</v>
+        <v>0.0009775627956521622</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001365441873708456</v>
+        <v>0.001365441873708452</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002087154423555943</v>
+        <v>0.002087154423555939</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002215057160891426</v>
+        <v>0.002215057160891419</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001882444596188157</v>
+        <v>0.001882444596188155</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001388375800649552</v>
+        <v>0.001388375800649547</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002067456767888946</v>
+        <v>0.002067456767888936</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002069140637970837</v>
+        <v>0.00206914063797083</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002058199793071138</v>
+        <v>0.002058199793071132</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002069278934654609</v>
+        <v>0.002069278934654602</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001352370307908135</v>
+        <v>0.001352370307908136</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00280421283931254</v>
+        <v>0.002804212839312533</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001667082721721353</v>
+        <v>0.001667082721721348</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002056120791058429</v>
+        <v>0.002056120791058423</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002056790419952012</v>
+        <v>0.002056790419952004</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002495563648454878</v>
+        <v>0.002495563648454873</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002045849297276381</v>
+        <v>0.002045849297276379</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002055106272223199</v>
+        <v>0.002055106272223195</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002056790142305181</v>
+        <v>0.002056790142305176</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00204584929740539</v>
+        <v>0.002045849297405387</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002056790142305181</v>
+        <v>0.002056790142305176</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001566078865302452</v>
+        <v>0.001830992249097713</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002056790142305181</v>
+        <v>0.002056790142305176</v>
       </c>
     </row>
     <row r="8">
@@ -4319,13 +4319,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002877167970514394</v>
+        <v>0.002877167970514395</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001086239210944975</v>
+        <v>0.001086239210944976</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001644853070997256</v>
+        <v>0.001644853070997258</v>
       </c>
       <c r="E8" t="n">
         <v>0.00133249032117412</v>
@@ -4337,16 +4337,16 @@
         <v>0.001368724561286139</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001639370777626113</v>
+        <v>0.001639370777626114</v>
       </c>
       <c r="I8" t="n">
         <v>0.00133249032117412</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001795644537564727</v>
+        <v>0.001795644537564724</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001897914903203674</v>
+        <v>0.001897914903203679</v>
       </c>
       <c r="L8" t="n">
         <v>0.001584229226403066</v>
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002836482880130321</v>
+        <v>0.002836482880130318</v>
       </c>
       <c r="C9" t="n">
         <v>0.001072986192907626</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001628782595445025</v>
+        <v>0.001628782595445028</v>
       </c>
       <c r="E9" t="n">
         <v>0.001335804888985648</v>
@@ -4374,7 +4374,7 @@
         <v>0.001335804888985648</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001357481354333613</v>
+        <v>0.001357481354333612</v>
       </c>
       <c r="H9" t="n">
         <v>0.001626588260805464</v>
@@ -4386,7 +4386,7 @@
         <v>0.001796509219904832</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001876180668557139</v>
+        <v>0.00187618066855714</v>
       </c>
       <c r="L9" t="n">
         <v>0.001566099653557854</v>
@@ -4475,31 +4475,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001351985440433204</v>
+        <v>0.001351985440433205</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001519534855004761</v>
+        <v>0.001519534855004756</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001808870791622341</v>
+        <v>0.001808870791622343</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002180721129158558</v>
+        <v>0.00218072112915854</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002180721129158558</v>
+        <v>0.00218072112915854</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001803384491319234</v>
+        <v>0.00180338449131921</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002209535247163103</v>
+        <v>0.002209535247163107</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002180721129158558</v>
+        <v>0.00218072112915854</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0029737855297031</v>
+        <v>0.002973785529703103</v>
       </c>
       <c r="K2" t="n">
         <v>0.001645433020863331</v>
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005093152630714524</v>
+        <v>0.0005093152630714533</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000449071921074593</v>
+        <v>0.0004490719210745898</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005093152630714524</v>
+        <v>0.0005093152630714533</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005667003786756881</v>
+        <v>0.0005667003786756893</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005667003786756874</v>
+        <v>0.0005667003786756894</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005077261408004359</v>
+        <v>0.0005077261408004368</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005093152630714524</v>
+        <v>0.0005093152630714533</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004990403614343902</v>
+        <v>0.0004990403614343907</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005093152630714524</v>
+        <v>0.0005093152630714533</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005093152630714524</v>
+        <v>0.0005093152630714533</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005093152630714524</v>
+        <v>0.0005093152630714533</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001867723057667456</v>
+        <v>0.001258728954064153</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001244382705987842</v>
+        <v>0.001244382705987862</v>
       </c>
       <c r="D4" t="n">
         <v>0.001253626662681105</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001174360187256441</v>
+        <v>0.001174360187256442</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001254014078265517</v>
+        <v>0.001254014078265516</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00186613393539644</v>
+        <v>0.001866133935396439</v>
       </c>
       <c r="H4" t="n">
         <v>0.00190211456660244</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001248454052427091</v>
+        <v>0.001857448156030393</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001871951468273287</v>
+        <v>0.001312201455480114</v>
       </c>
       <c r="K4" t="n">
         <v>0.001259791736337682</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001254241630889801</v>
+        <v>0.001254241630889747</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009544484692148489</v>
+        <v>0.0009544484692148485</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009537643503437258</v>
+        <v>0.0009537643503437225</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009544025926442653</v>
+        <v>0.0009544025926442644</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009590070891020938</v>
+        <v>0.0009590070891020927</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009590070891020938</v>
+        <v>0.0009590070891020927</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009528593469438318</v>
+        <v>0.0009528593469438305</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009544484692148489</v>
+        <v>0.0009544484692148485</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009441735675777854</v>
+        <v>0.0009441735675777851</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009544484692148489</v>
+        <v>0.0009544484692148485</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009544484692148489</v>
+        <v>0.0009544484692148485</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009544484692148489</v>
+        <v>0.0009544484692148485</v>
       </c>
     </row>
     <row r="6">
@@ -4635,31 +4635,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001333824096188584</v>
+        <v>0.001333824096188587</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002033881792294887</v>
+        <v>0.002033881792294888</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002162518808837323</v>
+        <v>0.002162518808837324</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001835043321118601</v>
+        <v>0.001835043321118605</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00135418238439852</v>
+        <v>0.001354182384398521</v>
       </c>
       <c r="G6" t="n">
         <v>0.002018606151598931</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002020195273870782</v>
+        <v>0.002020195273870783</v>
       </c>
       <c r="I6" t="n">
         <v>0.002009920372232886</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002020330165219214</v>
+        <v>0.002020330165219216</v>
       </c>
       <c r="K6" t="n">
         <v>0.001321074399201317</v>
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001539017766680618</v>
+        <v>0.001539017766680617</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001893826232856296</v>
+        <v>0.001893826232856292</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001894510614637812</v>
+        <v>0.001894510614637813</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00229446657895335</v>
+        <v>0.002294466578953347</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001884235438659709</v>
+        <v>0.001884235438659701</v>
       </c>
       <c r="G7" t="n">
         <v>0.001892921229456402</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001894510351727422</v>
+        <v>0.001894510351727416</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001884235450090357</v>
+        <v>0.001884235450090353</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001894510351727422</v>
+        <v>0.001894510351727416</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001680180038977153</v>
+        <v>0.001680180038977151</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001894510351727422</v>
+        <v>0.001894510351727416</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00231232634040422</v>
+        <v>0.002312326340404216</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001066783208211799</v>
+        <v>0.001066783208211798</v>
       </c>
       <c r="D8" t="n">
         <v>0.001632999919350118</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001250912609171557</v>
+        <v>0.001250912609171556</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001250912609171557</v>
+        <v>0.001250912609171556</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00126896590138859</v>
+        <v>0.001268965901388588</v>
       </c>
       <c r="H8" t="n">
         <v>0.001628533588330895</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001250912609171557</v>
+        <v>0.001250912609171556</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00150495300858548</v>
+        <v>0.001504953008585481</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001876008976098453</v>
+        <v>0.001876008976098446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00155102522573743</v>
+        <v>0.001551025225737429</v>
       </c>
     </row>
     <row r="9">
@@ -4755,22 +4755,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002278103948046881</v>
+        <v>0.002278103948046878</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001052519808922341</v>
+        <v>0.00105251980892234</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00161437123572745</v>
+        <v>0.001614371235727451</v>
       </c>
       <c r="E9" t="n">
         <v>0.001243358357991043</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001243358357991043</v>
+        <v>0.001243358357991042</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001255416531175253</v>
+        <v>0.001255416531175252</v>
       </c>
       <c r="H9" t="n">
         <v>0.001612585640464655</v>
@@ -4782,7 +4782,7 @@
         <v>0.001502894542290623</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001851200128831309</v>
+        <v>0.001851200128831289</v>
       </c>
       <c r="L9" t="n">
         <v>0.001531295052836573</v>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02149815209962284</v>
+        <v>0.02149815209962279</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008282537020936082</v>
+        <v>0.008282537020936096</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02589074065730742</v>
+        <v>0.02589074065730744</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008282537020936082</v>
+        <v>0.008282537020936096</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008282537020936082</v>
+        <v>0.008282537020936096</v>
       </c>
       <c r="G2" t="n">
         <v>0.02657078687345922</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06494450836581515</v>
+        <v>0.06494450836581532</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008282537020936082</v>
+        <v>0.008282537020936096</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03306729572857037</v>
+        <v>0.0330672957285703</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01167892897750547</v>
+        <v>0.0116789289775055</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0282619955249833</v>
+        <v>0.02826199552498329</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006232923342840838</v>
+        <v>0.0006232923342840839</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005379345641720655</v>
+        <v>0.0005379345641720632</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006232923342840838</v>
+        <v>0.0006232923342840839</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005554365248662361</v>
+        <v>0.0005554365248662344</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005554365248662359</v>
+        <v>0.0005554365248662343</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006209520726537884</v>
+        <v>0.0006209520726537874</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006232923342840838</v>
+        <v>0.0006232923342840839</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006082314507898673</v>
+        <v>0.0006082314507898672</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006232923342840838</v>
+        <v>0.0006232923342840839</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006232923342840838</v>
+        <v>0.0006232923342840839</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006232923342840838</v>
+        <v>0.0006232923342840839</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002238919726840915</v>
+        <v>0.002238919726840912</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001402900081515171</v>
+        <v>0.001402900081515165</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001470164298461922</v>
+        <v>0.001470164298461911</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001318767497277541</v>
+        <v>0.001318767497277539</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001435864284778553</v>
+        <v>0.001435864284778549</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001453720533835125</v>
+        <v>0.002236579465210613</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001471425994695889</v>
+        <v>0.002288106599076345</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0022238588433467</v>
+        <v>0.002223858843346698</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002251516488533108</v>
+        <v>0.002251516488533107</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001433841667055765</v>
+        <v>0.001433841667055763</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001485372512057261</v>
+        <v>0.00148537251205726</v>
       </c>
     </row>
     <row r="5">
@@ -4994,25 +4994,25 @@
         <v>0.001186791284202813</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001171730400708598</v>
+        <v>0.001171730400708597</v>
       </c>
       <c r="D5" t="n">
         <v>0.001186737091859441</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001170881276883859</v>
+        <v>0.001170881276883855</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001170881276883859</v>
+        <v>0.001170881276883855</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001184451022572517</v>
+        <v>0.001184451022572516</v>
       </c>
       <c r="H5" t="n">
         <v>0.001186791284202813</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001171730400708598</v>
+        <v>0.001171730400708597</v>
       </c>
       <c r="J5" t="n">
         <v>0.001186791284202813</v>
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00167298730173045</v>
+        <v>0.001672987301730448</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002510473601355272</v>
+        <v>0.002510473601355271</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002703012542432665</v>
+        <v>0.002703012542432668</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002277199531484587</v>
+        <v>0.002277199531484588</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001684494927659528</v>
+        <v>0.00168449492765953</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002523771389396272</v>
+        <v>0.002523771389396271</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002526111651026581</v>
+        <v>0.002526111651026586</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002511050767532351</v>
+        <v>0.002511050767532352</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002526279314274552</v>
+        <v>0.002526279314274555</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001657140078957754</v>
+        <v>0.001657140078957757</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003417271370844157</v>
+        <v>0.003417271370844163</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00253529979151963</v>
+        <v>0.002535299791519626</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003130041101644076</v>
+        <v>0.003130041101644069</v>
       </c>
       <c r="D7" t="n">
         <v>0.003145102096107112</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003833738853453659</v>
+        <v>0.003833738853453656</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003130040181606334</v>
+        <v>0.003130040181606327</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003142761723507993</v>
+        <v>0.003142761723508</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003145101985138296</v>
+        <v>0.003145101985138288</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003130041101644076</v>
+        <v>0.003130041101644069</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003145101985138296</v>
+        <v>0.003145101985138288</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002791780245951538</v>
+        <v>0.002791780245951534</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003145101985138296</v>
+        <v>0.003145101985138288</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001193879135286241</v>
+        <v>0.00119387913528624</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001482715483268433</v>
+        <v>0.001482715483268435</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001104896441990716</v>
+        <v>0.001104896441990715</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001482715483268433</v>
+        <v>0.001482715483268435</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001482715483268433</v>
+        <v>0.001482715483268435</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001099770999563816</v>
+        <v>0.001099770999563817</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003761844845537583</v>
+        <v>0.000376184484553756</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001482715483268433</v>
+        <v>0.001482715483268435</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000985702107988952</v>
+        <v>0.0009857021079889517</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00143436131256388</v>
+        <v>0.001434361312563878</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0004694847803195241</v>
+        <v>0.001120639873079835</v>
       </c>
     </row>
     <row r="9">
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001449509684035801</v>
+        <v>0.001449509684035802</v>
       </c>
       <c r="C9" t="n">
         <v>0.001553079890622695</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001413283109086719</v>
+        <v>0.001413283109086717</v>
       </c>
       <c r="E9" t="n">
         <v>0.001553079890622695</v>
@@ -5166,10 +5166,10 @@
         <v>0.001553079890622695</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001409074092874705</v>
+        <v>0.001409074092874704</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001117690400182483</v>
+        <v>0.00111769040018248</v>
       </c>
       <c r="I9" t="n">
         <v>0.001553079890622695</v>
@@ -5178,10 +5178,10 @@
         <v>0.001364988960337997</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0015474700382552</v>
+        <v>0.001547470038255197</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0007736674192469526</v>
+        <v>0.001420104281490273</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01591916405163625</v>
+        <v>0.01591916405163624</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008297120456490142</v>
+        <v>0.008297120456490151</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02315697403724737</v>
+        <v>0.02315697403724725</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008297120456490142</v>
+        <v>0.008297120456490151</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008297120456490142</v>
+        <v>0.008297120456490151</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02289319673558905</v>
+        <v>0.02289319673558909</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05064779858968828</v>
+        <v>0.05064779858968826</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008297120456490142</v>
+        <v>0.008297120456490151</v>
       </c>
       <c r="J2" t="n">
         <v>0.02283627544235484</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0101429817534115</v>
+        <v>0.01014298175341151</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09580694330182549</v>
+        <v>0.03025152024391803</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000601909887309289</v>
+        <v>0.0006019098873092899</v>
       </c>
       <c r="C3" t="n">
         <v>0.0005341727468398131</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000601909887309289</v>
+        <v>0.0006019098873092901</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000549666439455484</v>
+        <v>0.0005496664394554845</v>
       </c>
       <c r="F3" t="n">
         <v>0.0005496664394554845</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000599742963040689</v>
+        <v>0.0005997429630406894</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000601909887309289</v>
+        <v>0.0006019098873092901</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000587970576675738</v>
+        <v>0.0005879705766757376</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000601909887309289</v>
+        <v>0.0006019098873092901</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000601909887309289</v>
+        <v>0.0006019098873092901</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000601909887309289</v>
+        <v>0.0006019098873092901</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001394866545979312</v>
+        <v>0.002119157315284515</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001350302509308051</v>
+        <v>0.001350302509308054</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001408638453182822</v>
+        <v>0.00140863845318283</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001269990119080487</v>
+        <v>0.001269990119080488</v>
       </c>
       <c r="F4" t="n">
         <v>0.001377227204699871</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001392699621710714</v>
+        <v>0.002116990391015916</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002157457592732591</v>
+        <v>0.002157457592732589</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001380927235345761</v>
+        <v>0.002105218004650965</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001455807952072566</v>
+        <v>0.00212739887105554</v>
       </c>
       <c r="K4" t="n">
         <v>0.001381160640048983</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001416875773046247</v>
+        <v>0.001416875773046248</v>
       </c>
     </row>
     <row r="5">
@@ -5387,13 +5387,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001118180129201015</v>
+        <v>0.001118180129201016</v>
       </c>
       <c r="C5" t="n">
         <v>0.001104240818567464</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001118129441954248</v>
+        <v>0.00111812944195425</v>
       </c>
       <c r="E5" t="n">
         <v>0.001103268199870018</v>
@@ -5405,19 +5405,19 @@
         <v>0.001116013204932416</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001118180129201015</v>
+        <v>0.001118180129201016</v>
       </c>
       <c r="I5" t="n">
         <v>0.001104240818567464</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001118180129201015</v>
+        <v>0.001118180129201016</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001118180129201015</v>
+        <v>0.001118180129201016</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001118180129201015</v>
+        <v>0.001118180129201016</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001560978992079418</v>
+        <v>0.001560978992079415</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002327365810749523</v>
+        <v>0.002327365810753719</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00250397301771861</v>
+        <v>0.002503973017718605</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002113821805273937</v>
+        <v>0.002113821805273936</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001571247474363061</v>
+        <v>0.00157124747436306</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002339852311024251</v>
+        <v>0.002339852311024249</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002342019235292946</v>
+        <v>0.00234201923529294</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0023280799246593</v>
+        <v>0.002328079924659299</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002342172731953607</v>
+        <v>0.002342172731953603</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001546470768585227</v>
+        <v>0.001546470768585225</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003157881078736879</v>
+        <v>0.003157881078736872</v>
       </c>
     </row>
     <row r="7">
@@ -5470,34 +5470,34 @@
         <v>0.002201469283219397</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002704611182042563</v>
+        <v>0.002704611182042558</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002718550669045786</v>
+        <v>0.002718550669045789</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003301311198702176</v>
+        <v>0.003301311198702167</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002704610466364544</v>
+        <v>0.002704610466364542</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002716383568407506</v>
+        <v>0.00271638356840751</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002718550492676114</v>
+        <v>0.002718550492676113</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002704611182042563</v>
+        <v>0.002704611182042558</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002718550492676114</v>
+        <v>0.002718550492676113</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002067452905590367</v>
+        <v>0.002067452905590366</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002718550492676114</v>
+        <v>0.002718550492676113</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001299889690109458</v>
+        <v>0.00129988969010946</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001457148861458594</v>
+        <v>0.001457148861458595</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001114540895966732</v>
+        <v>0.001114540895966736</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001457148861458594</v>
+        <v>0.001457148861458595</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001457148861458594</v>
+        <v>0.001457148861458595</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001133081466123368</v>
+        <v>0.00113308146612337</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0005890388339091161</v>
+        <v>0.0005890388339091188</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001457148861458594</v>
+        <v>0.001457148861458595</v>
       </c>
       <c r="J8" t="n">
         <v>0.001166075341068716</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001433682440170187</v>
+        <v>0.001433682440170188</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0003138167786230193</v>
+        <v>0.001022297789074908</v>
       </c>
     </row>
     <row r="9">
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001489275947873952</v>
+        <v>0.001489275947873953</v>
       </c>
       <c r="C9" t="n">
         <v>0.001537846976839629</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001413799659516402</v>
+        <v>0.001413799659516405</v>
       </c>
       <c r="E9" t="n">
         <v>0.001537846976839629</v>
@@ -5562,22 +5562,22 @@
         <v>0.001537846976839629</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001419488956371568</v>
+        <v>0.001419488956371569</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001200769788240979</v>
+        <v>0.001200769788240982</v>
       </c>
       <c r="I9" t="n">
         <v>0.001537846976839629</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001434971595963343</v>
+        <v>0.001434971595963346</v>
       </c>
       <c r="K9" t="n">
         <v>0.001543782099364579</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001376708005178942</v>
+        <v>0.001376708005178943</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01333721076049519</v>
+        <v>0.01333721076049509</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01038669751186687</v>
+        <v>0.01038669751186683</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0187389955990482</v>
+        <v>0.01873899559904818</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01038669751186687</v>
+        <v>0.01038669751186683</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01038669751186687</v>
+        <v>0.01038669751186683</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01938602615277394</v>
+        <v>0.01938602615277376</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03480583887154071</v>
+        <v>0.03480583887154076</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01038669751186687</v>
+        <v>0.01038669751186683</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01468716370953085</v>
+        <v>0.01468716370953077</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008434056881918877</v>
+        <v>0.008434056881918679</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08533182328199958</v>
+        <v>0.08533182328199966</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000605002923676481</v>
+        <v>0.0006050029236764792</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005478557994428907</v>
+        <v>0.0005478557994428876</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000605002923676481</v>
+        <v>0.0006050029236764793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005627310570238839</v>
+        <v>0.0005627310570238817</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005627310570238836</v>
+        <v>0.0005627310570238816</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006029916272008199</v>
+        <v>0.000602991627200819</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000605002923676481</v>
+        <v>0.0006050029236764793</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005920428185778031</v>
+        <v>0.0005920428185777996</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000605002923676481</v>
+        <v>0.0006050029236764793</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000605002923676481</v>
+        <v>0.0006050029236764793</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000605002923676481</v>
+        <v>0.0006050029236764793</v>
       </c>
     </row>
     <row r="4">
@@ -5746,34 +5746,34 @@
         <v>0.001399482088615791</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00136669695865831</v>
+        <v>0.001366696958658306</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002118848687931666</v>
+        <v>0.002118848687931661</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001285841404285685</v>
+        <v>0.001285841404285681</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001385723561380707</v>
+        <v>0.001385723561380705</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001397470792140132</v>
+        <v>0.001397470792140133</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002147954247572856</v>
+        <v>0.002147954247572851</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002099249377184526</v>
+        <v>0.002099249377184514</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002120082505843283</v>
+        <v>0.001458598696835021</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001389232761694325</v>
+        <v>0.001389232761694323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001423330047875091</v>
+        <v>0.001423330047875089</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001111878984760472</v>
+        <v>0.001111878984760476</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001098918879661802</v>
+        <v>0.001098918879661793</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001111827995376269</v>
+        <v>0.001111827995376267</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001097962380500512</v>
+        <v>0.001097962380500508</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001097962380500512</v>
+        <v>0.001097962380500508</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001109867688284818</v>
+        <v>0.001109867688284813</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001111878984760472</v>
+        <v>0.001111878984760474</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001098918879661802</v>
+        <v>0.001098918879661793</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001111878984760472</v>
+        <v>0.001111878984760474</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001111878984760472</v>
+        <v>0.001111878984760474</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001111878984760472</v>
+        <v>0.001111878984760474</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001541863531616023</v>
+        <v>0.001541863531616021</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002293130612426942</v>
+        <v>0.002293130612426936</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002465404620069537</v>
+        <v>0.002465404620069532</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002083991234294684</v>
+        <v>0.002083991234294676</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001552610289999279</v>
+        <v>0.001552610289999275</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002304780470878075</v>
+        <v>0.00230478047087807</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002306791767353873</v>
+        <v>0.002306791767353868</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002293831662255058</v>
+        <v>0.002293831662255052</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002306942097547134</v>
+        <v>0.002306942097547127</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001527654596932287</v>
+        <v>0.001527654596932284</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003105823271728985</v>
+        <v>0.003105823271728965</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002024029151100403</v>
+        <v>0.002024029151100399</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002477351888214172</v>
+        <v>0.002477351888214171</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002490312236641939</v>
+        <v>0.002490312236641933</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003015431980035729</v>
+        <v>0.003015431980035719</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002477351375202206</v>
+        <v>0.002477351375202197</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002488300696837188</v>
+        <v>0.002488300696837192</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002490311993312851</v>
+        <v>0.002490311993312846</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002477351888214172</v>
+        <v>0.002477351888214171</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002490311993312851</v>
+        <v>0.002490311993312846</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002220145985644993</v>
+        <v>0.00222014598564499</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002490311993312851</v>
+        <v>0.002490311993312846</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001280754772468249</v>
+        <v>0.001280754772468252</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001284215205048902</v>
+        <v>0.001284215205048904</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001136965486193981</v>
+        <v>0.001136965486193983</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001284215205048902</v>
+        <v>0.001284215205048904</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001284215205048902</v>
+        <v>0.001284215205048904</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001135109567325026</v>
+        <v>0.001135109567325024</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008287631832858275</v>
+        <v>0.0008287631832858285</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001284215205048902</v>
+        <v>0.001284215205048904</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001282203863383896</v>
+        <v>0.001282203863383899</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001394507936832932</v>
+        <v>0.001394507936832936</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0001951469077670678</v>
+        <v>-0.0001951469077670648</v>
       </c>
     </row>
     <row r="9">
@@ -5943,13 +5943,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00143875403231714</v>
+        <v>0.001438754032317146</v>
       </c>
       <c r="C9" t="n">
         <v>0.001401250989640148</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001380202108951577</v>
+        <v>0.001380202108951578</v>
       </c>
       <c r="E9" t="n">
         <v>0.001401250989640148</v>
@@ -5961,7 +5961,7 @@
         <v>0.001378162896295558</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001255387537374583</v>
+        <v>0.001255387537374584</v>
       </c>
       <c r="I9" t="n">
         <v>0.001401250989640148</v>
@@ -5970,10 +5970,10 @@
         <v>0.001439469083743281</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001485096345891325</v>
+        <v>0.001485096345891326</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0008389956086939737</v>
+        <v>0.0008389956086939767</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005187343549293018</v>
+        <v>0.005187343549293016</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004613266222669473</v>
+        <v>0.00461326622266947</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008244263837527027</v>
+        <v>0.008244263837527018</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004613266222669473</v>
+        <v>0.00461326622266947</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004613266222669473</v>
+        <v>0.00461326622266947</v>
       </c>
       <c r="G2" t="n">
         <v>0.01004143795973281</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02074308381249165</v>
+        <v>0.02074308381249164</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004613266222669473</v>
+        <v>0.00461326622266947</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01874531108629703</v>
+        <v>0.01874531108629699</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007835289037225466</v>
+        <v>0.007835289037225452</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01365178709665886</v>
+        <v>0.02647942371375321</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005722000571758514</v>
+        <v>0.0005722000571758481</v>
       </c>
       <c r="C3" t="n">
         <v>0.0004978319400739517</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005722000571758514</v>
+        <v>0.0005722000571758481</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005143444761470459</v>
+        <v>0.0005143444761470454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005143444761470459</v>
+        <v>0.0005143444761470455</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005703043776126313</v>
+        <v>0.0005703043776126295</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005722000571758514</v>
+        <v>0.0005722000571758481</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005599719444067825</v>
+        <v>0.0005599719444067819</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005722000571758514</v>
+        <v>0.0005722000571758481</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005722000571758514</v>
+        <v>0.0005722000571758481</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005722000571758514</v>
+        <v>0.0005722000571758481</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001364592830447972</v>
+        <v>0.001364592830447969</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001330739001071046</v>
+        <v>0.001330739001071051</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001365992005563863</v>
+        <v>0.002050786577302691</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001248575374899556</v>
+        <v>0.001248575374899554</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001348029040985012</v>
+        <v>0.001348029040985011</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002033019196114642</v>
+        <v>0.001362697150884751</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002079522789774919</v>
+        <v>0.002079522789774915</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002022686762908794</v>
+        <v>0.001352364717678904</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002050234509639451</v>
+        <v>0.002050234509639447</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001357525242374158</v>
+        <v>0.001357525242374157</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00136944915356351</v>
+        <v>0.001369449153563509</v>
       </c>
     </row>
     <row r="5">
@@ -6179,13 +6179,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001062070771351093</v>
+        <v>0.001062070771351092</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001049842658582024</v>
+        <v>0.001049842658582026</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00106201737574019</v>
+        <v>0.001062017375740189</v>
       </c>
       <c r="E5" t="n">
         <v>0.001049059397443736</v>
@@ -6194,22 +6194,22 @@
         <v>0.001049059397443736</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001060175091787874</v>
+        <v>0.001060175091787872</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001062070771351093</v>
+        <v>0.001062070771351092</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001049842658582024</v>
+        <v>0.001049842658582026</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001062070771351093</v>
+        <v>0.001062070771351092</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001062070771351093</v>
+        <v>0.001062070771351092</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001062070771351093</v>
+        <v>0.001062070771351092</v>
       </c>
     </row>
     <row r="6">
@@ -6219,28 +6219,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001483839799684128</v>
+        <v>0.001483839799684129</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002221862889409014</v>
+        <v>0.002221862889404725</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002390306630215983</v>
+        <v>0.002390306630215984</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002016572959973723</v>
+        <v>0.002016572959973727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001494975055810888</v>
+        <v>0.001494975055810889</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002232730503208082</v>
+        <v>0.002232730503208086</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002234626182771297</v>
+        <v>0.002234626182771299</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002222398070002232</v>
+        <v>0.002222398070002237</v>
       </c>
       <c r="J6" t="n">
         <v>0.002234773733707457</v>
@@ -6249,7 +6249,7 @@
         <v>0.001469893557171096</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003018885339551049</v>
+        <v>0.003018885339551051</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002082437475195536</v>
+        <v>0.002082437475195533</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00256253680927717</v>
+        <v>0.002562536809277168</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002574765145254505</v>
+        <v>0.002574765145254503</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003130672044569733</v>
+        <v>0.003130672044569731</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002562536488378782</v>
+        <v>0.002562536488378779</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002572869242483015</v>
+        <v>0.002572869242483014</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002574764922046234</v>
+        <v>0.002574764922046233</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00256253680927717</v>
+        <v>0.002562536809277168</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002574764922046234</v>
+        <v>0.002574764922046233</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001954836728472986</v>
+        <v>0.00228950855970322</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002574764922046234</v>
+        <v>0.002574764922046233</v>
       </c>
     </row>
     <row r="8">
@@ -6299,13 +6299,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001513439493713036</v>
+        <v>0.001513439493713035</v>
       </c>
       <c r="C8" t="n">
         <v>0.001513137872892453</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001431868938006563</v>
+        <v>0.001431868938006562</v>
       </c>
       <c r="E8" t="n">
         <v>0.001513137872892453</v>
@@ -6314,22 +6314,22 @@
         <v>0.001513137872892453</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001396204300876792</v>
+        <v>0.00139620430087679</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001168218181385849</v>
+        <v>0.001168218181385848</v>
       </c>
       <c r="I8" t="n">
         <v>0.001513137872892453</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00122837336627379</v>
+        <v>0.001228373366273788</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001445813242937208</v>
+        <v>0.001445813242937206</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001093554357639187</v>
+        <v>0.001349665023927526</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001540845357313183</v>
+        <v>0.001540845357313181</v>
       </c>
       <c r="C9" t="n">
         <v>0.001532372981895805</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001507627254290511</v>
+        <v>0.001507627254290509</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001532372981895805</v>
+        <v>0.001532372981895806</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001532372981895805</v>
+        <v>0.001532372981895806</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001492113967548896</v>
+        <v>0.001492113967548895</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001400662047798473</v>
+        <v>0.001400662047798471</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001532372981895805</v>
+        <v>0.001532372981895806</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001424890186760559</v>
+        <v>0.001424890186760558</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001513310975799711</v>
+        <v>0.001513310975799708</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001474344864348998</v>
+        <v>0.001370229632777951</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004137940365520054</v>
+        <v>0.004137940365520055</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005773187988744862</v>
+        <v>0.005773187988744858</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00484812098836436</v>
+        <v>0.004848120988364361</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005773187988744862</v>
+        <v>0.005773187988744858</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005773187988744862</v>
+        <v>0.005773187988744858</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00649926264886884</v>
+        <v>0.006499262648868785</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003634294347394234</v>
+        <v>0.003634294347394237</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005773187988744862</v>
+        <v>0.005773187988744858</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01190527455733316</v>
+        <v>0.01190527455733314</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007124720356414611</v>
+        <v>0.00712472035641462</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00449534063966638</v>
+        <v>0.004495340639666378</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005522906108056914</v>
+        <v>0.0005522906108056931</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004981557323654771</v>
+        <v>0.0004981557323654759</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005522906108056914</v>
+        <v>0.0005522906108056931</v>
       </c>
       <c r="E3" t="n">
+        <v>0.0005123977484262898</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.0005123977484262905</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.0005123977484262904</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.0005506546682999257</v>
+        <v>0.0005506546682999236</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005522906108056914</v>
+        <v>0.0005522906108056931</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005417339262405151</v>
+        <v>0.0005417339262405141</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005522906108056914</v>
+        <v>0.0005522906108056931</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005522906108056914</v>
+        <v>0.0005522906108056931</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005522906108056914</v>
+        <v>0.0005522906108056931</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001308266083183476</v>
+        <v>0.001915435718661178</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001286204418358139</v>
+        <v>0.001286204418358135</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001306471111450372</v>
+        <v>0.001306467275372616</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001207548733553994</v>
+        <v>0.001207548733553992</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00129538742399558</v>
+        <v>0.001295387423995579</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001306630140677708</v>
+        <v>0.001306630140677709</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001945161264417996</v>
+        <v>0.00130385188394693</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0012977093986183</v>
+        <v>0.001297709398618297</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00136303613106558</v>
+        <v>0.001924302952744844</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0013100902837374</v>
+        <v>0.001310090283737403</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00130271814394257</v>
+        <v>0.001302718143942569</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009954001546044434</v>
+        <v>0.0009954001546044425</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009848434700392671</v>
+        <v>0.0009848434700392647</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009953498940284593</v>
+        <v>0.0009953498940284574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009841642444921334</v>
+        <v>0.0009841642444921323</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009841642444921334</v>
+        <v>0.0009841642444921323</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009937642120986761</v>
+        <v>0.0009937642120986766</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009954001546044434</v>
+        <v>0.0009954001546044425</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009848434700392671</v>
+        <v>0.0009848434700392647</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009954001546044434</v>
+        <v>0.0009954001546044425</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009954001546044434</v>
+        <v>0.0009954001546044425</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009954001546044434</v>
+        <v>0.0009954001546044425</v>
       </c>
     </row>
     <row r="6">
@@ -6618,34 +6618,34 @@
         <v>0.001371803917156486</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002038025480667432</v>
+        <v>0.00203802548066743</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002189465164513017</v>
+        <v>0.002189465164513012</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001852844361544812</v>
+        <v>0.001852844361544809</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001382339253678539</v>
+        <v>0.001382339253678536</v>
       </c>
       <c r="G6" t="n">
         <v>0.002047400621026658</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002049036563532329</v>
+        <v>0.002049036563532326</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00203847987896725</v>
+        <v>0.002038479878967248</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002049169659067681</v>
+        <v>0.002049169659067676</v>
       </c>
       <c r="K6" t="n">
         <v>0.001359223973064448</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002756462691867826</v>
+        <v>0.002756462691867821</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001792506092288</v>
+        <v>0.001792506092287997</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002193064312712238</v>
+        <v>0.002193064312712235</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002203621333037967</v>
+        <v>0.00220362133303796</v>
       </c>
       <c r="E7" t="n">
         <v>0.002667482441496256</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002193064266270347</v>
+        <v>0.002193064266270343</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002201985054771642</v>
+        <v>0.00220198505477164</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002203620997277417</v>
+        <v>0.002203620997277403</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002193064312712238</v>
+        <v>0.002193064312712235</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002203620997277417</v>
+        <v>0.002203620997277403</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001955755400659415</v>
+        <v>0.001955755400659414</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002203620997277417</v>
+        <v>0.002203620997277403</v>
       </c>
     </row>
     <row r="8">
@@ -6695,19 +6695,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001523912854065531</v>
+        <v>0.00152391285406553</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001463890166263027</v>
+        <v>0.001463890166263026</v>
       </c>
       <c r="D8" t="n">
         <v>0.001499216746221307</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001463890166263027</v>
+        <v>0.001463890166263026</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001463890166263027</v>
+        <v>0.001463890166263026</v>
       </c>
       <c r="G8" t="n">
         <v>0.00145900414969745</v>
@@ -6716,10 +6716,10 @@
         <v>0.001542706346285023</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001463890166263027</v>
+        <v>0.001463890166263026</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001334331740674527</v>
+        <v>0.001334331740674526</v>
       </c>
       <c r="K8" t="n">
         <v>0.001439894061939715</v>
@@ -6735,28 +6735,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001540033372985448</v>
+        <v>0.001540033372985447</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001507795013172968</v>
+        <v>0.001507795013172967</v>
       </c>
       <c r="D9" t="n">
         <v>0.001529977851634079</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001507795013172968</v>
+        <v>0.001507795013172967</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001507795013172968</v>
+        <v>0.001507795013172967</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001513114826996812</v>
+        <v>0.00151311482699681</v>
       </c>
       <c r="H9" t="n">
         <v>0.001547754175863181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001507795013172968</v>
+        <v>0.001507795013172967</v>
       </c>
       <c r="J9" t="n">
         <v>0.001462924874252138</v>
@@ -6765,7 +6765,7 @@
         <v>0.001505822263396852</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001539737746858925</v>
+        <v>0.001562074185296685</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006089136773616887</v>
+        <v>0.006089136773616875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006431420581325998</v>
+        <v>0.006431420581326004</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003681293075724243</v>
+        <v>0.003681293075724242</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006431420581325998</v>
+        <v>0.006431420581326004</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006431420581325998</v>
+        <v>0.006431420581326004</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005978763456169675</v>
+        <v>0.005978763456169719</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003376897052341077</v>
+        <v>0.003376897052341084</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006431420581325998</v>
+        <v>0.006431420581326004</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009846959041133495</v>
+        <v>0.009846959041133477</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006140278825134369</v>
+        <v>0.006140278825134382</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005266655142565808</v>
+        <v>0.00326050217858182</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005545254802766265</v>
+        <v>0.0005545254802766197</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005071065976565238</v>
+        <v>0.0005071065976565254</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005545254802766265</v>
+        <v>0.0005545254802766196</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000520920388044452</v>
+        <v>0.000520920388044454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005209203880444521</v>
+        <v>0.0005209203880444526</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005528755562728684</v>
+        <v>0.0005528755562728778</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005545254802766265</v>
+        <v>0.0005545254802766197</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005438624263190377</v>
+        <v>0.0005438624263190398</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005545254802766265</v>
+        <v>0.0005545254802766197</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005545254802766265</v>
+        <v>0.0005545254802766197</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005545254802766265</v>
+        <v>0.0005545254802766197</v>
       </c>
     </row>
     <row r="4">
@@ -6931,34 +6931,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001316505395472523</v>
+        <v>0.001316505395472496</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001296786578075666</v>
+        <v>0.001296786578075675</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00193160583688837</v>
+        <v>0.001308281970240848</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001217453381181574</v>
+        <v>0.001217453381181571</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001303811452644095</v>
+        <v>0.001303811452644099</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001314855471468749</v>
+        <v>0.00192757601268022</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001954017510938195</v>
+        <v>0.001954017510938202</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001305842341514919</v>
+        <v>0.001305842341514925</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001370266468530429</v>
+        <v>0.001933558696947637</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001318547657693283</v>
+        <v>0.001318547657693267</v>
       </c>
       <c r="L4" t="n">
         <v>0.001314454838232773</v>
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009958343561052687</v>
+        <v>0.0009958343561052886</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009851713021477057</v>
+        <v>0.0009851713021477079</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009957838582419921</v>
+        <v>0.0009957838582419949</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009844818862824521</v>
+        <v>0.0009844818862824536</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009844818862824521</v>
+        <v>0.0009844818862824536</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009941844321015552</v>
+        <v>0.0009941844321015483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009958343561052687</v>
+        <v>0.0009958343561052886</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009851713021477057</v>
+        <v>0.0009851713021477079</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009958343561052687</v>
+        <v>0.0009958343561052886</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009958343561052687</v>
+        <v>0.0009958343561052886</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009958343561052687</v>
+        <v>0.0009958343561052886</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001369151725952337</v>
+        <v>0.001369151725952326</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002031871808736217</v>
+        <v>0.002031871808739754</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002182725562383611</v>
+        <v>0.002182725562383606</v>
       </c>
       <c r="E6" t="n">
         <v>0.001847617158453842</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001379467442973386</v>
+        <v>0.001379467442973387</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002041349026639396</v>
+        <v>0.002041349026639383</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002042998950643001</v>
+        <v>0.002042998950643005</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002032335896685537</v>
+        <v>0.002032335896685543</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002043131380850432</v>
+        <v>0.002043131380850402</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001356634667805788</v>
+        <v>0.00135663466780577</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002746888722948155</v>
+        <v>0.002746888722948149</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001683065014342443</v>
+        <v>0.001683065014342446</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00205251036825252</v>
+        <v>0.002052510368252527</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002063173729495787</v>
+        <v>0.00206317372949579</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002491147638687198</v>
+        <v>0.002491147638687204</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00205251032791134</v>
+        <v>0.002052510327911346</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002061523498206354</v>
+        <v>0.002061523498206362</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002063173422210107</v>
+        <v>0.002063173422210104</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00205251036825252</v>
+        <v>0.002052510368252527</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002063173422210107</v>
+        <v>0.002063173422210104</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001842937247134598</v>
+        <v>0.001834001974844172</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002063173422210107</v>
+        <v>0.002063173422210104</v>
       </c>
     </row>
     <row r="8">
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001407454262855082</v>
+        <v>0.001407454262855079</v>
       </c>
       <c r="C8" t="n">
         <v>0.001334246484216006</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001468535487086771</v>
+        <v>0.001468535487086766</v>
       </c>
       <c r="E8" t="n">
         <v>0.001334246484216006</v>
@@ -7106,22 +7106,22 @@
         <v>0.001334246484216006</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001410585542019524</v>
+        <v>0.001410585542019513</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001485508092998583</v>
+        <v>0.001485508092998582</v>
       </c>
       <c r="I8" t="n">
         <v>0.001334246484216006</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001323713362514497</v>
+        <v>0.001323713362514495</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001397907533939277</v>
+        <v>0.001397907533939276</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001440198217017476</v>
+        <v>0.001440198217017473</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001454746417975062</v>
+        <v>0.001454746417975065</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001388925955862979</v>
+        <v>0.00138892595586298</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001479626531993188</v>
+        <v>0.001479626531993181</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001388925955862979</v>
+        <v>0.00138892595586298</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001388925955862979</v>
+        <v>0.00138892595586298</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001455684682740826</v>
+        <v>0.001455684682740824</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001486595746589795</v>
+        <v>0.001486595746589799</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001388925955862979</v>
+        <v>0.00138892595586298</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001420724983520328</v>
+        <v>0.001420724983520331</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001450866056529185</v>
+        <v>0.001450866056529176</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001468163544009312</v>
+        <v>0.001488622477601317</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01381116996556129</v>
+        <v>0.0138111699655613</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007159127332110431</v>
+        <v>0.007159127332110423</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02382311419293673</v>
+        <v>0.02382311419293674</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007159127332110431</v>
+        <v>0.007159127332110423</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007159127332110431</v>
+        <v>0.007159127332110423</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02277166339412121</v>
+        <v>0.02277166339412117</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0583832579726072</v>
+        <v>0.05838325797260726</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007159127332110431</v>
+        <v>0.007159127332110423</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02234622276602951</v>
+        <v>0.02234622276602955</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01108606348175525</v>
+        <v>0.01108606348175528</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09547613542446361</v>
+        <v>0.09547613542446365</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006100827189552217</v>
+        <v>0.0006100827189552216</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005263679082691727</v>
+        <v>0.0005263679082691744</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006100827189552217</v>
+        <v>0.0006100827189552216</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005436830890058628</v>
+        <v>0.0005436830890058643</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005436830890058628</v>
+        <v>0.0005436830890058642</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006078152841882663</v>
+        <v>0.0006078152841882667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006100827189552217</v>
+        <v>0.0006100827189552216</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005954848600564985</v>
+        <v>0.0005954848600565008</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006100827189552217</v>
+        <v>0.0006100827189552216</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006100827189552217</v>
+        <v>0.0006100827189552216</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006100827189552217</v>
+        <v>0.0006100827189552216</v>
       </c>
     </row>
     <row r="4">
@@ -7330,28 +7330,28 @@
         <v>0.001431030401347973</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001381201927472004</v>
+        <v>0.001381201927472006</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00144783201306392</v>
+        <v>0.001447832013063921</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001297899083021374</v>
+        <v>0.001297899083021372</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001411545636643905</v>
+        <v>0.001411545636643904</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002187308139397613</v>
+        <v>0.002187308139397614</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002244395206734259</v>
+        <v>0.00224439520673426</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00141643254244925</v>
+        <v>0.002174977715265845</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002207183296893005</v>
+        <v>0.002207183296893006</v>
       </c>
       <c r="K4" t="n">
         <v>0.001412975229415609</v>
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001153586469458369</v>
+        <v>0.00115358646945837</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001138988610559645</v>
+        <v>0.001138988610559648</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001153532553970153</v>
+        <v>0.001153532553970154</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001138114876032635</v>
+        <v>0.001138114876032638</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001138114876032635</v>
+        <v>0.001138114876032638</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001151319034691414</v>
+        <v>0.001151319034691415</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001153586469458369</v>
+        <v>0.00115358646945837</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001138988610559645</v>
+        <v>0.001138988610559648</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001153586469458369</v>
+        <v>0.00115358646945837</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001153586469458369</v>
+        <v>0.00115358646945837</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001153586469458369</v>
+        <v>0.00115358646945837</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001623439288574886</v>
+        <v>0.001623439288574887</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002434525372325221</v>
+        <v>0.002434525372329995</v>
       </c>
       <c r="D6" t="n">
         <v>0.002621066186009302</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002208593323070348</v>
+        <v>0.002208593323070352</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001634544492456735</v>
+        <v>0.00163454449245674</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002447462088340208</v>
+        <v>0.002447462088340211</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00244972952310725</v>
+        <v>0.002449729523107251</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002435131664208441</v>
+        <v>0.002435131664208446</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002449891912688175</v>
+        <v>0.002449891912688178</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001608090523260058</v>
+        <v>0.001608090523260059</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003312858766226892</v>
+        <v>0.003312858766226897</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002437538994546132</v>
+        <v>0.002437538994546133</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003007730262137939</v>
+        <v>0.003007730262137943</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003022328165099203</v>
+        <v>0.003022328165099206</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003682563440032244</v>
+        <v>0.003682563440032249</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003007729370636012</v>
+        <v>0.003007729370636021</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003020060686269702</v>
+        <v>0.003020060686269706</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003022328121036659</v>
+        <v>0.003022328121036664</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003007730262137939</v>
+        <v>0.003007730262137943</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003022328121036659</v>
+        <v>0.003022328121036664</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002669752296737812</v>
+        <v>0.002683499023037321</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003022328121036659</v>
+        <v>0.003022328121036664</v>
       </c>
     </row>
     <row r="8">
@@ -7487,28 +7487,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001356097071595938</v>
+        <v>0.001356097071595939</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001490835920311274</v>
+        <v>0.001490835920311273</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001110041920085206</v>
+        <v>0.001110041920085208</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001490835920311274</v>
+        <v>0.001490835920311273</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001490835920311274</v>
+        <v>0.001490835920311273</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001152560015653368</v>
+        <v>0.001152560015653367</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003863151390427935</v>
+        <v>0.0003863151390427934</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001490835920311274</v>
+        <v>0.001490835920311273</v>
       </c>
       <c r="J8" t="n">
         <v>0.001199130670077779</v>
@@ -7517,7 +7517,7 @@
         <v>0.001423688257160599</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001260972856033908</v>
+        <v>-0.0001984465655914456</v>
       </c>
     </row>
     <row r="9">
@@ -7533,7 +7533,7 @@
         <v>0.001545677302737656</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001404556270895076</v>
+        <v>0.001404556270895077</v>
       </c>
       <c r="E9" t="n">
         <v>0.001545677302737656</v>
@@ -7542,7 +7542,7 @@
         <v>0.001545677302737656</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001419933748497256</v>
+        <v>0.001419933748497257</v>
       </c>
       <c r="H9" t="n">
         <v>0.001110967865379841</v>
@@ -7554,10 +7554,10 @@
         <v>0.001441006598600605</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001532300622345224</v>
+        <v>0.001532300622345225</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00146632044701041</v>
+        <v>0.0008730182253874037</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002704252549387828</v>
+        <v>0.002704252549387826</v>
       </c>
       <c r="C2" t="n">
         <v>0.004982689781134014</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01939514359039632</v>
+        <v>0.01939514359039635</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004982689781134013</v>
+        <v>0.004982689781134014</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004982689781134013</v>
+        <v>0.004982689781134014</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01312770962196829</v>
+        <v>0.0131277096219683</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008132751857594876</v>
+        <v>0.008132751857594865</v>
       </c>
       <c r="I2" t="n">
         <v>0.004982689781134014</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01438860889692124</v>
+        <v>0.01438860889692123</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004895065595051515</v>
+        <v>0.004895065595051509</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05238967152271238</v>
+        <v>0.00599899084749178</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005656620241668102</v>
+        <v>0.0005656620241668095</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000503852998650308</v>
+        <v>0.0005038529986503066</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005656620241668102</v>
+        <v>0.0005656620241668095</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005186630338866162</v>
+        <v>0.0005186630338866153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005186630338866162</v>
+        <v>0.0005186630338866153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005637288655733983</v>
+        <v>0.0005637288655733967</v>
       </c>
       <c r="H3" t="n">
         <v>0.0005656620241668095</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005532112154755191</v>
+        <v>0.0005532112154755182</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005656620241668102</v>
+        <v>0.0005656620241668095</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005656620241668102</v>
+        <v>0.0005656620241668095</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005656620241668102</v>
+        <v>0.0005656620241668095</v>
       </c>
     </row>
     <row r="4">
@@ -7723,34 +7723,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001330760253546178</v>
+        <v>0.001989323548507006</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001296206547256516</v>
+        <v>0.001296206547256515</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001353893618653374</v>
+        <v>0.001353893618653311</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00121725783177749</v>
+        <v>0.001217257831777483</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001315193220616125</v>
+        <v>0.001315193220616124</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001987390389913594</v>
+        <v>0.001328827094952763</v>
       </c>
       <c r="H4" t="n">
         <v>0.002022150629776914</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001976872739815714</v>
+        <v>0.00197687273981571</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002000020825019948</v>
+        <v>0.001387803844482496</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0013203073890115</v>
+        <v>0.001320307389011501</v>
       </c>
       <c r="L4" t="n">
         <v>0.001341315717995472</v>
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001035794655949663</v>
+        <v>0.001035794655949661</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001023343847258372</v>
+        <v>0.001023343847258371</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001035744394629051</v>
+        <v>0.001035744394629046</v>
       </c>
       <c r="E5" t="n">
         <v>0.001022520257903285</v>
@@ -7778,22 +7778,22 @@
         <v>0.001022520257903285</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001033861497356252</v>
+        <v>0.00103386149735625</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001035794655949663</v>
+        <v>0.001035794655949661</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001023343847258372</v>
+        <v>0.001023343847258371</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001035794655949663</v>
+        <v>0.001035794655949661</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001035794655949663</v>
+        <v>0.001035794655949661</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001035794655949663</v>
+        <v>0.001035794655949661</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001440984676371207</v>
+        <v>0.001440984676371208</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002146657892790143</v>
+        <v>0.002146657892793979</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00230872187120191</v>
+        <v>0.002308721871201904</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001950147358981311</v>
+        <v>0.00195014735898131</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001450854484610304</v>
+        <v>0.0014508544846103</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002157759856609078</v>
+        <v>0.002157759856609077</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002159693015202413</v>
+        <v>0.002159693015202411</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002147242206511199</v>
+        <v>0.002147242206511197</v>
       </c>
       <c r="J6" t="n">
         <v>0.002159834261884068</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001427634299999787</v>
+        <v>0.001427634299999786</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002910443972434327</v>
+        <v>0.002910443972434325</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001949967684526872</v>
+        <v>0.001949967684526869</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002391098603344386</v>
+        <v>0.00239109860334438</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002403549880506739</v>
+        <v>0.00240354988050674</v>
       </c>
       <c r="E7" t="n">
         <v>0.00291452252869246</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0023910984479835</v>
+        <v>0.002391098447983494</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002401616253442258</v>
+        <v>0.002401616253442256</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002403549412035675</v>
+        <v>0.00240354941203567</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002391098603344386</v>
+        <v>0.00239109860334438</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002403549412035675</v>
+        <v>0.00240354941203567</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002140742574802055</v>
+        <v>0.00183240893163339</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002403549412035675</v>
+        <v>0.00240354941203567</v>
       </c>
     </row>
     <row r="8">
@@ -7886,34 +7886,34 @@
         <v>0.001582607819736304</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001501201825584089</v>
+        <v>0.001501201825584088</v>
       </c>
       <c r="D8" t="n">
         <v>0.001127214033082472</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001501201825584089</v>
+        <v>0.001501201825584088</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001501201825584089</v>
+        <v>0.001501201825584088</v>
       </c>
       <c r="G8" t="n">
         <v>0.001312034086737246</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001457046182615194</v>
+        <v>0.001457046182615193</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001501201825584089</v>
+        <v>0.001501201825584088</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001313951618554892</v>
+        <v>0.001313951618554891</v>
       </c>
       <c r="K8" t="n">
         <v>0.001523035439549245</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00151287838722045</v>
+        <v>0.0005130204653502505</v>
       </c>
     </row>
     <row r="9">
@@ -7929,7 +7929,7 @@
         <v>0.001531155863262761</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001391152197400021</v>
+        <v>0.00139115219740002</v>
       </c>
       <c r="E9" t="n">
         <v>0.001531155863262761</v>
@@ -7947,13 +7947,13 @@
         <v>0.001531155863262761</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00146731847515055</v>
+        <v>0.001467318475150549</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001552360207136422</v>
+        <v>0.001552360207136423</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001548308988670123</v>
+        <v>0.001141831949404544</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen eutrophication marine results.xlsx
+++ b/Results/Hydrogen/hydrogen eutrophication marine results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02888116415279566</v>
+        <v>0.02888116415279576</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01513942999642756</v>
+        <v>0.01513942999642757</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05865733979347293</v>
+        <v>0.05865733979347303</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01513942999642756</v>
+        <v>0.01513942999642757</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01513942999642756</v>
+        <v>0.01513942999642757</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03813631489947275</v>
+        <v>0.0381363148994727</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07880398026956502</v>
+        <v>0.07880398026956498</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01513942999642756</v>
+        <v>0.01513942999642757</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0360403052543799</v>
+        <v>0.03604030525438004</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01574380501930671</v>
+        <v>0.01574380501930672</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03212267781495749</v>
+        <v>0.1223964115472981</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007123338257491606</v>
+        <v>0.0007123338257491609</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006553626560496922</v>
+        <v>0.0006553626560496913</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007123338257491606</v>
+        <v>0.0007123338257491609</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000674487536591408</v>
+        <v>0.0006744875365914065</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0006744875365914066</v>
+        <v>0.0006744875365914065</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007101619255812688</v>
+        <v>0.0007101619255812748</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007123338257491606</v>
+        <v>0.0007123338257491609</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006984535555144519</v>
+        <v>0.000698453555514454</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007123338257491606</v>
+        <v>0.0007123338257491609</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007123338257491606</v>
+        <v>0.0007123338257491609</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007123338257491606</v>
+        <v>0.0007123338257491609</v>
       </c>
     </row>
     <row r="4">
@@ -595,34 +595,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001650054115013734</v>
+        <v>0.001650054115013732</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001598271453166542</v>
+        <v>0.001598271453166527</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001710300415302096</v>
+        <v>0.00171030625585864</v>
       </c>
       <c r="E4" t="n">
         <v>0.001504742499186781</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001634542951575161</v>
+        <v>0.00163454295157516</v>
       </c>
       <c r="G4" t="n">
         <v>0.002566167541848276</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002625352167206037</v>
+        <v>0.002625352167206042</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001636173844779027</v>
+        <v>0.002554459171781456</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001721755508722815</v>
+        <v>0.0025747667683272</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001624144813699047</v>
+        <v>0.001624144813699045</v>
       </c>
       <c r="L4" t="n">
         <v>0.001683281238037236</v>
@@ -638,25 +638,25 @@
         <v>0.001375314015569849</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001361433745335146</v>
+        <v>0.001361433745335143</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001375254005885969</v>
+        <v>0.001375254005885967</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001360557110117743</v>
+        <v>0.001360557110117741</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001360557110117743</v>
+        <v>0.001360557110117741</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001373142115401966</v>
+        <v>0.001373142115401964</v>
       </c>
       <c r="H5" t="n">
         <v>0.001375314015569849</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001361433745335146</v>
+        <v>0.001361433745335143</v>
       </c>
       <c r="J5" t="n">
         <v>0.001375314015569849</v>
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001948890565030777</v>
+        <v>0.00194889056503078</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002932759860549492</v>
+        <v>0.002932759860555109</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003154214865369068</v>
+        <v>0.003154214865369056</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002659774034264548</v>
+        <v>0.002659774034264544</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00196616823939116</v>
+        <v>0.001966168239391153</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002945035471852977</v>
+        <v>0.002945035471852984</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002947207372020927</v>
+        <v>0.002947207372020899</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002933327101786153</v>
+        <v>0.002933327101786162</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002947403569729818</v>
+        <v>0.002947403569729811</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001930346317815959</v>
+        <v>0.00193034631781596</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003990032754678948</v>
+        <v>0.003990032754678966</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003521769701192665</v>
+        <v>0.003521769701192667</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004377397803454514</v>
+        <v>0.004377397803454508</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004391278352882413</v>
+        <v>0.004391278352882408</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00538079094832693</v>
+        <v>0.005380790948326927</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004377396737198234</v>
+        <v>0.004377396737198235</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004389106173521334</v>
+        <v>0.00438910617352133</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004391278073689225</v>
+        <v>0.004391278073689221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004377397803454514</v>
+        <v>0.004377397803454508</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004391278073689225</v>
+        <v>0.004391278073689221</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003887481625270313</v>
+        <v>0.00329641175366071</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004391278073689225</v>
+        <v>0.004391278073689221</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001135728969600711</v>
+        <v>0.001135728969600704</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001446042362253146</v>
+        <v>0.001446042362253145</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005146423656717438</v>
+        <v>0.0005146423656717419</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001446042362253146</v>
+        <v>0.001446042362253145</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001446042362253146</v>
+        <v>0.001446042362253145</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009694298668947922</v>
+        <v>0.0009694298668947933</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0002738010818122727</v>
+        <v>0.000273801081812274</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001446042362253146</v>
+        <v>0.001446042362253145</v>
       </c>
       <c r="J8" t="n">
         <v>0.00104028573292882</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00143515220640008</v>
+        <v>0.001435152206400083</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001152487928766264</v>
+        <v>0.001152487928766263</v>
       </c>
     </row>
     <row r="9">
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001465445476710212</v>
+        <v>0.001465445476710214</v>
       </c>
       <c r="C9" t="n">
         <v>0.001593251791687278</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0012125138261843</v>
+        <v>0.001212513826184299</v>
       </c>
       <c r="E9" t="n">
         <v>0.001593251791687278</v>
@@ -810,7 +810,7 @@
         <v>0.001593251791687278</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001395410959503081</v>
+        <v>0.00139541095950308</v>
       </c>
       <c r="H9" t="n">
         <v>0.001115768847512963</v>
@@ -819,13 +819,13 @@
         <v>0.001593251791687278</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001426845604672792</v>
+        <v>0.001426845604672791</v>
       </c>
       <c r="K9" t="n">
         <v>0.001587415702755038</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001472722716379881</v>
+        <v>0.0008095142860333039</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002357454088996893</v>
+        <v>0.002357454088996897</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005796715854394399</v>
+        <v>0.005796715854394415</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004825673873168733</v>
+        <v>0.004825673873168731</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005796715854394399</v>
+        <v>0.005796715854394415</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005796715854394399</v>
+        <v>0.005796715854394415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006819852019234226</v>
+        <v>0.00681985201923422</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005053068363022807</v>
+        <v>0.005053068363022818</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005796715854394399</v>
+        <v>0.005796715854394415</v>
       </c>
       <c r="J2" t="n">
         <v>0.009411506195027184</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004556896355457294</v>
+        <v>0.004556896355457286</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00344654496494164</v>
+        <v>0.003446544964941638</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005549807825525946</v>
+        <v>0.0005549807825525941</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005061597788830196</v>
+        <v>0.0005061597788830197</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005549807825525946</v>
+        <v>0.0005549807825525941</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005200852085627869</v>
+        <v>0.0005200852085627881</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000520085208562787</v>
+        <v>0.0005200852085627877</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000553279047831826</v>
+        <v>0.0005532790478318248</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005549807825525946</v>
+        <v>0.0005549807825525941</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005439883413838689</v>
+        <v>0.00054398834138387</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005549807825525946</v>
+        <v>0.0005549807825525941</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005549807825525946</v>
+        <v>0.0005549807825525941</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005549807825525946</v>
+        <v>0.0005549807825525941</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001924077701727948</v>
+        <v>0.00131384574240943</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001293893579470991</v>
+        <v>0.001293893579471004</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001934975575615246</v>
+        <v>0.001934975575615242</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001214620874693912</v>
+        <v>0.001214620874693906</v>
       </c>
       <c r="F4" t="n">
         <v>0.001302409852743481</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001312144007688663</v>
+        <v>0.001922375967007184</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001959409209313777</v>
+        <v>0.00195940920931378</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001302853301240704</v>
+        <v>0.001302853301240705</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001936794194889608</v>
+        <v>0.001369440127342447</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001314042285451027</v>
+        <v>0.001314042285451014</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001313875967113681</v>
+        <v>0.001313875967113683</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001001775188947014</v>
+        <v>0.001001775188947017</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009907827477782891</v>
+        <v>0.0009907827477782893</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001001724689642436</v>
+        <v>0.00100172468964244</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009900888870349866</v>
+        <v>0.0009900888870349876</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009900888870349866</v>
+        <v>0.0009900888870349876</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001000073454226247</v>
+        <v>0.001000073454226248</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001001775188947014</v>
+        <v>0.001001775188947017</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009907827477782891</v>
+        <v>0.0009907827477782893</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001001775188947014</v>
+        <v>0.001001775188947017</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001001775188947014</v>
+        <v>0.001001775188947017</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001001775188947014</v>
+        <v>0.001001775188947017</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0013805546905604</v>
+        <v>0.001380554690560401</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002051170782959375</v>
+        <v>0.002051170782962955</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002204062679890799</v>
+        <v>0.002204062679890804</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001864666115389193</v>
+        <v>0.001864666115389196</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001390799185159106</v>
+        <v>0.001390799185159109</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002060928199993595</v>
+        <v>0.002060928199993602</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002062629934714335</v>
+        <v>0.002062629934714339</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002051637493545636</v>
+        <v>0.002051637493545641</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002062763981959416</v>
+        <v>0.002062763981959419</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001367884792728543</v>
+        <v>0.001367884792728547</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002775114561360664</v>
+        <v>0.00277511456136067</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001698221192128122</v>
+        <v>0.001698221192128123</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002071956389665965</v>
+        <v>0.002071956389665967</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002082949152179933</v>
+        <v>0.002082949152179934</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002515924135190005</v>
+        <v>0.002515924135190009</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002071956323672976</v>
+        <v>0.002071956323672973</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002081247096113922</v>
+        <v>0.002081247096113925</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002082948830834691</v>
+        <v>0.002082948830834693</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002071956389665965</v>
+        <v>0.002071956389665967</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002082948830834691</v>
+        <v>0.002082948830834693</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001860036261183412</v>
+        <v>0.001860036261183415</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002082948830834691</v>
+        <v>0.002082948830834693</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00150505377902605</v>
+        <v>0.001505053779026049</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001352397473257019</v>
+        <v>0.00135239747325702</v>
       </c>
       <c r="D8" t="n">
         <v>0.001439658351766643</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001352397473257019</v>
+        <v>0.00135239747325702</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001352397473257019</v>
+        <v>0.00135239747325702</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001391579940483863</v>
+        <v>0.001391579940483862</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00144877816218733</v>
+        <v>0.001448778162187328</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001352397473257019</v>
+        <v>0.00135239747325702</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001342484530835188</v>
+        <v>0.00134248453083519</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001443386705515912</v>
+        <v>0.001443386705515909</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001488746779492833</v>
+        <v>0.001488746779492829</v>
       </c>
     </row>
     <row r="9">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0014954941509558</v>
+        <v>0.001495494150955799</v>
       </c>
       <c r="C9" t="n">
         <v>0.001397368461479902</v>
@@ -1209,19 +1209,19 @@
         <v>0.001448784785749155</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001472667724144988</v>
+        <v>0.001472667724144985</v>
       </c>
       <c r="I9" t="n">
         <v>0.001397368461479902</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001429359916485231</v>
+        <v>0.00142935991648523</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001470383187831555</v>
+        <v>0.001470383187831553</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001479065193755786</v>
+        <v>0.001488898829391464</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006302078885303057</v>
+        <v>0.006302078885303048</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009594410728319796</v>
+        <v>0.009594410728319791</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01671249283341017</v>
+        <v>0.01671249283341019</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007963301996171559</v>
+        <v>0.007963301996171549</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007963301996171559</v>
+        <v>0.007963301996171549</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0149307591274212</v>
+        <v>0.01493075912742126</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03433290738343973</v>
+        <v>0.03433290738343971</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007963301996171559</v>
+        <v>0.007963301996171549</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02830406137785924</v>
+        <v>0.02830406137785921</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007467634140212324</v>
+        <v>0.007467634140212303</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02427979573568995</v>
+        <v>0.02427979573568993</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005642020218236115</v>
+        <v>0.0005642020218236118</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004853117457798577</v>
+        <v>0.0004853117457798572</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005642020218236117</v>
+        <v>0.0005642020218236116</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005339936364825223</v>
+        <v>0.0005339936364825233</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005339936364825224</v>
+        <v>0.0005339936364825233</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005620359132407758</v>
+        <v>0.0005620359132407777</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005642020218236117</v>
+        <v>0.0005642020218236118</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005501937874740909</v>
+        <v>0.0005501937874740917</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005642020218236117</v>
+        <v>0.0005642020218236118</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005642020218236117</v>
+        <v>0.0005642020218236116</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005642020218236117</v>
+        <v>0.0005642020218236116</v>
       </c>
     </row>
     <row r="4">
@@ -1387,28 +1387,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001362329657635273</v>
+        <v>0.002056374876000495</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001340654221207997</v>
+        <v>0.001340654221207999</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001372045928070306</v>
+        <v>0.001372050294837979</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001248990640132056</v>
+        <v>0.001248990640132055</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001347374040110531</v>
+        <v>0.00134737404011053</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00205420876741766</v>
+        <v>0.001360163549052437</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002110381362945668</v>
+        <v>0.002110381362945667</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002042366641650975</v>
+        <v>0.001348321423285751</v>
       </c>
       <c r="J4" t="n">
         <v>0.002065593364019784</v>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001084506150114603</v>
+        <v>0.001084506150114604</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001083439116145951</v>
+        <v>0.001083439116145952</v>
       </c>
       <c r="D5" t="n">
         <v>0.001084457028350448</v>
@@ -1442,22 +1442,22 @@
         <v>0.00107186709924634</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001082340041531767</v>
+        <v>0.001082340041531768</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001084506150114603</v>
+        <v>0.001084506150114604</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001070497915765081</v>
+        <v>0.001070497915765082</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001084506150114603</v>
+        <v>0.001084506150114604</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001084506150114603</v>
+        <v>0.001084506150114604</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001084506150114603</v>
+        <v>0.001084506150114604</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001531553942445148</v>
+        <v>0.001531553942445151</v>
       </c>
       <c r="C6" t="n">
         <v>0.002324725415103292</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002488642830457247</v>
+        <v>0.002488642830457254</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002094811637885224</v>
+        <v>0.002094811637885227</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001543519618358413</v>
+        <v>0.001543519618358416</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002322102228167564</v>
+        <v>0.002322102228167567</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002324268336751324</v>
+        <v>0.002324268336751327</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00231026010240088</v>
+        <v>0.002310260102400885</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002324424127711076</v>
+        <v>0.002324424127711081</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001516828865600368</v>
+        <v>0.001516828865600369</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003152324807186031</v>
+        <v>0.003152324807186038</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002169631037683374</v>
+        <v>0.002169631037683372</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002690058993282532</v>
+        <v>0.00269005899328253</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002691126257723182</v>
+        <v>0.002691126257723187</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003278911638995189</v>
+        <v>0.003278911638995186</v>
       </c>
       <c r="F7" t="n">
         <v>0.002677117374716063</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002688959918668345</v>
+        <v>0.002688959918668346</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002691126027251176</v>
+        <v>0.002691126027251182</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002677117792901666</v>
+        <v>0.002677117792901663</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002691126027251176</v>
+        <v>0.002691126027251182</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002388969879163186</v>
+        <v>0.002388969879163187</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002691126027251176</v>
+        <v>0.002691126027251183</v>
       </c>
     </row>
     <row r="8">
@@ -1547,19 +1547,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003082045433884202</v>
+        <v>0.003082045433884203</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009477450194473534</v>
+        <v>0.0009477450194473532</v>
       </c>
       <c r="D8" t="n">
         <v>0.001343981051833632</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001233935975189953</v>
+        <v>0.001233935975189952</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001233935975189953</v>
+        <v>0.001233935975189952</v>
       </c>
       <c r="G8" t="n">
         <v>0.001132663394450969</v>
@@ -1568,13 +1568,13 @@
         <v>0.001029349980645344</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001233935975189953</v>
+        <v>0.001233935975189952</v>
       </c>
       <c r="J8" t="n">
         <v>0.00125184798763594</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001770955691116302</v>
+        <v>0.001770955691116304</v>
       </c>
       <c r="L8" t="n">
         <v>0.00138026323349421</v>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003098473435151388</v>
+        <v>0.00309847343515139</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001038637768150878</v>
+        <v>0.001038637768150879</v>
       </c>
       <c r="D9" t="n">
         <v>0.001526889190430715</v>
@@ -1605,19 +1605,19 @@
         <v>0.001289524235522643</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001399373925416272</v>
+        <v>0.001399373925416273</v>
       </c>
       <c r="I9" t="n">
         <v>0.001300954711764521</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001572181268011264</v>
+        <v>0.001572181268011263</v>
       </c>
       <c r="K9" t="n">
         <v>0.001823495055521824</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001620728519570582</v>
+        <v>0.001620728519570583</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003277360994062617</v>
+        <v>0.003277360994062616</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006663008402527799</v>
+        <v>0.006663008402527814</v>
       </c>
       <c r="D2" t="n">
         <v>0.0115659218871192</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005036409147328611</v>
+        <v>0.005036409147328623</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005036409147328611</v>
+        <v>0.005036409147328623</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009159230727237712</v>
+        <v>0.009159230727237776</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01746641939187344</v>
+        <v>0.01746641939187345</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005036409147328611</v>
+        <v>0.005036409147328623</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01818707070270402</v>
+        <v>0.01818707070270403</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003812813518921434</v>
+        <v>0.00381281351892143</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008249532478640499</v>
+        <v>0.008249532478640506</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005390954554493518</v>
+        <v>0.0005390954554493577</v>
       </c>
       <c r="C3" t="n">
         <v>0.0004734029366716137</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005390954554493518</v>
+        <v>0.0005390954554493577</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005804080451127597</v>
+        <v>0.0005804080451127616</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005804080451127609</v>
+        <v>0.0005804080451127616</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005371670885479839</v>
+        <v>0.0005371670885479859</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005390954554493518</v>
+        <v>0.0005390954554493577</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005266128917809148</v>
+        <v>0.0005266128917809152</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005390954554493517</v>
+        <v>0.0005390954554493577</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005390954554493518</v>
+        <v>0.0005390954554493577</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005390954554493518</v>
+        <v>0.0005390954554493577</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00194321774628004</v>
+        <v>0.001943217746280046</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001285817826480011</v>
+        <v>0.001285817826479995</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001950979976802378</v>
+        <v>0.001950979976802393</v>
       </c>
       <c r="E4" t="n">
         <v>0.00120833424359802</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001294616247367691</v>
+        <v>0.001294616247367692</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001300537790807071</v>
+        <v>0.001941289379378673</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001989411158193291</v>
+        <v>0.001989411158193292</v>
       </c>
       <c r="I4" t="n">
         <v>0.001289983594040004</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001361668538451257</v>
+        <v>0.001361668538451254</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00129436919578495</v>
+        <v>0.001294369195784952</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001300151551918274</v>
+        <v>0.001300151551918278</v>
       </c>
     </row>
     <row r="5">
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001020837710383893</v>
+        <v>0.001020837710383894</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001019951454724185</v>
+        <v>0.001019951454724184</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001020791584666499</v>
+        <v>0.001020791584666491</v>
       </c>
       <c r="E5" t="n">
         <v>0.001017161175269407</v>
@@ -1838,22 +1838,22 @@
         <v>0.001017161175269407</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001018909343482523</v>
+        <v>0.00101890934348252</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001020837710383893</v>
+        <v>0.001020837710383894</v>
       </c>
       <c r="I5" t="n">
         <v>0.001008355146715451</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001020837710383893</v>
+        <v>0.001020837710383894</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001020837710383893</v>
+        <v>0.001020837710383894</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001020837710383893</v>
+        <v>0.001020837710383894</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001431999535669093</v>
+        <v>0.001431999535669102</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002175363116420028</v>
+        <v>0.002175363116414512</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002320171274693159</v>
+        <v>0.00232017127469316</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001961657250707786</v>
+        <v>0.001961657250707788</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001448116153681698</v>
+        <v>0.0014481161536817</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002165704536747719</v>
+        <v>0.002165704536747716</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002167632903650903</v>
+        <v>0.00216763290365091</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002155150339980646</v>
+        <v>0.002155150339980645</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002167777476489441</v>
+        <v>0.002167777476489446</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00141833476819958</v>
+        <v>0.001418334768199582</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002936063468991334</v>
+        <v>0.002936063468991341</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001833251615038094</v>
+        <v>0.0018332516150381</v>
       </c>
       <c r="C7" t="n">
         <v>0.002263520418292128</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002264406954877062</v>
+        <v>0.002264406954877072</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002749467910374928</v>
+        <v>0.002749467910374929</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002251923910376459</v>
+        <v>0.002251923910376462</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002262478307050463</v>
+        <v>0.002262478307050465</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00226440667395183</v>
+        <v>0.002264406673951839</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002251924110283395</v>
+        <v>0.002251924110283394</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00226440667395183</v>
+        <v>0.002264406673951839</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002014593857697482</v>
+        <v>0.002014593857697481</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00226440667395183</v>
+        <v>0.002264406673951839</v>
       </c>
     </row>
     <row r="8">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003133458442330862</v>
+        <v>0.003133458442330863</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009890241507717341</v>
+        <v>0.0009890241507717347</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001433751047898147</v>
+        <v>0.001433751047898148</v>
       </c>
       <c r="E8" t="n">
         <v>0.001292068866998126</v>
@@ -1958,22 +1958,22 @@
         <v>0.001292068866998126</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001242352177603974</v>
+        <v>0.001242352177603973</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001338982945092805</v>
+        <v>0.001338982945092807</v>
       </c>
       <c r="I8" t="n">
         <v>0.001292068866998126</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001473789359083561</v>
+        <v>0.001473789359083564</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001851718586215084</v>
+        <v>0.00185171858621509</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001460133349035869</v>
+        <v>0.001460133349035871</v>
       </c>
     </row>
     <row r="9">
@@ -1986,10 +1986,10 @@
         <v>0.003112442755886059</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001046182136740868</v>
+        <v>0.001046182136740867</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001555346579453641</v>
+        <v>0.001555346579453639</v>
       </c>
       <c r="E9" t="n">
         <v>0.001323392874236855</v>
@@ -2001,19 +2001,19 @@
         <v>0.001329510211072298</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001517081018623576</v>
+        <v>0.001517081018623581</v>
       </c>
       <c r="I9" t="n">
         <v>0.001323392874236855</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001675452190832486</v>
+        <v>0.001675452190832488</v>
       </c>
       <c r="K9" t="n">
         <v>0.001857405400065835</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0015197378432001</v>
+        <v>0.001519737843200102</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001640608874312366</v>
+        <v>0.001640608874312359</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004985534879649704</v>
+        <v>0.004985534879649683</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007500878151977627</v>
+        <v>0.0075008781519776</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002166627070394684</v>
+        <v>0.00216662707039468</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002166627070394684</v>
+        <v>0.00216662707039468</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005462935018253366</v>
+        <v>0.005462935018253449</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008785205825380586</v>
+        <v>0.00878520582538057</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002166627070394684</v>
+        <v>0.00216662707039468</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008765832536700052</v>
+        <v>0.00876583253670005</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002094120116096857</v>
+        <v>0.002094120116096848</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0033579871845637</v>
+        <v>0.003357987184563695</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00052143688682327</v>
+        <v>0.0005214368868232693</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004631199147401385</v>
+        <v>0.0004631199147401376</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00052143688682327</v>
+        <v>0.0005214368868232691</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005604762271465074</v>
+        <v>0.000560476227146507</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005604762271465074</v>
+        <v>0.0005604762271465073</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005196553938146283</v>
+        <v>0.0005196553938146276</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00052143688682327</v>
+        <v>0.0005214368868232691</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005099279131728008</v>
+        <v>0.0005099279131728018</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00052143688682327</v>
+        <v>0.0005214368868232691</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00052143688682327</v>
+        <v>0.0005214368868232691</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00052143688682327</v>
+        <v>0.0005214368868232691</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001277818392991215</v>
+        <v>0.00127781839299121</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001265452828244958</v>
+        <v>0.001265452828244961</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001280205010503246</v>
+        <v>0.001280200329223664</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001184649191405633</v>
+        <v>0.001184649191405625</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001270296954005983</v>
+        <v>0.001270296954005981</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001900174095200409</v>
+        <v>0.001900174095200408</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001942632827647639</v>
+        <v>0.001942632827647637</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001890446614558581</v>
+        <v>0.001890446614558577</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001907531825042422</v>
+        <v>0.001907531825042417</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001274521514247264</v>
+        <v>0.001274521514247139</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001273782065207892</v>
+        <v>0.001273782065207834</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009850358955308636</v>
+        <v>0.0009850358955308608</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009842629829125585</v>
+        <v>0.0009842629829125576</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009849894313116571</v>
+        <v>0.0009849894313116545</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009839702793890464</v>
+        <v>0.0009839702793890443</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009839702793890464</v>
+        <v>0.0009839702793890443</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000983254402522223</v>
+        <v>0.0009832544025222224</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009850358955308636</v>
+        <v>0.0009850358955308608</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009735269218803951</v>
+        <v>0.0009735269218803942</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009850358955308636</v>
+        <v>0.0009850358955308608</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009850358955308636</v>
+        <v>0.0009850358955308608</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009850358955308636</v>
+        <v>0.0009850358955308608</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001381622363800129</v>
+        <v>0.001381622363800126</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002102694057640708</v>
+        <v>0.002102694057646354</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002240855403228209</v>
+        <v>0.0022408554032282</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001896235853578206</v>
+        <v>0.001896235853578204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001398929750932922</v>
+        <v>0.00139892975093292</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002091505593843559</v>
+        <v>0.002091505593843557</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002093287086853995</v>
+        <v>0.002093287086853994</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002081778113201731</v>
+        <v>0.00208177811320173</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002093426949152446</v>
+        <v>0.00209342694915244</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001368402826216734</v>
+        <v>0.001368402826216729</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002836680398327907</v>
+        <v>0.0028366803983279</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001623389797811533</v>
+        <v>0.001623389797811527</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001999233220623275</v>
+        <v>0.001999233220623258</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002000006411348526</v>
+        <v>0.002000006411348513</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002423104529675014</v>
+        <v>0.002423104529675003</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001988497042110168</v>
+        <v>0.00198849704211016</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00199822464023294</v>
+        <v>0.001998224640232926</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002000006133241578</v>
+        <v>0.002000006133241573</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001988497159591113</v>
+        <v>0.001988497159591104</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002000006133241578</v>
+        <v>0.002000006133241573</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001525778869078643</v>
+        <v>0.001772940083441769</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002000006133241578</v>
+        <v>0.002000006133241573</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003158151083911238</v>
+        <v>0.003158151083911236</v>
       </c>
       <c r="C8" t="n">
         <v>0.001003053942079238</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001507862694660612</v>
+        <v>0.00150786269466061</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001260072655263581</v>
+        <v>0.00126007265526358</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001260072655263581</v>
+        <v>0.00126007265526358</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001269463582284925</v>
+        <v>0.001269463582284926</v>
       </c>
       <c r="H8" t="n">
         <v>0.00150075375687253</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001260072655263581</v>
+        <v>0.00126007265526358</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001387889472733906</v>
+        <v>0.001387889472733904</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001872693809971352</v>
+        <v>0.001872693809971349</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001528843405384198</v>
+        <v>0.001528843405384197</v>
       </c>
     </row>
     <row r="9">
@@ -2379,19 +2379,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003114526341833947</v>
+        <v>0.003114526341833949</v>
       </c>
       <c r="C9" t="n">
         <v>0.001037129903219819</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001571187723754936</v>
+        <v>0.001571187723754934</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001252014208560742</v>
+        <v>0.001252014208560741</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001252014208560742</v>
+        <v>0.001252014208560741</v>
       </c>
       <c r="G9" t="n">
         <v>0.001305784292150731</v>
@@ -2400,13 +2400,13 @@
         <v>0.001568453982102122</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001252014208560742</v>
+        <v>0.001252014208560741</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001464994887074983</v>
+        <v>0.001464994887074982</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001854078758692989</v>
+        <v>0.001854078758692988</v>
       </c>
       <c r="L9" t="n">
         <v>0.001527852803597038</v>
@@ -2498,34 +2498,34 @@
         <v>0.0022953628188493</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001806206675995396</v>
+        <v>0.001806206675995394</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009362671141319152</v>
+        <v>0.009362671141319126</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004638717644930795</v>
+        <v>0.004638717644930779</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004638717644930795</v>
+        <v>0.004638717644930779</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009790515569171007</v>
+        <v>0.009790515569171064</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0270635864109329</v>
+        <v>0.02706358641093288</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004638717644930795</v>
+        <v>0.004638717644930779</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02671771821334061</v>
+        <v>0.02671771821334062</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005305409492797756</v>
+        <v>0.005305409492797768</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02273987961328349</v>
+        <v>0.02273987961328348</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005445549919631974</v>
+        <v>0.0005445549919631986</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004592496206228296</v>
+        <v>0.0004592496206228309</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005445549919631974</v>
+        <v>0.0005445549919631986</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000557640371607105</v>
+        <v>0.0005576403716071056</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005576403716071052</v>
+        <v>0.0005576403716071056</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005425071956086765</v>
+        <v>0.0005425071956086768</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005445549919631974</v>
+        <v>0.0005445549919631986</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005312738395232916</v>
+        <v>0.0005312738395232912</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005445549919631974</v>
+        <v>0.0005445549919631986</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005445549919631974</v>
+        <v>0.0005445549919631986</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005445549919631974</v>
+        <v>0.0005445549919631986</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001325042088928075</v>
+        <v>0.001325042088928076</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001296289512232392</v>
+        <v>0.001296289512232375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001327729209839674</v>
+        <v>0.001327724679698274</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00122117658125619</v>
+        <v>0.001221176581256184</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001313782488822855</v>
+        <v>0.001313782488822854</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001322994292573554</v>
+        <v>0.001322994292573555</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002048697620225627</v>
+        <v>0.002048697620225629</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001311760936488169</v>
+        <v>0.001984252737341994</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002008106504388938</v>
+        <v>0.001386859891684128</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00131396792423929</v>
+        <v>0.001313967924239289</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001328899858824942</v>
+        <v>0.001328899858824941</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001055702661523207</v>
+        <v>0.001055702661523209</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001054683039701809</v>
+        <v>0.001054683039701811</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001055654984584607</v>
+        <v>0.00105565498458461</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001055417721390958</v>
+        <v>0.001055417721390959</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001055417721390958</v>
+        <v>0.001055417721390959</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001053654865168687</v>
+        <v>0.001053654865168688</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001055702661523207</v>
+        <v>0.001055702661523209</v>
       </c>
       <c r="I5" t="n">
         <v>0.001042421509083302</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001055702661523207</v>
+        <v>0.001055702661523209</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001055702661523207</v>
+        <v>0.001055702661523209</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001055702661523207</v>
+        <v>0.001055702661523209</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001489973541824262</v>
+        <v>0.001489973541824264</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002280506568280739</v>
+        <v>0.002280506568286197</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002430411032004238</v>
+        <v>0.002430411032004239</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002053873420881279</v>
+        <v>0.002053873420881281</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001509164351905483</v>
+        <v>0.001509164351905485</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002266848523441017</v>
+        <v>0.002266848523441021</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002268896319795131</v>
+        <v>0.002268896319795138</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00225561516735563</v>
+        <v>0.002255615167355634</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002269049400229262</v>
+        <v>0.002269049400229263</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001475504651341686</v>
+        <v>0.001475504651341688</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003082546293657097</v>
+        <v>0.003082546293657103</v>
       </c>
     </row>
     <row r="7">
@@ -2695,16 +2695,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002028786412423403</v>
+        <v>0.002028786412423401</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002515806921196448</v>
+        <v>0.002515806921196446</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002516826757123854</v>
+        <v>0.00251682675712385</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003066733155641059</v>
+        <v>0.003066733155641055</v>
       </c>
       <c r="F7" t="n">
         <v>0.002503545077721769</v>
@@ -2713,19 +2713,19 @@
         <v>0.002514778746663322</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002516826543017846</v>
+        <v>0.002516826543017848</v>
       </c>
       <c r="I7" t="n">
         <v>0.002503545390577937</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002516826543017846</v>
+        <v>0.002516826543017847</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001902296848253564</v>
+        <v>0.002234054264722911</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002516826543017846</v>
+        <v>0.002516826543017847</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003098487753687259</v>
+        <v>0.003098487753687264</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00109947185366718</v>
+        <v>0.001099471853667181</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001494520100930838</v>
+        <v>0.00149452010093084</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001308222657391522</v>
+        <v>0.001308222657391523</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001308222657391522</v>
+        <v>0.001308222657391523</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001234738446408813</v>
+        <v>0.001234738446408814</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00115824835787104</v>
+        <v>0.001158248357871042</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001308222657391522</v>
+        <v>0.001308222657391523</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001292818306763071</v>
+        <v>0.001292818306763072</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00183288617771939</v>
+        <v>0.001832886177719391</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00141174979399618</v>
+        <v>0.001411749793996181</v>
       </c>
     </row>
     <row r="9">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003063198054793014</v>
+        <v>0.003063198054793015</v>
       </c>
       <c r="C9" t="n">
         <v>0.00108727505821118</v>
@@ -2784,10 +2784,10 @@
         <v>0.001577402814152955</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001330548531964356</v>
+        <v>0.001330548531964355</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001330548531964356</v>
+        <v>0.001330548531964355</v>
       </c>
       <c r="G9" t="n">
         <v>0.001323787858349058</v>
@@ -2796,7 +2796,7 @@
         <v>0.001440940000333455</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001330548531964356</v>
+        <v>0.001330548531964355</v>
       </c>
       <c r="J9" t="n">
         <v>0.001592749398963822</v>
@@ -2805,7 +2805,7 @@
         <v>0.001856090076907895</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001634257683851954</v>
+        <v>0.001634257683851955</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001426569029939341</v>
+        <v>0.00142656902993934</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001553886617342953</v>
+        <v>0.001553886617342955</v>
       </c>
       <c r="D2" t="n">
         <v>0.002095198327437071</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003188964497113143</v>
+        <v>0.003188964497113127</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003188964497113143</v>
+        <v>0.003188964497113127</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002665098779850055</v>
+        <v>0.00266509877985002</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00340218462821194</v>
+        <v>0.003402184628211935</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003188964497113143</v>
+        <v>0.003188964497113127</v>
       </c>
       <c r="J2" t="n">
         <v>0.009219380818927991</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001829838045788946</v>
+        <v>0.001829838045788945</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004154688373875845</v>
+        <v>0.004154688373875846</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005181644144748779</v>
+        <v>0.0005181644144748775</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004505888937986666</v>
+        <v>0.0004505888937986672</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005181644144748779</v>
+        <v>0.0005181644144748775</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005886490095354308</v>
+        <v>0.0005886490095354307</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000588649009535431</v>
+        <v>0.0005886490095354307</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005164444416674763</v>
+        <v>0.0005164444416674769</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005181644144748779</v>
+        <v>0.0005181644144748775</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005069970595917427</v>
+        <v>0.0005069970595917429</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005181644144748779</v>
+        <v>0.0005181644144748775</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005181644144748779</v>
+        <v>0.0005181644144748775</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005181644144748779</v>
+        <v>0.0005181644144748775</v>
       </c>
     </row>
     <row r="4">
@@ -2971,34 +2971,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001263822983243035</v>
+        <v>0.001263822983243038</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001246730149436528</v>
+        <v>0.00124673014943652</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001261075960073505</v>
+        <v>0.001882759125521007</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001181608907829614</v>
+        <v>0.001181608907829613</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001259490853542441</v>
+        <v>0.001259490853542443</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001876062729579813</v>
+        <v>0.001262103010435637</v>
       </c>
       <c r="H4" t="n">
         <v>0.001915207208551609</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001866615347504079</v>
+        <v>0.001866615347504077</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001319211538352589</v>
+        <v>0.001882208490897408</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001261076020902328</v>
+        <v>0.001261076020902329</v>
       </c>
       <c r="L4" t="n">
         <v>0.001260730168669836</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009776283896510045</v>
+        <v>0.0009776283896510034</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009769165179371094</v>
+        <v>0.0009769165179371092</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009775831993368929</v>
+        <v>0.0009775831993368916</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009824506638299274</v>
+        <v>0.0009824506638299259</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009824506638299274</v>
+        <v>0.0009824506638299259</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009759084168436056</v>
+        <v>0.0009759084168436047</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009776283896510045</v>
+        <v>0.0009776283896510034</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009664610347678704</v>
+        <v>0.0009664610347678718</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009776283896510045</v>
+        <v>0.0009776283896510034</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009776283896510045</v>
+        <v>0.0009776283896510034</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009776283896510045</v>
+        <v>0.0009776283896510034</v>
       </c>
     </row>
     <row r="6">
@@ -3051,28 +3051,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001367951910726788</v>
+        <v>0.001367951910726787</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002087835151530399</v>
+        <v>0.00208783515152504</v>
       </c>
       <c r="D6" t="n">
         <v>0.002219283818771931</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001882891205267867</v>
+        <v>0.001882891205267865</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001388701337206239</v>
+        <v>0.001388701337206236</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002071352503314097</v>
+        <v>0.002071352503314096</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00207307247612184</v>
+        <v>0.002073072476121838</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002061905121238363</v>
+        <v>0.002061905121238362</v>
       </c>
       <c r="J6" t="n">
         <v>0.002073211052267088</v>
@@ -3081,7 +3081,7 @@
         <v>0.001354853934236645</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002809629867671072</v>
+        <v>0.002809629867671071</v>
       </c>
     </row>
     <row r="7">
@@ -3094,34 +3094,34 @@
         <v>0.001675319817560083</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002066518053629431</v>
+        <v>0.002066518053629428</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002067230206986742</v>
+        <v>0.00206723020698674</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002508318761175401</v>
+        <v>0.002508318761175399</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002056062555714606</v>
+        <v>0.002056062555714607</v>
       </c>
       <c r="G7" t="n">
         <v>0.002065509952535927</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002067229925343326</v>
+        <v>0.002067229925343324</v>
       </c>
       <c r="I7" t="n">
         <v>0.002056062570460193</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002067229925343326</v>
+        <v>0.002067229925343324</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00157374507094243</v>
+        <v>0.001840155788202851</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002067229925343326</v>
+        <v>0.002067229925343324</v>
       </c>
     </row>
     <row r="8">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003080893018728332</v>
+        <v>0.003080893018728329</v>
       </c>
       <c r="C8" t="n">
         <v>0.001086480672234789</v>
@@ -3140,10 +3140,10 @@
         <v>0.001641740777196003</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001325506947614026</v>
+        <v>0.001325506947614027</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001325506947614026</v>
+        <v>0.001325506947614027</v>
       </c>
       <c r="G8" t="n">
         <v>0.001370923561656327</v>
@@ -3152,13 +3152,13 @@
         <v>0.001618579994172915</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001325506947614026</v>
+        <v>0.001325506947614027</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001663138323152335</v>
+        <v>0.001663138323152336</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001894102076021651</v>
+        <v>0.001894102076021644</v>
       </c>
       <c r="L8" t="n">
         <v>0.001535486956669389</v>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003035642613446464</v>
+        <v>0.003035642613446465</v>
       </c>
       <c r="C9" t="n">
         <v>0.001072378385128024</v>
@@ -3186,7 +3186,7 @@
         <v>0.001330844064627701</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001367552424329598</v>
+        <v>0.001367552424329597</v>
       </c>
       <c r="H9" t="n">
         <v>0.001617618615136985</v>
@@ -3198,7 +3198,7 @@
         <v>0.001742136570759756</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001871583980137918</v>
+        <v>0.001871583980137912</v>
       </c>
       <c r="L9" t="n">
         <v>0.001544232228649839</v>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001272671048087206</v>
+        <v>0.001272671048087191</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001504489438004688</v>
+        <v>0.001504489438004689</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001865272314112856</v>
+        <v>0.001865272314112844</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002206360593530636</v>
+        <v>0.002206360593530624</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002206360593530636</v>
+        <v>0.002206360593530624</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001832854843610402</v>
+        <v>0.001832854843610416</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002271531586945525</v>
+        <v>0.00227153158694551</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002206360593530636</v>
+        <v>0.002206360593530624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003009133444787356</v>
+        <v>0.00300913344478735</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001368196355616881</v>
+        <v>0.001368196355616862</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001834435347385608</v>
+        <v>0.001834435347385606</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005082721716442728</v>
+        <v>0.0005082721716442563</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004493174276809611</v>
+        <v>0.0004493174276809618</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005082721716442728</v>
+        <v>0.0005082721716442563</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005587091239688333</v>
+        <v>0.000558709123968834</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005587091239688334</v>
+        <v>0.0005587091239688341</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005066415237221259</v>
+        <v>0.0005066415237220924</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005082721716442728</v>
+        <v>0.0005082721716442563</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004977232178698127</v>
+        <v>0.0004977232178697796</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005082721716442728</v>
+        <v>0.0005082721716442563</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005082721716442728</v>
+        <v>0.0005082721716442563</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005082721716442728</v>
+        <v>0.0005082721716442563</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001862801908050731</v>
+        <v>0.001862801908050723</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001241536308857209</v>
+        <v>0.001241536308857192</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001250822273255128</v>
+        <v>0.001250822273255117</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001170344724222024</v>
+        <v>0.001170344724222022</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001250221039470805</v>
+        <v>0.001250221039470808</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001861171260128564</v>
+        <v>0.001861171260128561</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001897439485169131</v>
+        <v>0.001252366282337394</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001245050663271731</v>
+        <v>0.001852252954276237</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001866459713731548</v>
+        <v>0.001309086968268307</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001255908043146664</v>
+        <v>0.001255908043146675</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00125118491161426</v>
+        <v>0.001251184911614245</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009540549283640297</v>
+        <v>0.0009540549283640264</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009533626686893612</v>
+        <v>0.0009533626686893623</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000954008819584655</v>
+        <v>0.0009540088195846485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009563589291755666</v>
+        <v>0.0009563589291755681</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009563589291755666</v>
+        <v>0.0009563589291755681</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009524242804418649</v>
+        <v>0.0009524242804418567</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009540549283640297</v>
+        <v>0.0009540549283640264</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009435059745895368</v>
+        <v>0.0009435059745895402</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009540549283640297</v>
+        <v>0.0009540549283640264</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009540549283640297</v>
+        <v>0.0009540549283640264</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009540549283640297</v>
+        <v>0.0009540549283640264</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001335412697381462</v>
+        <v>0.001335412697381461</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002034506511810925</v>
+        <v>0.002034506511816354</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002165238815542405</v>
+        <v>0.0021652388155424</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001835346100547014</v>
+        <v>0.001835346100547016</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00135434527205447</v>
+        <v>0.001354345272054469</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002021090320283229</v>
+        <v>0.002021090320283234</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002022720968206403</v>
+        <v>0.002022720968206401</v>
       </c>
       <c r="I6" t="n">
         <v>0.002012172014430907</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002022856043746081</v>
+        <v>0.002022856043746069</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001322645593405324</v>
+        <v>0.001322645593405316</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002740671928656714</v>
+        <v>0.002740671928656719</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001538904196167075</v>
+        <v>0.001538904196167072</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001893641651344917</v>
+        <v>0.00189364165134492</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001894334173023954</v>
+        <v>0.001894334173023959</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002293943528781812</v>
+        <v>0.002293943528781814</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00188378494130557</v>
+        <v>0.001883784941305571</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00189270326309742</v>
+        <v>0.001892703263097422</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001894333911019584</v>
+        <v>0.001894333911019575</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001883784957245096</v>
+        <v>0.001883784957245098</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001894333911019584</v>
+        <v>0.001894333911019575</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001680041503046069</v>
+        <v>0.001688396648552645</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001894333911019584</v>
+        <v>0.001894333911019575</v>
       </c>
     </row>
     <row r="8">
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003036952466198927</v>
+        <v>0.003036952466198924</v>
       </c>
       <c r="C8" t="n">
         <v>0.001067016536896037</v>
@@ -3536,25 +3536,25 @@
         <v>0.001630746323504196</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001247656417284947</v>
+        <v>0.001247656417284948</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001247656417284947</v>
+        <v>0.001247656417284948</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00133018017869625</v>
+        <v>0.001330180178696245</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00162632149950495</v>
+        <v>0.001626321499504946</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001247656417284947</v>
+        <v>0.001247656417284948</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001501146130353984</v>
+        <v>0.001501146130353985</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001879789747578682</v>
+        <v>0.001879789747578679</v>
       </c>
       <c r="L8" t="n">
         <v>0.001548719660163809</v>
@@ -3570,10 +3570,10 @@
         <v>0.002990275981461368</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001052518926433698</v>
+        <v>0.0010525189264337</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001612916698640379</v>
+        <v>0.001612916698640386</v>
       </c>
       <c r="E9" t="n">
         <v>0.001240483230483954</v>
@@ -3582,22 +3582,22 @@
         <v>0.001240483230483954</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0013160457295685</v>
+        <v>0.001316045729568494</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001611149212265464</v>
+        <v>0.001611149212265461</v>
       </c>
       <c r="I9" t="n">
         <v>0.001240483230483954</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001499589856004761</v>
+        <v>0.001499589856004763</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001851004012201261</v>
+        <v>0.001851004012201257</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001528949537701133</v>
+        <v>0.001528949537701127</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001989668864084132</v>
+        <v>0.001989668864084115</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001654214787601852</v>
+        <v>0.00165421478760185</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003352436325151239</v>
+        <v>0.003352436325151219</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004242039362627853</v>
+        <v>0.004242039362627834</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004242039362627853</v>
+        <v>0.004242039362627834</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005071000989675642</v>
+        <v>0.0050710009896756</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02264136541858738</v>
+        <v>0.02264136541858739</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004242039362627853</v>
+        <v>0.004242039362627834</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00638759337124075</v>
+        <v>0.006387593371240719</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002968793521750262</v>
+        <v>0.002968793521750268</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01851446405359099</v>
+        <v>0.01851446405359098</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005373847077772</v>
+        <v>0.0005373847077771923</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004534941410524083</v>
+        <v>0.000453494141052408</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005373847077772</v>
+        <v>0.0005373847077771923</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005608458666992838</v>
+        <v>0.0005608458666992808</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005608458666992838</v>
+        <v>0.0005608458666992808</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005354929026662447</v>
+        <v>0.0005354929026662558</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005373847077772</v>
+        <v>0.0005373847077771923</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005250921776133726</v>
+        <v>0.0005250921776133728</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005373847077772</v>
+        <v>0.0005373847077771923</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005373847077772</v>
+        <v>0.0005373847077771923</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005373847077772</v>
+        <v>0.0005373847077771923</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001301848197388178</v>
+        <v>0.001301848197388157</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001279447417361474</v>
+        <v>0.001279447417361456</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001298430576870941</v>
+        <v>0.001298430576870934</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001206879990465834</v>
+        <v>0.001206879990465831</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001292587532834755</v>
+        <v>0.00129258753283475</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001960549958824615</v>
+        <v>0.001299956392277212</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002009940283754718</v>
+        <v>0.002009940283754714</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001950149233771749</v>
+        <v>0.001289555667224336</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001970718941786618</v>
+        <v>0.001356102278114272</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001291909705385648</v>
+        <v>0.001291909705385692</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001304444433188654</v>
+        <v>0.001304444433188649</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001031947501813706</v>
+        <v>0.001031947501813707</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001031139944799113</v>
+        <v>0.001031139944799111</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001031900357765511</v>
+        <v>0.001031900357765485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001034608635975759</v>
+        <v>0.001034608635975757</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001034608635975759</v>
+        <v>0.001034608635975757</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001030055696702766</v>
+        <v>0.001030055696702746</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001031947501813706</v>
+        <v>0.001031947501813707</v>
       </c>
       <c r="I5" t="n">
         <v>0.001019654971649891</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001031947501813706</v>
+        <v>0.001031947501813707</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001031947501813706</v>
+        <v>0.001031947501813707</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001031947501813706</v>
+        <v>0.001031947501813707</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001453897005411126</v>
+        <v>0.001453897005411121</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002226259235418916</v>
+        <v>0.002226259235413475</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002369887183261073</v>
+        <v>0.002369887183261079</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002005743860452016</v>
+        <v>0.002005743860452015</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001474601984809176</v>
+        <v>0.001474601984809173</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002210679350765209</v>
+        <v>0.002210679350765188</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002212571155875335</v>
+        <v>0.002212571155875337</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00220027862571234</v>
+        <v>0.002200278625712335</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002212720256841709</v>
+        <v>0.002212720256841704</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001439804243583457</v>
+        <v>0.001439804243583451</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003005069745112931</v>
+        <v>0.003005069745112906</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001916070147012616</v>
+        <v>0.001916070147012604</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002373294427727714</v>
+        <v>0.002373294427727712</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002374102098424548</v>
+        <v>0.002374102098424531</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002890368251455802</v>
+        <v>0.002890368251455794</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002361809186748312</v>
+        <v>0.002361809186748306</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002372210179631369</v>
+        <v>0.002372210179631352</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002374101984742318</v>
+        <v>0.002374101984742315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0023618094545785</v>
+        <v>0.002361809454578491</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002374101984742318</v>
+        <v>0.002374101984742315</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002108716586947021</v>
+        <v>0.002108716586947007</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002374101984742318</v>
+        <v>0.002374101984742315</v>
       </c>
     </row>
     <row r="8">
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003077790070089602</v>
+        <v>0.0030777900700896</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001096216890038798</v>
+        <v>0.001096216890038797</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001624835413969979</v>
+        <v>0.001624835413969982</v>
       </c>
       <c r="E8" t="n">
         <v>0.001310101757923876</v>
@@ -3938,22 +3938,22 @@
         <v>0.001310101757923876</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001326920745661859</v>
+        <v>0.001326920745661852</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001239812793858536</v>
+        <v>0.001239812793858535</v>
       </c>
       <c r="I8" t="n">
         <v>0.001310101757923876</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001713481909249919</v>
+        <v>0.001713481909249921</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001873860645366799</v>
+        <v>0.001873860645366791</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001488713541348297</v>
+        <v>0.001488713541348293</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003038876846383624</v>
+        <v>0.003038876846383622</v>
       </c>
       <c r="C9" t="n">
         <v>0.001082151450179136</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001625581923063754</v>
+        <v>0.001625581923063749</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001327241422245637</v>
+        <v>0.001327241422245636</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001327241422245637</v>
+        <v>0.001327241422245636</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00135347851527783</v>
+        <v>0.001353478515277829</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001469182760198425</v>
+        <v>0.001469182760198419</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001327241422245637</v>
+        <v>0.001327241422245636</v>
       </c>
       <c r="J9" t="n">
         <v>0.001749312522311332</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001865449113661575</v>
+        <v>0.001865449113661565</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001661285216650935</v>
+        <v>0.001661285216650932</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001524705120260523</v>
+        <v>0.001524705120260518</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001612729752052666</v>
+        <v>0.00161272975205266</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002001222502615638</v>
+        <v>0.002001222502615627</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00304813673428866</v>
+        <v>0.003048136734288661</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00304813673428866</v>
+        <v>0.003048136734288661</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00208325591613363</v>
+        <v>0.002083255916133472</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002474129315241057</v>
+        <v>0.002474129315241044</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00304813673428866</v>
+        <v>0.003048136734288661</v>
       </c>
       <c r="J2" t="n">
         <v>0.003529587174409709</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001886615949083769</v>
+        <v>0.001886615949083763</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002008448644312231</v>
+        <v>0.002008448644312226</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005193774656857245</v>
+        <v>0.000519377465685724</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004504955006404731</v>
+        <v>0.0004504955006404718</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005193774656857245</v>
+        <v>0.000519377465685724</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0006020879298062655</v>
+        <v>0.0006020879298062663</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0006020879298062658</v>
+        <v>0.0006020879298062663</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005176935956037465</v>
+        <v>0.0005176935956037459</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005193774656857245</v>
+        <v>0.000519377465685724</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000508436620785939</v>
+        <v>0.0005084366207859404</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005193774656857245</v>
+        <v>0.000519377465685724</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005193774656857245</v>
+        <v>0.000519377465685724</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005193774656857245</v>
+        <v>0.000519377465685724</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001264383476066253</v>
+        <v>0.001880208060719207</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001247786846619196</v>
+        <v>0.001247786846619174</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001261768720280009</v>
+        <v>0.001261773330617103</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001184423208807079</v>
+        <v>0.001184423208807081</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00126098283047487</v>
+        <v>0.001260982830474868</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001262699605984275</v>
+        <v>0.001262699605984273</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00191650318260773</v>
+        <v>0.001916503182607728</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001869267215819427</v>
+        <v>0.001869267215819423</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001885011966615831</v>
+        <v>0.001317824356830224</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001262540932643149</v>
+        <v>0.001262540932643117</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001260524922964626</v>
+        <v>0.001260524922964624</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009775627956521622</v>
+        <v>0.0009775627956521607</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009768934444054119</v>
+        <v>0.0009768934444054096</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009775180187146645</v>
+        <v>0.0009775180187146621</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009859697406751898</v>
+        <v>0.0009859697406751887</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009859697406751898</v>
+        <v>0.0009859697406751887</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009758789255701832</v>
+        <v>0.0009758789255701809</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009775627956521622</v>
+        <v>0.0009775627956521607</v>
       </c>
       <c r="I5" t="n">
         <v>0.0009666219507523763</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009775627956521622</v>
+        <v>0.0009775627956521607</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009775627956521622</v>
+        <v>0.0009775627956521607</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009775627956521622</v>
+        <v>0.0009775627956521607</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001365441873708452</v>
+        <v>0.001365441873708449</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002087154423555939</v>
+        <v>0.002087154423555933</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002215057160891419</v>
+        <v>0.00221505716089141</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001882444596188155</v>
+        <v>0.001882444596188152</v>
       </c>
       <c r="F6" t="n">
         <v>0.001388375800649547</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002067456767888936</v>
+        <v>0.002067456767888934</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00206914063797083</v>
+        <v>0.002069140637970823</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002058199793071132</v>
+        <v>0.002058199793071128</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002069278934654602</v>
+        <v>0.002069278934654595</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001352370307908136</v>
+        <v>0.001352370307908132</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002804212839312533</v>
+        <v>0.002804212839312529</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001667082721721348</v>
+        <v>0.001667082721721333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002056120791058423</v>
+        <v>0.002056120791058413</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002056790419952004</v>
+        <v>0.002056790419951991</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002495563648454873</v>
+        <v>0.002495563648454864</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002045849297276379</v>
+        <v>0.002045849297276373</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002055106272223195</v>
+        <v>0.002055106272223189</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002056790142305176</v>
+        <v>0.002056790142305165</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002045849297405387</v>
+        <v>0.002045849297405379</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002056790142305176</v>
+        <v>0.002056790142305165</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001830992249097713</v>
+        <v>0.001566078865302441</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002056790142305176</v>
+        <v>0.002056790142305165</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002877167970514395</v>
+        <v>0.002877167970514394</v>
       </c>
       <c r="C8" t="n">
         <v>0.001086239210944976</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001644853070997258</v>
+        <v>0.001644853070997256</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00133249032117412</v>
+        <v>0.001332490321174119</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00133249032117412</v>
+        <v>0.001332490321174119</v>
       </c>
       <c r="G8" t="n">
         <v>0.001368724561286139</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001639370777626114</v>
+        <v>0.001639370777626112</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00133249032117412</v>
+        <v>0.001332490321174119</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001795644537564724</v>
+        <v>0.001795644537564722</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001897914903203679</v>
+        <v>0.001897914903203674</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001584229226403066</v>
+        <v>0.001584229226403065</v>
       </c>
     </row>
     <row r="9">
@@ -4359,34 +4359,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002836482880130318</v>
+        <v>0.002836482880130319</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001072986192907626</v>
+        <v>0.001072986192907625</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001628782595445028</v>
+        <v>0.001628782595445027</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001335804888985648</v>
+        <v>0.001335804888985647</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001335804888985648</v>
+        <v>0.001335804888985647</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001357481354333612</v>
+        <v>0.001357481354333611</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001626588260805464</v>
+        <v>0.001626588260805463</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001335804888985648</v>
+        <v>0.001335804888985647</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001796509219904832</v>
+        <v>0.001796509219904829</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00187618066855714</v>
+        <v>0.001876180668557137</v>
       </c>
       <c r="L9" t="n">
         <v>0.001566099653557854</v>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001351985440433205</v>
+        <v>0.001351985440433208</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001519534855004756</v>
+        <v>0.001519534855004753</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001808870791622343</v>
+        <v>0.001808870791622344</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00218072112915854</v>
+        <v>0.002180721129158538</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00218072112915854</v>
+        <v>0.002180721129158538</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00180338449131921</v>
+        <v>0.001803384491319209</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002209535247163107</v>
+        <v>0.002209535247163102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00218072112915854</v>
+        <v>0.002180721129158538</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002973785529703103</v>
+        <v>0.0029737855297031</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001645433020863331</v>
+        <v>0.00164543302086334</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001838216147354704</v>
+        <v>0.00183821614735471</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005093152630714533</v>
+        <v>0.0005093152630714564</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004490719210745898</v>
+        <v>0.0004490719210745894</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005093152630714533</v>
+        <v>0.0005093152630714564</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005667003786756893</v>
+        <v>0.0005667003786756877</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005667003786756894</v>
+        <v>0.0005667003786756879</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005077261408004368</v>
+        <v>0.0005077261408004383</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005093152630714533</v>
+        <v>0.0005093152630714564</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004990403614343907</v>
+        <v>0.0004990403614343898</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005093152630714533</v>
+        <v>0.0005093152630714564</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005093152630714533</v>
+        <v>0.0005093152630714564</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005093152630714533</v>
+        <v>0.0005093152630714564</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001258728954064153</v>
+        <v>0.001867723057667465</v>
       </c>
       <c r="C4" t="n">
         <v>0.001244382705987862</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001253626662681105</v>
+        <v>0.001253621894354371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001174360187256442</v>
+        <v>0.001174360187256443</v>
       </c>
       <c r="F4" t="n">
         <v>0.001254014078265516</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001866133935396439</v>
+        <v>0.001257139831793137</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00190211456660244</v>
+        <v>0.001902114566602445</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001857448156030393</v>
+        <v>0.00124845405242709</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001312201455480114</v>
+        <v>0.001871951468273289</v>
       </c>
       <c r="K4" t="n">
         <v>0.001259791736337682</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001254241630889747</v>
+        <v>0.001254241630889799</v>
       </c>
     </row>
     <row r="5">
@@ -4598,25 +4598,25 @@
         <v>0.0009544484692148485</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009537643503437225</v>
+        <v>0.0009537643503437221</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009544025926442644</v>
+        <v>0.0009544025926442755</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009590070891020927</v>
+        <v>0.0009590070891020929</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009590070891020927</v>
+        <v>0.0009590070891020929</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009528593469438305</v>
+        <v>0.0009528593469438361</v>
       </c>
       <c r="H5" t="n">
         <v>0.0009544484692148485</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009441735675777851</v>
+        <v>0.000944173567577784</v>
       </c>
       <c r="J5" t="n">
         <v>0.0009544484692148485</v>
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001333824096188587</v>
+        <v>0.001333824096188589</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002033881792294888</v>
+        <v>0.002033881792289423</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002162518808837324</v>
+        <v>0.002162518808837323</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001835043321118605</v>
+        <v>0.001835043321118599</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001354182384398521</v>
+        <v>0.001354182384398518</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002018606151598931</v>
+        <v>0.002018606151598935</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002020195273870783</v>
+        <v>0.002020195273870785</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002009920372232886</v>
+        <v>0.002009920372232884</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002020330165219216</v>
+        <v>0.002020330165219213</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001321074399201317</v>
+        <v>0.001321074399201315</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002737167362150779</v>
+        <v>0.002737167362150783</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001539017766680617</v>
+        <v>0.001539017766680618</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001893826232856292</v>
+        <v>0.00189382623285629</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001894510614637813</v>
+        <v>0.001894510614637809</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002294466578953347</v>
+        <v>0.002294466578953343</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001884235438659701</v>
+        <v>0.001884235438659702</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001892921229456402</v>
+        <v>0.001892921229456401</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001894510351727416</v>
+        <v>0.001894510351727421</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001884235450090353</v>
+        <v>0.001884235450090352</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001894510351727416</v>
+        <v>0.001894510351727421</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001680180038977151</v>
+        <v>0.001680180038977159</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001894510351727416</v>
+        <v>0.001894510351727421</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002312326340404216</v>
+        <v>0.002312326340404222</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001066783208211798</v>
+        <v>0.001066783208211797</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001632999919350118</v>
+        <v>0.00163299991935012</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001250912609171556</v>
+        <v>0.001250912609171555</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001250912609171556</v>
+        <v>0.001250912609171555</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001268965901388588</v>
+        <v>0.001268965901388587</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001628533588330895</v>
+        <v>0.0016285335883309</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001250912609171556</v>
+        <v>0.001250912609171555</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001504953008585481</v>
+        <v>0.001504953008585484</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001876008976098446</v>
+        <v>0.00187600897609845</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001551025225737429</v>
+        <v>0.001551025225737428</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002278103948046878</v>
+        <v>0.002278103948046881</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00105251980892234</v>
+        <v>0.001052519808922341</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001614371235727451</v>
+        <v>0.001614371235727453</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001243358357991043</v>
+        <v>0.001243358357991042</v>
       </c>
       <c r="F9" t="n">
         <v>0.001243358357991042</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001255416531175252</v>
+        <v>0.001255416531175253</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001612585640464655</v>
+        <v>0.001612585640464657</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001243358357991043</v>
+        <v>0.001243358357991042</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001502894542290623</v>
+        <v>0.001502894542290626</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001851200128831289</v>
+        <v>0.001851200128831301</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001531295052836573</v>
+        <v>0.001531295052836577</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02149815209962279</v>
+        <v>0.02149815209962302</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008282537020936096</v>
+        <v>0.008282537020936077</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02589074065730744</v>
+        <v>0.02589074065730742</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008282537020936096</v>
+        <v>0.008282537020936077</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008282537020936096</v>
+        <v>0.008282537020936077</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02657078687345922</v>
+        <v>0.02657078687345928</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06494450836581532</v>
+        <v>0.06494450836581515</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008282537020936096</v>
+        <v>0.008282537020936077</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0330672957285703</v>
+        <v>0.03306729572857029</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0116789289775055</v>
+        <v>0.01167892897750555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02826199552498329</v>
+        <v>0.02826199552498331</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006232923342840839</v>
+        <v>0.0006232923342840853</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005379345641720632</v>
+        <v>0.0005379345641720642</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006232923342840839</v>
+        <v>0.0006232923342840853</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005554365248662344</v>
+        <v>0.0005554365248662359</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005554365248662343</v>
+        <v>0.0005554365248662358</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006209520726537874</v>
+        <v>0.0006209520726537881</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006232923342840839</v>
+        <v>0.0006232923342840853</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006082314507898672</v>
+        <v>0.000608231450789868</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006232923342840839</v>
+        <v>0.0006232923342840853</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006232923342840839</v>
+        <v>0.0006232923342840853</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006232923342840839</v>
+        <v>0.0006232923342840853</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002238919726840912</v>
+        <v>0.001456060795465422</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001402900081515165</v>
+        <v>0.00140290008151517</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001470164298461911</v>
+        <v>0.00147016784701364</v>
       </c>
       <c r="E4" t="n">
         <v>0.001318767497277539</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001435864284778549</v>
+        <v>0.00143586428477855</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002236579465210613</v>
+        <v>0.001453720533835125</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002288106599076345</v>
+        <v>0.002288106599076347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002223858843346698</v>
+        <v>0.0022238588433467</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002251516488533107</v>
+        <v>0.00152178235679446</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001433841667055763</v>
+        <v>0.001433841667055761</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00148537251205726</v>
+        <v>0.001485372512057263</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001186791284202813</v>
+        <v>0.001186791284202811</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001171730400708597</v>
+        <v>0.001171730400708598</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001186737091859441</v>
+        <v>0.001186737091859443</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001170881276883855</v>
+        <v>0.001170881276883857</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001170881276883855</v>
+        <v>0.001170881276883857</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001184451022572516</v>
+        <v>0.001184451022572517</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001186791284202813</v>
+        <v>0.001186791284202811</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001171730400708597</v>
+        <v>0.001171730400708598</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001186791284202813</v>
+        <v>0.001186791284202811</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001186791284202813</v>
+        <v>0.001186791284202811</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001186791284202813</v>
+        <v>0.001186791284202811</v>
       </c>
     </row>
     <row r="6">
@@ -5034,34 +5034,34 @@
         <v>0.001672987301730448</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002510473601355271</v>
+        <v>0.002510473601360208</v>
       </c>
       <c r="D6" t="n">
         <v>0.002703012542432668</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002277199531484588</v>
+        <v>0.002277199531484589</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00168449492765953</v>
+        <v>0.001684494927659528</v>
       </c>
       <c r="G6" t="n">
         <v>0.002523771389396271</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002526111651026586</v>
+        <v>0.002526111651026588</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002511050767532352</v>
+        <v>0.002511050767532351</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002526279314274555</v>
+        <v>0.002526279314274554</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001657140078957757</v>
+        <v>0.001657140078957756</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003417271370844163</v>
+        <v>0.003417271370844159</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002535299791519626</v>
+        <v>0.002535299791519627</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003130041101644069</v>
+        <v>0.003130041101644077</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003145102096107112</v>
+        <v>0.003145102096107118</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003833738853453656</v>
+        <v>0.003833738853453662</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003130040181606327</v>
+        <v>0.003130040181606336</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003142761723508</v>
+        <v>0.003142761723507993</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003145101985138288</v>
+        <v>0.003145101985138289</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003130041101644069</v>
+        <v>0.003130041101644077</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003145101985138288</v>
+        <v>0.003145101985138289</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002791780245951534</v>
+        <v>0.002791780245951538</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003145101985138288</v>
+        <v>0.003145101985138289</v>
       </c>
     </row>
     <row r="8">
@@ -5114,34 +5114,34 @@
         <v>0.00119387913528624</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001482715483268435</v>
+        <v>0.001482715483268434</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001104896441990715</v>
+        <v>0.001104896441990719</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001482715483268435</v>
+        <v>0.001482715483268434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001482715483268435</v>
+        <v>0.001482715483268434</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001099770999563817</v>
+        <v>0.001099770999563816</v>
       </c>
       <c r="H8" t="n">
-        <v>0.000376184484553756</v>
+        <v>0.0003761844845537594</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001482715483268435</v>
+        <v>0.001482715483268434</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009857021079889517</v>
+        <v>0.000985702107988953</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001434361312563878</v>
+        <v>0.001434361312563881</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001120639873079835</v>
+        <v>0.001120639873079838</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001449509684035802</v>
+        <v>0.0014495096840358</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001553079890622695</v>
+        <v>0.001553079890622696</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001413283109086717</v>
+        <v>0.001413283109086719</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001553079890622695</v>
+        <v>0.001553079890622696</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001553079890622695</v>
+        <v>0.001553079890622696</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001409074092874704</v>
+        <v>0.001409074092874705</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00111769040018248</v>
+        <v>0.001117690400182482</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001553079890622695</v>
+        <v>0.001553079890622696</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001364988960337997</v>
+        <v>0.001364988960338</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001547470038255197</v>
+        <v>0.001547470038255199</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001420104281490273</v>
+        <v>0.0007736674192469522</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01591916405163624</v>
+        <v>0.01591916405163625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008297120456490151</v>
+        <v>0.008297120456490139</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02315697403724725</v>
+        <v>0.02315697403724735</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008297120456490151</v>
+        <v>0.008297120456490139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008297120456490151</v>
+        <v>0.008297120456490139</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02289319673558909</v>
+        <v>0.02289319673558917</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05064779858968826</v>
+        <v>0.05064779858968816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008297120456490151</v>
+        <v>0.008297120456490139</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02283627544235484</v>
+        <v>0.02283627544235487</v>
       </c>
       <c r="K2" t="n">
         <v>0.01014298175341151</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03025152024391803</v>
+        <v>0.03025152024391805</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006019098873092899</v>
+        <v>0.0006019098873092898</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005341727468398131</v>
+        <v>0.0005341727468398136</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006019098873092901</v>
+        <v>0.0006019098873092892</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005496664394554845</v>
+        <v>0.0005496664394554847</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005496664394554845</v>
+        <v>0.0005496664394554848</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005997429630406894</v>
+        <v>0.0005997429630406915</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006019098873092901</v>
+        <v>0.0006019098873092892</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005879705766757376</v>
+        <v>0.0005879705766757378</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006019098873092901</v>
+        <v>0.0006019098873092892</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006019098873092901</v>
+        <v>0.0006019098873092892</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006019098873092901</v>
+        <v>0.0006019098873092892</v>
       </c>
     </row>
     <row r="4">
@@ -5347,34 +5347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002119157315284515</v>
+        <v>0.001394866545979313</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001350302509308054</v>
+        <v>0.001350302509308048</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00140863845318283</v>
+        <v>0.001408638453182823</v>
       </c>
       <c r="E4" t="n">
         <v>0.001269990119080488</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001377227204699871</v>
+        <v>0.001377227204699872</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002116990391015916</v>
+        <v>0.001392699621710712</v>
       </c>
       <c r="H4" t="n">
         <v>0.002157457592732589</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002105218004650965</v>
+        <v>0.002105218004650966</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00212739887105554</v>
+        <v>0.001455807952072549</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001381160640048983</v>
+        <v>0.001381160640048985</v>
       </c>
       <c r="L4" t="n">
         <v>0.001416875773046248</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001118180129201016</v>
+        <v>0.001118180129201021</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001104240818567464</v>
+        <v>0.001104240818567465</v>
       </c>
       <c r="D5" t="n">
         <v>0.00111812944195425</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001103268199870018</v>
+        <v>0.001103268199870019</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001103268199870018</v>
+        <v>0.001103268199870019</v>
       </c>
       <c r="G5" t="n">
         <v>0.001116013204932416</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001118180129201016</v>
+        <v>0.001118180129201021</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001104240818567464</v>
+        <v>0.001104240818567465</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001118180129201016</v>
+        <v>0.001118180129201021</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001118180129201016</v>
+        <v>0.001118180129201021</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001118180129201016</v>
+        <v>0.001118180129201021</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001560978992079415</v>
+        <v>0.001560978992079419</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002327365810753719</v>
+        <v>0.002327365810753722</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002503973017718605</v>
+        <v>0.002503973017718609</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002113821805273936</v>
+        <v>0.002113821805273941</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00157124747436306</v>
+        <v>0.001571247474363063</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002339852311024249</v>
+        <v>0.002339852311024251</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00234201923529294</v>
+        <v>0.002342019235292942</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002328079924659299</v>
+        <v>0.002328079924659301</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002342172731953603</v>
+        <v>0.00234217273195361</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001546470768585225</v>
+        <v>0.001546470768585227</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003157881078736872</v>
+        <v>0.003157881078736878</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002201469283219397</v>
+        <v>0.002201469283219402</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002704611182042558</v>
+        <v>0.002704611182042564</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002718550669045789</v>
+        <v>0.002718550669045792</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003301311198702167</v>
+        <v>0.003301311198702172</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002704610466364542</v>
+        <v>0.002704610466364548</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00271638356840751</v>
+        <v>0.002716383568407513</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002718550492676113</v>
+        <v>0.002718550492676119</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002704611182042558</v>
+        <v>0.002704611182042564</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002718550492676113</v>
+        <v>0.002718550492676119</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002067452905590366</v>
+        <v>0.002418951683363484</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002718550492676113</v>
+        <v>0.002718550492676119</v>
       </c>
     </row>
     <row r="8">
@@ -5510,34 +5510,34 @@
         <v>0.00129988969010946</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001457148861458595</v>
+        <v>0.001457148861458596</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001114540895966736</v>
+        <v>0.001114540895966733</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001457148861458595</v>
+        <v>0.001457148861458596</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001457148861458595</v>
+        <v>0.001457148861458596</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00113308146612337</v>
+        <v>0.001133081466123368</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0005890388339091188</v>
+        <v>0.0005890388339091203</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001457148861458595</v>
+        <v>0.001457148861458596</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001166075341068716</v>
+        <v>0.001166075341068717</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001433682440170188</v>
+        <v>0.00143368244017019</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001022297789074908</v>
+        <v>0.001022297789074907</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001489275947873953</v>
+        <v>0.001489275947873954</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001537846976839629</v>
+        <v>0.00153784697683963</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001413799659516405</v>
+        <v>0.001413799659516404</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001537846976839629</v>
+        <v>0.00153784697683963</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001537846976839629</v>
+        <v>0.00153784697683963</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001419488956371569</v>
+        <v>0.001419488956371568</v>
       </c>
       <c r="H9" t="n">
         <v>0.001200769788240982</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001537846976839629</v>
+        <v>0.00153784697683963</v>
       </c>
       <c r="J9" t="n">
         <v>0.001434971595963346</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001543782099364579</v>
+        <v>0.001543782099364581</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001376708005178943</v>
+        <v>0.0008335364482485067</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01333721076049509</v>
+        <v>0.01333721076049514</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01038669751186683</v>
+        <v>0.01038669751186686</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01873899559904818</v>
+        <v>0.01873899559904821</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01038669751186683</v>
+        <v>0.01038669751186686</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01038669751186683</v>
+        <v>0.01038669751186686</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01938602615277376</v>
+        <v>0.01938602615277383</v>
       </c>
       <c r="H2" t="n">
         <v>0.03480583887154076</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01038669751186683</v>
+        <v>0.01038669751186686</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01468716370953077</v>
+        <v>0.01468716370953079</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008434056881918679</v>
+        <v>0.008434056881918658</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08533182328199966</v>
+        <v>0.02019859024568573</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006050029236764792</v>
+        <v>0.0006050029236764858</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005478557994428876</v>
+        <v>0.0005478557994428885</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006050029236764793</v>
+        <v>0.0006050029236764858</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005627310570238817</v>
+        <v>0.0005627310570238819</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005627310570238816</v>
+        <v>0.0005627310570238815</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000602991627200819</v>
+        <v>0.0006029916272008196</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006050029236764793</v>
+        <v>0.0006050029236764858</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005920428185777996</v>
+        <v>0.0005920428185778004</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006050029236764793</v>
+        <v>0.0006050029236764857</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006050029236764793</v>
+        <v>0.0006050029236764858</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006050029236764793</v>
+        <v>0.0006050029236764858</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001399482088615791</v>
+        <v>0.001399482088615796</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001366696958658306</v>
+        <v>0.00136669695865833</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002118848687931661</v>
+        <v>0.001405854083514814</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001285841404285681</v>
+        <v>0.001285841404285679</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001385723561380705</v>
+        <v>0.001385723561380704</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001397470792140133</v>
+        <v>0.002110198185807541</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002147954247572851</v>
+        <v>0.002147954247572856</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002099249377184514</v>
+        <v>0.001386521983517115</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001458598696835021</v>
+        <v>0.002120082505843285</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001389232761694323</v>
+        <v>0.001389232761694324</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001423330047875089</v>
+        <v>0.001423330047875091</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001111878984760476</v>
+        <v>0.001111878984760478</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001098918879661793</v>
+        <v>0.001098918879661796</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001111827995376267</v>
+        <v>0.001111827995376271</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001097962380500508</v>
+        <v>0.001097962380500509</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001097962380500508</v>
+        <v>0.001097962380500509</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001109867688284813</v>
+        <v>0.001109867688284816</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001111878984760474</v>
+        <v>0.001111878984760478</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001098918879661793</v>
+        <v>0.001098918879661796</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001111878984760474</v>
+        <v>0.001111878984760478</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001111878984760474</v>
+        <v>0.001111878984760478</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001111878984760474</v>
+        <v>0.001111878984760478</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001541863531616021</v>
+        <v>0.001541863531616025</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002293130612426936</v>
+        <v>0.002293130612426939</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002465404620069532</v>
+        <v>0.002465404620069537</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002083991234294676</v>
+        <v>0.00208399123429468</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001552610289999275</v>
+        <v>0.001552610289999278</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00230478047087807</v>
+        <v>0.002304780470878076</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002306791767353868</v>
+        <v>0.002306791767353874</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002293831662255052</v>
+        <v>0.002293831662255057</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002306942097547127</v>
+        <v>0.002306942097547134</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001527654596932284</v>
+        <v>0.001527654596932288</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003105823271728965</v>
+        <v>0.003105823271728974</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002024029151100399</v>
+        <v>0.002024029151100405</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002477351888214171</v>
+        <v>0.002477351888214174</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002490312236641933</v>
+        <v>0.002490312236641939</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003015431980035719</v>
+        <v>0.003015431980035723</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002477351375202197</v>
+        <v>0.002477351375202205</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002488300696837192</v>
+        <v>0.00248830069683719</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002490311993312846</v>
+        <v>0.002490311993312849</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002477351888214171</v>
+        <v>0.002477351888214174</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002490311993312846</v>
+        <v>0.002490311993312849</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00222014598564499</v>
+        <v>0.002220145985644992</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002490311993312846</v>
+        <v>0.002490311993312849</v>
       </c>
     </row>
     <row r="8">
@@ -5906,34 +5906,34 @@
         <v>0.001280754772468252</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001284215205048904</v>
+        <v>0.001284215205048903</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001136965486193983</v>
+        <v>0.001136965486193984</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001284215205048904</v>
+        <v>0.001284215205048903</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001284215205048904</v>
+        <v>0.001284215205048903</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001135109567325024</v>
+        <v>0.001135109567325026</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008287631832858285</v>
+        <v>0.0008287631832858293</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001284215205048904</v>
+        <v>0.001284215205048903</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001282203863383899</v>
+        <v>0.0012822038633839</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001394507936832936</v>
+        <v>0.001394507936832937</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0001951469077670648</v>
+        <v>-0.0001951469077670645</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001438754032317146</v>
+        <v>0.001438754032317147</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001401250989640148</v>
+        <v>0.001401250989640149</v>
       </c>
       <c r="D9" t="n">
         <v>0.001380202108951578</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001401250989640148</v>
+        <v>0.001401250989640149</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001401250989640148</v>
+        <v>0.001401250989640149</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001378162896295558</v>
+        <v>0.00137816289629556</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001255387537374584</v>
+        <v>0.001255387537374586</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001401250989640148</v>
+        <v>0.001401250989640149</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001439469083743281</v>
+        <v>0.001439469083743283</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001485096345891326</v>
+        <v>0.001485096345891328</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0008389956086939767</v>
+        <v>0.0008389956086939772</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005187343549293016</v>
+        <v>0.005187343549293049</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00461326622266947</v>
+        <v>0.004613266222669468</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008244263837527018</v>
+        <v>0.008244263837527022</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00461326622266947</v>
+        <v>0.004613266222669468</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00461326622266947</v>
+        <v>0.004613266222669468</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01004143795973281</v>
+        <v>0.0100414379597328</v>
       </c>
       <c r="H2" t="n">
         <v>0.02074308381249164</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00461326622266947</v>
+        <v>0.004613266222669468</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01874531108629699</v>
+        <v>0.018745311086297</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007835289037225452</v>
+        <v>0.00783528903722547</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02647942371375321</v>
+        <v>0.02647942371375323</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005722000571758481</v>
+        <v>0.0005722000571758495</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004978319400739517</v>
+        <v>0.0004978319400739504</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005722000571758481</v>
+        <v>0.0005722000571758495</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005143444761470454</v>
+        <v>0.0005143444761470439</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005143444761470455</v>
+        <v>0.000514344476147044</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005703043776126295</v>
+        <v>0.00057030437761263</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005722000571758481</v>
+        <v>0.0005722000571758495</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005599719444067819</v>
+        <v>0.000559971944406782</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005722000571758481</v>
+        <v>0.0005722000571758495</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005722000571758481</v>
+        <v>0.0005722000571758495</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005722000571758481</v>
+        <v>0.0005722000571758495</v>
       </c>
     </row>
     <row r="4">
@@ -6139,31 +6139,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001364592830447969</v>
+        <v>0.00203491487567786</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001330739001071051</v>
+        <v>0.001330739001071057</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002050786577302691</v>
+        <v>0.00205078657730269</v>
       </c>
       <c r="E4" t="n">
         <v>0.001248575374899554</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001348029040985011</v>
+        <v>0.00134802904098501</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001362697150884751</v>
+        <v>0.002033019196114641</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002079522789774915</v>
+        <v>0.001367174081077922</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001352364717678904</v>
+        <v>0.002022686762908791</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002050234509639447</v>
+        <v>0.002050234509639446</v>
       </c>
       <c r="K4" t="n">
         <v>0.001357525242374157</v>
@@ -6182,16 +6182,16 @@
         <v>0.001062070771351092</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001049842658582026</v>
+        <v>0.001049842658582023</v>
       </c>
       <c r="D5" t="n">
         <v>0.001062017375740189</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001049059397443736</v>
+        <v>0.001049059397443735</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001049059397443736</v>
+        <v>0.001049059397443735</v>
       </c>
       <c r="G5" t="n">
         <v>0.001060175091787872</v>
@@ -6200,7 +6200,7 @@
         <v>0.001062070771351092</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001049842658582026</v>
+        <v>0.001049842658582023</v>
       </c>
       <c r="J5" t="n">
         <v>0.001062070771351092</v>
@@ -6222,16 +6222,16 @@
         <v>0.001483839799684129</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002221862889404725</v>
+        <v>0.002221862889404726</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002390306630215984</v>
+        <v>0.002390306630215988</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002016572959973727</v>
+        <v>0.002016572959973728</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001494975055810889</v>
+        <v>0.001494975055810887</v>
       </c>
       <c r="G6" t="n">
         <v>0.002232730503208086</v>
@@ -6243,13 +6243,13 @@
         <v>0.002222398070002237</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002234773733707457</v>
+        <v>0.002234773733707455</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001469893557171096</v>
+        <v>0.001469893557171095</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003018885339551051</v>
+        <v>0.003018885339551053</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002082437475195533</v>
+        <v>0.002082437475195535</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002562536809277168</v>
+        <v>0.002562536809277169</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002574765145254503</v>
+        <v>0.002574765145254504</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003130672044569731</v>
+        <v>0.003130672044569732</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002562536488378779</v>
+        <v>0.00256253648837878</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002572869242483014</v>
+        <v>0.002572869242483016</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002574764922046233</v>
+        <v>0.002574764922046234</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002562536809277168</v>
+        <v>0.002562536809277169</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002574764922046233</v>
+        <v>0.002574764922046234</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00228950855970322</v>
+        <v>0.002289508559703222</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002574764922046233</v>
+        <v>0.002574764922046234</v>
       </c>
     </row>
     <row r="8">
@@ -6314,22 +6314,22 @@
         <v>0.001513137872892453</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00139620430087679</v>
+        <v>0.001396204300876791</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001168218181385848</v>
+        <v>0.001168218181385847</v>
       </c>
       <c r="I8" t="n">
         <v>0.001513137872892453</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001228373366273788</v>
+        <v>0.001228373366273789</v>
       </c>
       <c r="K8" t="n">
         <v>0.001445813242937206</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001349665023927526</v>
+        <v>0.001093554357639187</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001540845357313181</v>
+        <v>0.001540845357313182</v>
       </c>
       <c r="C9" t="n">
         <v>0.001532372981895805</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001507627254290509</v>
+        <v>0.00150762725429051</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001532372981895806</v>
+        <v>0.001532372981895805</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001532372981895806</v>
+        <v>0.001532372981895805</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001492113967548895</v>
+        <v>0.001492113967548897</v>
       </c>
       <c r="H9" t="n">
         <v>0.001400662047798471</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001532372981895806</v>
+        <v>0.001532372981895805</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001424890186760558</v>
+        <v>0.001424890186760557</v>
       </c>
       <c r="K9" t="n">
         <v>0.001513310975799708</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001370229632777951</v>
+        <v>0.00137022963277795</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004137940365520055</v>
+        <v>0.004137940365520056</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005773187988744858</v>
+        <v>0.00577318798874486</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004848120988364361</v>
+        <v>0.004848120988364359</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005773187988744858</v>
+        <v>0.00577318798874486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005773187988744858</v>
+        <v>0.00577318798874486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006499262648868785</v>
+        <v>0.00649926264886888</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003634294347394237</v>
+        <v>0.003634294347394239</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005773187988744858</v>
+        <v>0.00577318798874486</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01190527455733314</v>
+        <v>0.01190527455733317</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00712472035641462</v>
+        <v>0.007124720356414618</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004495340639666378</v>
+        <v>0.004495340639666384</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005522906108056931</v>
+        <v>0.0005522906108056919</v>
       </c>
       <c r="C3" t="n">
         <v>0.0004981557323654759</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005522906108056931</v>
+        <v>0.0005522906108056919</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005123977484262898</v>
+        <v>0.0005123977484262901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005123977484262905</v>
+        <v>0.0005123977484262909</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005506546682999236</v>
+        <v>0.0005506546682999256</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005522906108056931</v>
+        <v>0.0005522906108056919</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005417339262405141</v>
+        <v>0.0005417339262405146</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005522906108056931</v>
+        <v>0.0005522906108056919</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005522906108056931</v>
+        <v>0.0005522906108056919</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005522906108056931</v>
+        <v>0.0005522906108056919</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001915435718661178</v>
+        <v>0.001915435718661182</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001286204418358135</v>
+        <v>0.001286204418358137</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001306467275372616</v>
+        <v>0.001306471111450375</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001207548733553992</v>
+        <v>0.001207548733553994</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001295387423995579</v>
+        <v>0.001295387423995578</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001306630140677709</v>
+        <v>0.001913799776155414</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00130385188394693</v>
+        <v>0.001945161264417999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001297709398618297</v>
+        <v>0.001904879034096001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001924302952744844</v>
+        <v>0.001363036131065581</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001310090283737403</v>
+        <v>0.001310090283737402</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001302718143942569</v>
+        <v>0.001302718143942571</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009954001546044425</v>
+        <v>0.0009954001546044428</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009848434700392647</v>
+        <v>0.000984843470039266</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009953498940284574</v>
+        <v>0.0009953498940284571</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009841642444921323</v>
+        <v>0.0009841642444921319</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009841642444921323</v>
+        <v>0.0009841642444921319</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009937642120986766</v>
+        <v>0.0009937642120986764</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009954001546044425</v>
+        <v>0.0009954001546044428</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009848434700392647</v>
+        <v>0.000984843470039266</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009954001546044425</v>
+        <v>0.0009954001546044428</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009954001546044425</v>
+        <v>0.0009954001546044428</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009954001546044425</v>
+        <v>0.0009954001546044428</v>
       </c>
     </row>
     <row r="6">
@@ -6618,34 +6618,34 @@
         <v>0.001371803917156486</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00203802548066743</v>
+        <v>0.002038025480667429</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002189465164513012</v>
+        <v>0.002189465164513015</v>
       </c>
       <c r="E6" t="n">
         <v>0.001852844361544809</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001382339253678536</v>
+        <v>0.001382339253678537</v>
       </c>
       <c r="G6" t="n">
         <v>0.002047400621026658</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002049036563532326</v>
+        <v>0.002049036563532329</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002038479878967248</v>
+        <v>0.002038479878967247</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002049169659067676</v>
+        <v>0.002049169659067681</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001359223973064448</v>
+        <v>0.00135922397306445</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002756462691867821</v>
+        <v>0.002756462691867825</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001792506092287997</v>
+        <v>0.001792506092287998</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002193064312712235</v>
+        <v>0.00219306431271224</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00220362133303796</v>
+        <v>0.002203621333037974</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002667482441496256</v>
+        <v>0.00266748244149626</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002193064266270343</v>
+        <v>0.002193064266270347</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00220198505477164</v>
+        <v>0.002201985054771648</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002203620997277403</v>
+        <v>0.002203620997277412</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002193064312712235</v>
+        <v>0.00219306431271224</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002203620997277403</v>
+        <v>0.002203620997277412</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001955755400659414</v>
+        <v>0.001965419547974084</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002203620997277403</v>
+        <v>0.002203620997277412</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00152391285406553</v>
+        <v>0.001523912854065532</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001463890166263026</v>
+        <v>0.001463890166263027</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001499216746221307</v>
+        <v>0.001499216746221308</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001463890166263026</v>
+        <v>0.001463890166263027</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001463890166263026</v>
+        <v>0.001463890166263027</v>
       </c>
       <c r="G8" t="n">
         <v>0.00145900414969745</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001542706346285023</v>
+        <v>0.001542706346285024</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001463890166263026</v>
+        <v>0.001463890166263027</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001334331740674526</v>
+        <v>0.001334331740674527</v>
       </c>
       <c r="K8" t="n">
         <v>0.001439894061939715</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001577961229916218</v>
+        <v>0.001523020373382488</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001540033372985447</v>
+        <v>0.001540033372985449</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001507795013172967</v>
+        <v>0.001507795013172969</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001529977851634079</v>
+        <v>0.00152997785163408</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001507795013172967</v>
+        <v>0.001507795013172969</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001507795013172967</v>
+        <v>0.001507795013172969</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00151311482699681</v>
+        <v>0.001513114826996811</v>
       </c>
       <c r="H9" t="n">
         <v>0.001547754175863181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001507795013172967</v>
+        <v>0.001507795013172969</v>
       </c>
       <c r="J9" t="n">
         <v>0.001462924874252138</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001505822263396852</v>
+        <v>0.001505822263396853</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001562074185296685</v>
+        <v>0.001539737746858926</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006089136773616875</v>
+        <v>0.00608913677361687</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006431420581326004</v>
+        <v>0.006431420581326007</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003681293075724242</v>
+        <v>0.003681293075724239</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006431420581326004</v>
+        <v>0.006431420581326007</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006431420581326004</v>
+        <v>0.006431420581326007</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005978763456169719</v>
+        <v>0.005978763456169699</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003376897052341084</v>
+        <v>0.003376897052341075</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006431420581326004</v>
+        <v>0.006431420581326007</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009846959041133477</v>
+        <v>0.00984695904113346</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006140278825134382</v>
+        <v>0.006140278825134366</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00326050217858182</v>
+        <v>0.005266655142565789</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005545254802766197</v>
+        <v>0.0005545254802766191</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005071065976565254</v>
+        <v>0.0005071065976565242</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005545254802766196</v>
+        <v>0.0005545254802766192</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000520920388044454</v>
+        <v>0.0005209203880444529</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005209203880444526</v>
+        <v>0.000520920388044453</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005528755562728778</v>
+        <v>0.0005528755562728775</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005545254802766197</v>
+        <v>0.0005545254802766192</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005438624263190398</v>
+        <v>0.0005438624263190383</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005545254802766197</v>
+        <v>0.0005545254802766191</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005545254802766197</v>
+        <v>0.0005545254802766192</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005545254802766197</v>
+        <v>0.0005545254802766192</v>
       </c>
     </row>
     <row r="4">
@@ -6931,34 +6931,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001316505395472496</v>
+        <v>0.001316505395472502</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001296786578075675</v>
+        <v>0.001296786578075659</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001308281970240848</v>
+        <v>0.001308281970240844</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001217453381181571</v>
+        <v>0.001217453381181572</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001303811452644099</v>
+        <v>0.001303811452644097</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00192757601268022</v>
+        <v>0.00131485547146876</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001954017510938202</v>
+        <v>0.001954017510938204</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001305842341514925</v>
+        <v>0.00130584234151492</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001933558696947637</v>
+        <v>0.001370266468530422</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001318547657693267</v>
+        <v>0.001318547657693268</v>
       </c>
       <c r="L4" t="n">
         <v>0.001314454838232773</v>
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009958343561052886</v>
+        <v>0.0009958343561052895</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009851713021477079</v>
+        <v>0.0009851713021477063</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009957838582419949</v>
+        <v>0.0009957838582419954</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009844818862824536</v>
+        <v>0.0009844818862824534</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009844818862824536</v>
+        <v>0.0009844818862824534</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009941844321015483</v>
+        <v>0.0009941844321015453</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009958343561052886</v>
+        <v>0.0009958343561052895</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009851713021477079</v>
+        <v>0.0009851713021477063</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009958343561052886</v>
+        <v>0.0009958343561052895</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009958343561052886</v>
+        <v>0.0009958343561052895</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009958343561052886</v>
+        <v>0.0009958343561052895</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001369151725952326</v>
+        <v>0.001369151725952327</v>
       </c>
       <c r="C6" t="n">
         <v>0.002031871808739754</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002182725562383606</v>
+        <v>0.002182725562383603</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001847617158453842</v>
+        <v>0.001847617158453844</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001379467442973387</v>
+        <v>0.001379467442973388</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002041349026639383</v>
+        <v>0.002041349026639381</v>
       </c>
       <c r="H6" t="n">
         <v>0.002042998950643005</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002032335896685543</v>
+        <v>0.002032335896685541</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002043131380850402</v>
+        <v>0.002043131380850399</v>
       </c>
       <c r="K6" t="n">
         <v>0.00135663466780577</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002746888722948149</v>
+        <v>0.002746888722948144</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001683065014342446</v>
+        <v>0.001683065014342441</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002052510368252527</v>
+        <v>0.00205251036825252</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00206317372949579</v>
+        <v>0.002063173729495789</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002491147638687204</v>
+        <v>0.002491147638687201</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002052510327911346</v>
+        <v>0.002052510327911341</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002061523498206362</v>
+        <v>0.002061523498206358</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002063173422210104</v>
+        <v>0.002063173422210099</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002052510368252527</v>
+        <v>0.00205251036825252</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002063173422210104</v>
+        <v>0.002063173422210099</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001834001974844172</v>
+        <v>0.001834001974844166</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002063173422210104</v>
+        <v>0.002063173422210099</v>
       </c>
     </row>
     <row r="8">
@@ -7091,19 +7091,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001407454262855079</v>
+        <v>0.001407454262855078</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001334246484216006</v>
+        <v>0.001334246484216005</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001468535487086766</v>
+        <v>0.001468535487086764</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001334246484216006</v>
+        <v>0.001334246484216005</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001334246484216006</v>
+        <v>0.001334246484216005</v>
       </c>
       <c r="G8" t="n">
         <v>0.001410585542019513</v>
@@ -7112,16 +7112,16 @@
         <v>0.001485508092998582</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001334246484216006</v>
+        <v>0.001334246484216005</v>
       </c>
       <c r="J8" t="n">
         <v>0.001323713362514495</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001397907533939276</v>
+        <v>0.001397907533939274</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001440198217017473</v>
+        <v>0.001490520306891593</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001454746417975065</v>
+        <v>0.001454746417975064</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00138892595586298</v>
+        <v>0.001388925955862978</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001479626531993181</v>
+        <v>0.001479626531993179</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00138892595586298</v>
+        <v>0.001388925955862978</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00138892595586298</v>
+        <v>0.001388925955862978</v>
       </c>
       <c r="G9" t="n">
         <v>0.001455684682740824</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001486595746589799</v>
+        <v>0.001486595746589798</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00138892595586298</v>
+        <v>0.001388925955862978</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001420724983520331</v>
+        <v>0.00142072498352033</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001450866056529176</v>
+        <v>0.001450866056529175</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001488622477601317</v>
+        <v>0.001488622477601316</v>
       </c>
     </row>
   </sheetData>
@@ -7253,7 +7253,7 @@
         <v>0.007159127332110423</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02382311419293674</v>
+        <v>0.02382311419293671</v>
       </c>
       <c r="E2" t="n">
         <v>0.007159127332110423</v>
@@ -7262,22 +7262,22 @@
         <v>0.007159127332110423</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02277166339412117</v>
+        <v>0.0227716633941211</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05838325797260726</v>
+        <v>0.05838325797260724</v>
       </c>
       <c r="I2" t="n">
         <v>0.007159127332110423</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02234622276602955</v>
+        <v>0.02234622276602953</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01108606348175528</v>
+        <v>0.01108606348175525</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09547613542446365</v>
+        <v>0.02052356817175122</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006100827189552216</v>
+        <v>0.0006100827189552195</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005263679082691744</v>
+        <v>0.0005263679082691731</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006100827189552216</v>
+        <v>0.0006100827189552194</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005436830890058643</v>
+        <v>0.0005436830890058632</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005436830890058642</v>
+        <v>0.0005436830890058612</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006078152841882667</v>
+        <v>0.0006078152841882661</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006100827189552216</v>
+        <v>0.0006100827189552195</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005954848600565008</v>
+        <v>0.0005954848600564993</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006100827189552216</v>
+        <v>0.0006100827189552194</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006100827189552216</v>
+        <v>0.0006100827189552194</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006100827189552216</v>
+        <v>0.0006100827189552194</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001431030401347973</v>
+        <v>0.00143103040134797</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001381201927472006</v>
+        <v>0.001381201927471982</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001447832013063921</v>
+        <v>0.001447832013063927</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001297899083021372</v>
+        <v>0.001297899083021376</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001411545636643904</v>
+        <v>0.001411545636643903</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002187308139397614</v>
+        <v>0.002187308139397613</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00224439520673426</v>
+        <v>0.002244395206734254</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002174977715265845</v>
+        <v>0.002174977715265848</v>
       </c>
       <c r="J4" t="n">
         <v>0.002207183296893006</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001412975229415609</v>
+        <v>0.001412975229415611</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001456299566757837</v>
+        <v>0.001456299566757834</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00115358646945837</v>
+        <v>0.001153586469458367</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001138988610559648</v>
+        <v>0.001138988610559647</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001153532553970154</v>
+        <v>0.001153532553970152</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001138114876032638</v>
+        <v>0.001138114876032634</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001138114876032638</v>
+        <v>0.001138114876032634</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001151319034691415</v>
+        <v>0.001151319034691411</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00115358646945837</v>
+        <v>0.001153586469458367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001138988610559648</v>
+        <v>0.001138988610559647</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00115358646945837</v>
+        <v>0.001153586469458367</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00115358646945837</v>
+        <v>0.001153586469458367</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00115358646945837</v>
+        <v>0.001153586469458367</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001623439288574887</v>
+        <v>0.001623439288574884</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002434525372329995</v>
+        <v>0.002434525372325217</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002621066186009302</v>
+        <v>0.002621066186009287</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002208593323070352</v>
+        <v>0.002208593323070346</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00163454449245674</v>
+        <v>0.001634544492456734</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002447462088340211</v>
+        <v>0.002447462088340204</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002449729523107251</v>
+        <v>0.002449729523107245</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002435131664208446</v>
+        <v>0.002435131664208435</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002449891912688178</v>
+        <v>0.002449891912688176</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001608090523260059</v>
+        <v>0.001608090523260056</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003312858766226897</v>
+        <v>0.003312858766226881</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002437538994546133</v>
+        <v>0.002437538994546128</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003007730262137943</v>
+        <v>0.003007730262137942</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003022328165099206</v>
+        <v>0.003022328165099199</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003682563440032249</v>
+        <v>0.003682563440032241</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003007729370636021</v>
+        <v>0.003007729370636012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003020060686269706</v>
+        <v>0.003020060686269697</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003022328121036664</v>
+        <v>0.003022328121036669</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003007730262137943</v>
+        <v>0.003007730262137942</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003022328121036664</v>
+        <v>0.003022328121036669</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002683499023037321</v>
+        <v>0.002683499023037316</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003022328121036664</v>
+        <v>0.003022328121036669</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001356097071595939</v>
+        <v>0.001356097071595938</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001490835920311273</v>
+        <v>0.001490835920311272</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001110041920085208</v>
+        <v>0.001110041920085204</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001490835920311273</v>
+        <v>0.001490835920311272</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001490835920311273</v>
+        <v>0.001490835920311272</v>
       </c>
       <c r="G8" t="n">
         <v>0.001152560015653367</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003863151390427934</v>
+        <v>0.0003863151390427943</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001490835920311273</v>
+        <v>0.001490835920311272</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001199130670077779</v>
+        <v>0.001199130670077777</v>
       </c>
       <c r="K8" t="n">
         <v>0.001423688257160599</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0001984465655914456</v>
+        <v>-0.0001984465655914466</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00150475809043323</v>
+        <v>0.001504758090433228</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001545677302737656</v>
+        <v>0.001545677302737654</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001404556270895077</v>
+        <v>0.001404556270895074</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001545677302737656</v>
+        <v>0.001545677302737654</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001545677302737656</v>
+        <v>0.001545677302737654</v>
       </c>
       <c r="G9" t="n">
         <v>0.001419933748497257</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001110967865379841</v>
+        <v>0.001110967865379838</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001545677302737656</v>
+        <v>0.001545677302737654</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001441006598600605</v>
+        <v>0.001441006598600604</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001532300622345225</v>
+        <v>0.001532300622345223</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0008730182253874037</v>
+        <v>0.001466320447010409</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002704252549387826</v>
+        <v>0.002704252549387825</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004982689781134014</v>
+        <v>0.004982689781134017</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01939514359039635</v>
+        <v>0.01939514359039634</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004982689781134014</v>
+        <v>0.004982689781134017</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004982689781134014</v>
+        <v>0.004982689781134017</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0131277096219683</v>
+        <v>0.01312770962196828</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008132751857594865</v>
+        <v>0.008132751857594878</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004982689781134014</v>
+        <v>0.004982689781134017</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01438860889692123</v>
+        <v>0.01438860889692124</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004895065595051509</v>
+        <v>0.004895065595051514</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00599899084749178</v>
+        <v>0.05238967152271241</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005656620241668095</v>
+        <v>0.0005656620241668104</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005038529986503066</v>
+        <v>0.000503852998650307</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005656620241668095</v>
+        <v>0.0005656620241668104</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005186630338866153</v>
+        <v>0.0005186630338866159</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005186630338866153</v>
+        <v>0.0005186630338866157</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005637288655733967</v>
+        <v>0.0005637288655733968</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005656620241668095</v>
+        <v>0.0005656620241668104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005532112154755182</v>
+        <v>0.0005532112154755186</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005656620241668095</v>
+        <v>0.0005656620241668104</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005656620241668095</v>
+        <v>0.0005656620241668104</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005656620241668095</v>
+        <v>0.0005656620241668104</v>
       </c>
     </row>
     <row r="4">
@@ -7723,13 +7723,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001989323548507006</v>
+        <v>0.001989323548507005</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001296206547256515</v>
+        <v>0.001296206547256519</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001353893618653311</v>
+        <v>0.001353897441203445</v>
       </c>
       <c r="E4" t="n">
         <v>0.001217257831777483</v>
@@ -7738,22 +7738,22 @@
         <v>0.001315193220616124</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001328827094952763</v>
+        <v>0.001987390389913592</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002022150629776914</v>
+        <v>0.00202215062977691</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00197687273981571</v>
+        <v>0.001976872739815714</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001387803844482496</v>
+        <v>0.001387803844482498</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001320307389011501</v>
+        <v>0.001320307389011499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001341315717995472</v>
+        <v>0.001341315717995471</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001035794655949661</v>
+        <v>0.001035794655949663</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001023343847258371</v>
+        <v>0.001023343847258372</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001035744394629046</v>
+        <v>0.001035744394629051</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001022520257903285</v>
+        <v>0.001022520257903284</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001022520257903285</v>
+        <v>0.001022520257903284</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00103386149735625</v>
+        <v>0.001033861497356249</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001035794655949661</v>
+        <v>0.001035794655949663</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001023343847258371</v>
+        <v>0.001023343847258372</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001035794655949661</v>
+        <v>0.001035794655949663</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001035794655949661</v>
+        <v>0.001035794655949663</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001035794655949661</v>
+        <v>0.001035794655949663</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001440984676371208</v>
+        <v>0.001440984676371209</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002146657892793979</v>
+        <v>0.002146657892793976</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002308721871201904</v>
+        <v>0.00230872187120191</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00195014735898131</v>
+        <v>0.001950147358981308</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0014508544846103</v>
+        <v>0.001450854484610301</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002157759856609077</v>
+        <v>0.002157759856609074</v>
       </c>
       <c r="H6" t="n">
         <v>0.002159693015202411</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002147242206511197</v>
+        <v>0.002147242206511198</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002159834261884068</v>
+        <v>0.002159834261884065</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001427634299999786</v>
+        <v>0.001427634299999784</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002910443972434325</v>
+        <v>0.002910443972434321</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001949967684526869</v>
+        <v>0.00194996768452687</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00239109860334438</v>
+        <v>0.002391098603344386</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00240354988050674</v>
+        <v>0.002403549880506741</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00291452252869246</v>
+        <v>0.002914522528692459</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002391098447983494</v>
+        <v>0.0023910984479835</v>
       </c>
       <c r="G7" t="n">
         <v>0.002401616253442256</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00240354941203567</v>
+        <v>0.002403549412035672</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00239109860334438</v>
+        <v>0.002391098603344386</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00240354941203567</v>
+        <v>0.002403549412035672</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00183240893163339</v>
+        <v>0.002140742574802051</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00240354941203567</v>
+        <v>0.002403549412035672</v>
       </c>
     </row>
     <row r="8">
@@ -7886,34 +7886,34 @@
         <v>0.001582607819736304</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001501201825584088</v>
+        <v>0.001501201825584087</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001127214033082472</v>
+        <v>0.00112721403308247</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001501201825584088</v>
+        <v>0.001501201825584087</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001501201825584088</v>
+        <v>0.001501201825584087</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001312034086737246</v>
+        <v>0.001312034086737245</v>
       </c>
       <c r="H8" t="n">
         <v>0.001457046182615193</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001501201825584088</v>
+        <v>0.001501201825584087</v>
       </c>
       <c r="J8" t="n">
         <v>0.001313951618554891</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001523035439549245</v>
+        <v>0.001523035439549244</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005130204653502505</v>
+        <v>0.0005130204653502499</v>
       </c>
     </row>
     <row r="9">
@@ -7923,34 +7923,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001576617699116483</v>
+        <v>0.001576617699116481</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001531155863262761</v>
+        <v>0.001531155863262759</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00139115219740002</v>
+        <v>0.001391152197400019</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001531155863262761</v>
+        <v>0.001531155863262759</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001531155863262761</v>
+        <v>0.001531155863262759</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001465133650741448</v>
+        <v>0.001465133650741447</v>
       </c>
       <c r="H9" t="n">
         <v>0.001525643529892211</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001531155863262761</v>
+        <v>0.001531155863262759</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001467318475150549</v>
+        <v>0.00146731847515055</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001552360207136423</v>
+        <v>0.001552360207136422</v>
       </c>
       <c r="L9" t="n">
         <v>0.001141831949404544</v>

--- a/Results/Hydrogen/hydrogen eutrophication marine results.xlsx
+++ b/Results/Hydrogen/hydrogen eutrophication marine results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02888116415279576</v>
+        <v>0.001747973185262491</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01513942999642757</v>
+        <v>0.001735851995685486</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05865733979347303</v>
+        <v>0.001777637918809822</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01513942999642757</v>
+        <v>0.001735851995685486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01513942999642757</v>
+        <v>0.001735851995685486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0381363148994727</v>
+        <v>0.001751696145681161</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07880398026956498</v>
+        <v>0.001790476491810177</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01513942999642757</v>
+        <v>0.001735851995685486</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03604030525438004</v>
+        <v>0.001752800290070323</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01574380501930672</v>
+        <v>0.001733704884358358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1223964115472981</v>
+        <v>0.001747625045104196</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.001756664639375886</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0006553626560496913</v>
+        <v>0.001759447208926159</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.001756664639375886</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0006744875365914065</v>
+        <v>0.001759447208926159</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0006744875365914065</v>
+        <v>0.001759447208926159</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007101619255812748</v>
+        <v>0.001752468747732656</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.001756664639375886</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000698453555514454</v>
+        <v>0.001759447208926159</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.001756664639375886</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.001756664639375886</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007123338257491609</v>
+        <v>0.001756664639375886</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001650054115013732</v>
+        <v>0.02888116415279578</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001598271453166527</v>
+        <v>0.0151394299964276</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00171030625585864</v>
+        <v>0.05865733979347301</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001504742499186781</v>
+        <v>0.0151394299964276</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00163454295157516</v>
+        <v>0.0151394299964276</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002566167541848276</v>
+        <v>0.03813631489947265</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002625352167206042</v>
+        <v>0.07880398026956496</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002554459171781456</v>
+        <v>0.0151394299964276</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0025747667683272</v>
+        <v>0.03604030525438003</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001624144813699045</v>
+        <v>0.01574380501930673</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001683281238037236</v>
+        <v>0.1223964115472984</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001375314015569849</v>
+        <v>0.0007123338257491594</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001361433745335143</v>
+        <v>0.0006553626560496913</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001375254005885967</v>
+        <v>0.0007123338257491594</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001360557110117741</v>
+        <v>0.0006744875365914064</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001360557110117741</v>
+        <v>0.0006744875365914062</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001373142115401964</v>
+        <v>0.0007101619255812739</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001375314015569849</v>
+        <v>0.0007123338257491594</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001361433745335143</v>
+        <v>0.0006984535555144524</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001375314015569849</v>
+        <v>0.0007123338257491594</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001375314015569849</v>
+        <v>0.0007123338257491594</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001375314015569849</v>
+        <v>0.0007123338257491594</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00194889056503078</v>
+        <v>0.001650054115013735</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002932759860555109</v>
+        <v>0.001598271453166538</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003154214865369056</v>
+        <v>0.001710306255858642</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002659774034264544</v>
+        <v>0.001504742499186777</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001966168239391153</v>
+        <v>0.001634542951575161</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002945035471852984</v>
+        <v>0.002566167541848274</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002947207372020899</v>
+        <v>0.002625352167206042</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002933327101786162</v>
+        <v>0.002554459171781453</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002947403569729811</v>
+        <v>0.002574766768327201</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00193034631781596</v>
+        <v>0.001624144813699049</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003990032754678966</v>
+        <v>0.001683281238037235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003521769701192667</v>
+        <v>0.001375314015569848</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004377397803454508</v>
+        <v>0.001361433745335141</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004391278352882408</v>
+        <v>0.001375254005885965</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005380790948326927</v>
+        <v>0.001360557110117739</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004377396737198235</v>
+        <v>0.001360557110117739</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00438910617352133</v>
+        <v>0.001373142115401963</v>
       </c>
       <c r="H7" t="n">
-        <v>0.004391278073689221</v>
+        <v>0.001375314015569848</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004377397803454508</v>
+        <v>0.001361433745335141</v>
       </c>
       <c r="J7" t="n">
-        <v>0.004391278073689221</v>
+        <v>0.001375314015569848</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00329641175366071</v>
+        <v>0.001375314015569848</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004391278073689221</v>
+        <v>0.001375314015569848</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001135728969600704</v>
+        <v>0.001948890565030778</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001446042362253145</v>
+        <v>0.002932759860555109</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005146423656717419</v>
+        <v>0.003154214865369058</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001446042362253145</v>
+        <v>0.002659774034264543</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001446042362253145</v>
+        <v>0.00196616823939115</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009694298668947933</v>
+        <v>0.002945035471852983</v>
       </c>
       <c r="H8" t="n">
-        <v>0.000273801081812274</v>
+        <v>0.002947207372020898</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001446042362253145</v>
+        <v>0.002933327101786162</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00104028573292882</v>
+        <v>0.00294740356972981</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001435152206400083</v>
+        <v>0.001930346317815957</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001152487928766263</v>
+        <v>0.003990032754678967</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.003521769701192666</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.00437739780345451</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.004391278352882409</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.005380790948326924</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.004377396737198234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.004389106173521329</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.004391278073689218</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.00437739780345451</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.004391278073689218</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.003296411753660711</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.004391278073689218</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.001135728969600705</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001446042362253146</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0005146423656717433</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001446042362253146</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001446042362253146</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0009694298668947928</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0002738010818122755</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001446042362253146</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.00104028573292882</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001435152206400083</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001152487928766265</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.001465445476710214</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.001465445476710213</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.001593251791687278</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>0.001212513826184299</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.001593251791687278</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.001593251791687278</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.00139541095950308</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.001115768847512963</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.001395410959503081</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.001115768847512964</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.001593251791687278</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.001426845604672791</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>0.001426845604672792</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.001587415702755038</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.0008095142860333039</v>
+      <c r="L11" t="n">
+        <v>0.0008095142860333048</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002357454088996897</v>
+        <v>0.00151573369973695</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005796715854394415</v>
+        <v>0.001458755348574054</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004825673873168731</v>
+        <v>0.001518856616352786</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005796715854394415</v>
+        <v>0.001458755348574054</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005796715854394415</v>
+        <v>0.001458755348574054</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00681985201923422</v>
+        <v>0.001520248994725358</v>
       </c>
       <c r="H2" t="n">
-        <v>0.005053068363022818</v>
+        <v>0.001518512857927506</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005796715854394415</v>
+        <v>0.001458755348574054</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009411506195027184</v>
+        <v>0.001523568991270678</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004556896355457286</v>
+        <v>0.001518681451581121</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003446544964941638</v>
+        <v>0.001517729430835752</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005549807825525941</v>
+        <v>0.001549535992267257</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005061597788830197</v>
+        <v>0.001487312763684782</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005549807825525941</v>
+        <v>0.001549535992267257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005200852085627881</v>
+        <v>0.001487312763684782</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005200852085627877</v>
+        <v>0.001487312763684782</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005532790478318248</v>
+        <v>0.001548643035969172</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005549807825525941</v>
+        <v>0.001549535992267257</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00054398834138387</v>
+        <v>0.001487312763684782</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005549807825525941</v>
+        <v>0.001549535992267257</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005549807825525941</v>
+        <v>0.001549535992267257</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005549807825525941</v>
+        <v>0.001549535992267257</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00131384574240943</v>
+        <v>0.002357454088996889</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001293893579471004</v>
+        <v>0.005796715854394415</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001934975575615242</v>
+        <v>0.004825673873168728</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001214620874693906</v>
+        <v>0.005796715854394415</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001302409852743481</v>
+        <v>0.005796715854394415</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001922375967007184</v>
+        <v>0.00681985201923424</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00195940920931378</v>
+        <v>0.005053068363022815</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001302853301240705</v>
+        <v>0.005796715854394415</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001369440127342447</v>
+        <v>0.009411506195027158</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001314042285451014</v>
+        <v>0.004556896355457285</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001313875967113683</v>
+        <v>0.003446544964941641</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001001775188947017</v>
+        <v>0.0005549807825525943</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009907827477782893</v>
+        <v>0.0005061597788830179</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00100172468964244</v>
+        <v>0.0005549807825525943</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009900888870349876</v>
+        <v>0.0005200852085627867</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009900888870349876</v>
+        <v>0.0005200852085627867</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001000073454226248</v>
+        <v>0.0005532790478318245</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001001775188947017</v>
+        <v>0.0005549807825525943</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009907827477782893</v>
+        <v>0.0005439883413838678</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001001775188947017</v>
+        <v>0.0005549807825525943</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001001775188947017</v>
+        <v>0.0005549807825525943</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001001775188947017</v>
+        <v>0.0005549807825525943</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001380554690560401</v>
+        <v>0.001313845742409426</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002051170782962955</v>
+        <v>0.001293893579470995</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002204062679890804</v>
+        <v>0.00193497557561524</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001864666115389196</v>
+        <v>0.001214620874693912</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001390799185159109</v>
+        <v>0.001302409852743479</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002060928199993602</v>
+        <v>0.001922375967007168</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002062629934714339</v>
+        <v>0.001959409209313776</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002051637493545641</v>
+        <v>0.001302853301240704</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002062763981959419</v>
+        <v>0.00136944012734244</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001367884792728547</v>
+        <v>0.001314042285451013</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00277511456136067</v>
+        <v>0.00131387596711368</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001698221192128123</v>
+        <v>0.001001775188947014</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002071956389665967</v>
+        <v>0.00099078274777829</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002082949152179934</v>
+        <v>0.001001724689642437</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002515924135190009</v>
+        <v>0.0009900888870349857</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002071956323672973</v>
+        <v>0.0009900888870349857</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002081247096113925</v>
+        <v>0.001000073454226248</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002082948830834693</v>
+        <v>0.001001775188947014</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002071956389665967</v>
+        <v>0.00099078274777829</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002082948830834693</v>
+        <v>0.001001775188947014</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001860036261183415</v>
+        <v>0.001001775188947014</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002082948830834693</v>
+        <v>0.001001775188947014</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001505053779026049</v>
+        <v>0.001380554690560403</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00135239747325702</v>
+        <v>0.002051170782962955</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001439658351766643</v>
+        <v>0.0022040626798908</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00135239747325702</v>
+        <v>0.001864666115389194</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00135239747325702</v>
+        <v>0.001390799185159105</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001391579940483862</v>
+        <v>0.002060928199993595</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001448778162187328</v>
+        <v>0.002062629934714336</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00135239747325702</v>
+        <v>0.002051637493545638</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00134248453083519</v>
+        <v>0.002062763981959418</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001443386705515909</v>
+        <v>0.001367884792728543</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001488746779492829</v>
+        <v>0.002775114561360667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001698221192128116</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002071956389665965</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002082949152179932</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002515924135190003</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002071956323672975</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002081247096113919</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002082948830834694</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002071956389665965</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002082948830834694</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.001860036261183407</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002082948830834694</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.00150505377902605</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.00135239747325702</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001439658351766642</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.00135239747325702</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.00135239747325702</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001391579940483863</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00144877816218733</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.00135239747325702</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001342484530835189</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.00144338670551591</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001488746779492832</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.001495494150955799</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.0014954941509558</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.001397368461479902</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>0.001468861939765742</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.001397368461479902</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.001397368461479902</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.001448784785749155</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.001472667724144985</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.001448784785749156</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.001472667724144987</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.001397368461479902</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.00142935991648523</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001470383187831553</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.001488898829391464</v>
+      <c r="J11" t="n">
+        <v>0.001429359916485232</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001470383187831554</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001488898829391467</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,321 +1463,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.006302078885303048</v>
+        <v>0.003158485158422718</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009594410728319791</v>
+        <v>0.001130974165986747</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01671249283341019</v>
+        <v>0.001696691536016832</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007963301996171549</v>
+        <v>0.001378093464827534</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007963301996171549</v>
+        <v>0.001378093464827534</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01493075912742126</v>
+        <v>0.001436150046603277</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03433290738343971</v>
+        <v>0.001712334411062794</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007963301996171549</v>
+        <v>0.001378093464827534</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02830406137785921</v>
+        <v>0.001849020876266156</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007467634140212303</v>
+        <v>0.001895772744807597</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02427979573568993</v>
+        <v>0.001836071795683142</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005642020218236118</v>
+        <v>0.003213938407408079</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004853117457798572</v>
+        <v>0.001150680736190457</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005642020218236116</v>
+        <v>0.001717170406343982</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005339936364825233</v>
+        <v>0.001403470508791077</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005339936364825233</v>
+        <v>0.001403470508791077</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005620359132407777</v>
+        <v>0.001454915667250033</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005642020218236118</v>
+        <v>0.001717170406343982</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005501937874740917</v>
+        <v>0.001403470508791077</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005642020218236118</v>
+        <v>0.00186028242563459</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005642020218236116</v>
+        <v>0.001929806642891752</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005642020218236116</v>
+        <v>0.001853541844182383</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002056374876000495</v>
+        <v>0.006302078885303051</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001340654221207999</v>
+        <v>0.009594410728319873</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001372050294837979</v>
+        <v>0.01671249283341019</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001248990640132055</v>
+        <v>0.007963301996171542</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00134737404011053</v>
+        <v>0.007963301996171542</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001360163549052437</v>
+        <v>0.0149307591274213</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002110381362945667</v>
+        <v>0.03433290738343973</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001348321423285751</v>
+        <v>0.007963301996171542</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002065593364019784</v>
+        <v>0.02830406137785919</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001347302299137546</v>
+        <v>0.007467634140212299</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001365562165139729</v>
+        <v>0.02427979573568993</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001084506150114604</v>
+        <v>0.0005642020218236115</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001083439116145952</v>
+        <v>0.0004853117457798585</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001084457028350448</v>
+        <v>0.0005642020218236114</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00107186709924634</v>
+        <v>0.0005339936364825227</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00107186709924634</v>
+        <v>0.0005339936364825229</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001082340041531768</v>
+        <v>0.0005620359132407758</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001084506150114604</v>
+        <v>0.0005642020218236114</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001070497915765082</v>
+        <v>0.000550193787474091</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001084506150114604</v>
+        <v>0.0005642020218236115</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001084506150114604</v>
+        <v>0.0005642020218236114</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001084506150114604</v>
+        <v>0.0005642020218236114</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001531553942445151</v>
+        <v>0.002056374876000497</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002324725415103292</v>
+        <v>0.001340654221207992</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002488642830457254</v>
+        <v>0.001372050294837981</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002094811637885227</v>
+        <v>0.001248990640132054</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001543519618358416</v>
+        <v>0.001347374040110531</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002322102228167567</v>
+        <v>0.001360163549052439</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002324268336751327</v>
+        <v>0.002110381362945669</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002310260102400885</v>
+        <v>0.001348321423285754</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002324424127711081</v>
+        <v>0.002065593364019782</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001516828865600369</v>
+        <v>0.001347302299137546</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003152324807186038</v>
+        <v>0.001365562165139729</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002169631037683372</v>
+        <v>0.001084506150114604</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00269005899328253</v>
+        <v>0.001083439116145952</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002691126257723187</v>
+        <v>0.001084457028350448</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003278911638995186</v>
+        <v>0.00107186709924634</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002677117374716063</v>
+        <v>0.00107186709924634</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002688959918668346</v>
+        <v>0.001082340041531767</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002691126027251182</v>
+        <v>0.001084506150114604</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002677117792901663</v>
+        <v>0.001070497915765082</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002691126027251182</v>
+        <v>0.001084506150114604</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002388969879163187</v>
+        <v>0.001084506150114604</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002691126027251183</v>
+        <v>0.001084506150114604</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003082045433884203</v>
+        <v>0.00153155394244515</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009477450194473532</v>
+        <v>0.002324725415103292</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001343981051833632</v>
+        <v>0.002488642830457252</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001233935975189952</v>
+        <v>0.002094811637885226</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001233935975189952</v>
+        <v>0.001543519618358412</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001132663394450969</v>
+        <v>0.002322102228167567</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001029349980645344</v>
+        <v>0.002324268336751323</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001233935975189952</v>
+        <v>0.002310260102400884</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00125184798763594</v>
+        <v>0.002324424127711079</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001770955691116304</v>
+        <v>0.00151682886560037</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00138026323349421</v>
+        <v>0.003152324807186033</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.002169631037683377</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002690058993282521</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002691126257723188</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.003278911638995186</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002677117374716061</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002688959918668342</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002691126027251174</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002677117792901662</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002691126027251174</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002388969879163184</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002691126027251174</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.003082045433884205</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0009477450194473529</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001343981051833632</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001233935975189953</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001233935975189953</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001132663394450967</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001029349980645343</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001233935975189953</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001251847987635941</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001770955691116301</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.00138026323349421</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.00309847343515139</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.003098473435151389</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.001038637768150879</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.001526889190430715</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.001526889190430716</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.001300954711764521</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.001300954711764521</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G11" t="n">
         <v>0.001289524235522643</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.001399373925416273</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="H11" t="n">
+        <v>0.001399373925416272</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.001300954711764521</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.001572181268011263</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001823495055521824</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.001620728519570583</v>
+      <c r="J11" t="n">
+        <v>0.001572181268011264</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001823495055521821</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001620728519570582</v>
       </c>
     </row>
   </sheetData>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.003277360994062616</v>
+        <v>0.003143476296008735</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006663008402527814</v>
+        <v>0.001112336442491846</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0115659218871192</v>
+        <v>0.001677813411667048</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005036409147328623</v>
+        <v>0.00137298274394769</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005036409147328623</v>
+        <v>0.00137298274394769</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009159230727237776</v>
+        <v>0.001422442525442398</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01746641939187345</v>
+        <v>0.001682667639621444</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005036409147328623</v>
+        <v>0.00137298274394769</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01818707070270403</v>
+        <v>0.001861422188536931</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00381281351892143</v>
+        <v>0.001893639443916087</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008249532478640506</v>
+        <v>0.001593553553456382</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005390954554493577</v>
+        <v>0.003201663547310878</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004734029366716137</v>
+        <v>0.001134417211015222</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005390954554493577</v>
+        <v>0.001702907035731485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005804080451127616</v>
+        <v>0.001401056828287818</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005804080451127616</v>
+        <v>0.001401056828287818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005371670885479859</v>
+        <v>0.001446597591842625</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005390954554493577</v>
+        <v>0.001702907035731485</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005266128917809152</v>
+        <v>0.001401056828287818</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005390954554493577</v>
+        <v>0.001882511766080086</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005390954554493577</v>
+        <v>0.001931353289664565</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005390954554493577</v>
+        <v>0.001622364543005413</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001943217746280046</v>
+        <v>0.00327736099406262</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001285817826479995</v>
+        <v>0.006663008402527816</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001950979976802393</v>
+        <v>0.01156592188711923</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00120833424359802</v>
+        <v>0.005036409147328618</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001294616247367692</v>
+        <v>0.005036409147328618</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001941289379378673</v>
+        <v>0.00915923072723774</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001989411158193292</v>
+        <v>0.01746641939187344</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001289983594040004</v>
+        <v>0.005036409147328618</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001361668538451254</v>
+        <v>0.018187070702704</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001294369195784952</v>
+        <v>0.00381281351892144</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001300151551918278</v>
+        <v>0.008249532478640515</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001020837710383894</v>
+        <v>0.0005390954554493543</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001019951454724184</v>
+        <v>0.000473402936671614</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001020791584666491</v>
+        <v>0.0005390954554493543</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001017161175269407</v>
+        <v>0.000580408045112761</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001017161175269407</v>
+        <v>0.00058040804511276</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00101890934348252</v>
+        <v>0.000537167088547985</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001020837710383894</v>
+        <v>0.0005390954554493543</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001008355146715451</v>
+        <v>0.000526612891780915</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001020837710383894</v>
+        <v>0.0005390954554493543</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001020837710383894</v>
+        <v>0.0005390954554493543</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001020837710383894</v>
+        <v>0.0005390954554493543</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001431999535669102</v>
+        <v>0.001943217746280048</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002175363116414512</v>
+        <v>0.001285817826480024</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00232017127469316</v>
+        <v>0.001950979976802391</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001961657250707788</v>
+        <v>0.001208334243598021</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0014481161536817</v>
+        <v>0.001294616247367693</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002165704536747716</v>
+        <v>0.001941289379378672</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00216763290365091</v>
+        <v>0.001989411158193288</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002155150339980645</v>
+        <v>0.001289983594040004</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002167777476489446</v>
+        <v>0.001361668538451255</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001418334768199582</v>
+        <v>0.001294369195784954</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002936063468991341</v>
+        <v>0.00130015155191828</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0018332516150381</v>
+        <v>0.001020837710383894</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002263520418292128</v>
+        <v>0.001019951454724186</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002264406954877072</v>
+        <v>0.001020791584666492</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002749467910374929</v>
+        <v>0.001017161175269408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002251923910376462</v>
+        <v>0.001017161175269408</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002262478307050465</v>
+        <v>0.001018909343482519</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002264406673951839</v>
+        <v>0.001020837710383894</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002251924110283394</v>
+        <v>0.00100835514671545</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002264406673951839</v>
+        <v>0.001020837710383894</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002014593857697481</v>
+        <v>0.001020837710383894</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002264406673951839</v>
+        <v>0.001020837710383894</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003133458442330863</v>
+        <v>0.0014319995356691</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009890241507717347</v>
+        <v>0.0021753631164145</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001433751047898148</v>
+        <v>0.002320171274693159</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001292068866998126</v>
+        <v>0.001961657250707791</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001292068866998126</v>
+        <v>0.001448116153681697</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001242352177603973</v>
+        <v>0.002165704536747713</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001338982945092807</v>
+        <v>0.002167632903650912</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001292068866998126</v>
+        <v>0.002155150339980648</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001473789359083564</v>
+        <v>0.00216777747648945</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00185171858621509</v>
+        <v>0.001418334768199582</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001460133349035871</v>
+        <v>0.002936063468991336</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001833251615038097</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002263520418292125</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002264406954877067</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002749467910374928</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002251923910376461</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.00226247830705046</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002264406673951834</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002251924110283397</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002264406673951834</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002014593857697478</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002264406673951834</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.003133458442330864</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.000989024150771735</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001433751047898145</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001292068866998126</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001292068866998126</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001242352177603974</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001338982945092807</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001292068866998126</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001473789359083563</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001851718586215086</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001460133349035871</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.003112442755886059</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.001046182136740867</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.001555346579453639</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.001323392874236855</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.001323392874236855</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>0.003112442755886057</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001046182136740868</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.001555346579453638</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001323392874236854</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001323392874236854</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.001329510211072298</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>0.001517081018623581</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.001323392874236855</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.001675452190832488</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001857405400065835</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.001519737843200102</v>
+      <c r="I11" t="n">
+        <v>0.001323392874236854</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.001675452190832485</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001857405400065832</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001519737843200103</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,320 +2415,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001640608874312359</v>
+        <v>0.003128147502249718</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004985534879649683</v>
+        <v>0.001085366634620199</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0075008781519776</v>
+        <v>0.001648728281872981</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00216662707039468</v>
+        <v>0.001270259438329519</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00216662707039468</v>
+        <v>0.001270259438329519</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005462935018253449</v>
+        <v>0.001359083886152676</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00878520582538057</v>
+        <v>0.001649229129568586</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00216662707039468</v>
+        <v>0.001270259438329519</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00876583253670005</v>
+        <v>0.001551863348510583</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002094120116096848</v>
+        <v>0.001871514650542797</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003357987184563695</v>
+        <v>0.0015549053166521</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005214368868232693</v>
+        <v>0.003188087490535642</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004631199147401376</v>
+        <v>0.001109067993845485</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005214368868232691</v>
+        <v>0.001678280310109686</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000560476227146507</v>
+        <v>0.001300171780495334</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005604762271465073</v>
+        <v>0.001300171780495334</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005196553938146276</v>
+        <v>0.001386604726670124</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005214368868232691</v>
+        <v>0.001678280310109686</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005099279131728018</v>
+        <v>0.001300171780495334</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005214368868232691</v>
+        <v>0.001578807831008391</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005214368868232691</v>
+        <v>0.001911014183004388</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005214368868232691</v>
+        <v>0.001588299061606455</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00127781839299121</v>
+        <v>0.001640608874312369</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001265452828244961</v>
+        <v>0.004985534879649698</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001280200329223664</v>
+        <v>0.007500878151977623</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001184649191405625</v>
+        <v>0.002166627070394684</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001270296954005981</v>
+        <v>0.002166627070394684</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001900174095200408</v>
+        <v>0.005462935018253389</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001942632827647637</v>
+        <v>0.008785205825380608</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001890446614558577</v>
+        <v>0.002166627070394684</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001907531825042417</v>
+        <v>0.008765832536700068</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001274521514247139</v>
+        <v>0.002094120116096854</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001273782065207834</v>
+        <v>0.0033579871845637</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009850358955308608</v>
+        <v>0.0005214368868232696</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009842629829125576</v>
+        <v>0.0004631199147401387</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009849894313116545</v>
+        <v>0.0005214368868232696</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009839702793890443</v>
+        <v>0.0005604762271465086</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009839702793890443</v>
+        <v>0.0005604762271465087</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009832544025222224</v>
+        <v>0.0005196553938146294</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009850358955308608</v>
+        <v>0.0005214368868232696</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009735269218803942</v>
+        <v>0.0005099279131728025</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009850358955308608</v>
+        <v>0.0005214368868232696</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009850358955308608</v>
+        <v>0.0005214368868232696</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009850358955308608</v>
+        <v>0.0005214368868232696</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001381622363800126</v>
+        <v>0.001277818392991213</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002102694057646354</v>
+        <v>0.001265452828244964</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0022408554032282</v>
+        <v>0.001280200329223617</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001896235853578204</v>
+        <v>0.00118464919140563</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00139892975093292</v>
+        <v>0.001270296954005984</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002091505593843557</v>
+        <v>0.001900174095200406</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002093287086853994</v>
+        <v>0.001942632827647641</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00208177811320173</v>
+        <v>0.00189044661455858</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00209342694915244</v>
+        <v>0.001907531825042424</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001368402826216729</v>
+        <v>0.001274521514247106</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0028366803983279</v>
+        <v>0.001273782065207839</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001623389797811527</v>
+        <v>0.0009850358955308636</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001999233220623258</v>
+        <v>0.0009842629829125602</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002000006411348513</v>
+        <v>0.0009849894313116575</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002423104529675003</v>
+        <v>0.0009839702793890486</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00198849704211016</v>
+        <v>0.0009839702793890486</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001998224640232926</v>
+        <v>0.0009832544025222243</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002000006133241573</v>
+        <v>0.0009850358955308636</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001988497159591104</v>
+        <v>0.0009735269218803971</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002000006133241573</v>
+        <v>0.0009850358955308636</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001772940083441769</v>
+        <v>0.0009850358955308636</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002000006133241573</v>
+        <v>0.0009850358955308636</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003158151083911236</v>
+        <v>0.001381622363800131</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001003053942079238</v>
+        <v>0.002102694057646357</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00150786269466061</v>
+        <v>0.002240855403228207</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00126007265526358</v>
+        <v>0.001896235853578205</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00126007265526358</v>
+        <v>0.001398929750932921</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001269463582284926</v>
+        <v>0.002091505593843557</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00150075375687253</v>
+        <v>0.002093287086853992</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00126007265526358</v>
+        <v>0.002081778113201733</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001387889472733904</v>
+        <v>0.002093426949152445</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001872693809971349</v>
+        <v>0.001368402826216734</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001528843405384197</v>
+        <v>0.002836680398327906</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001623389797811535</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.001999233220623274</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002000006411348527</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.00242310452967502</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.001988497042110173</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001998224640232938</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002000006133241578</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.001988497159591115</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002000006133241578</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.00177294008344178</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002000006133241578</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.00315815108391124</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001003053942079238</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001507862694660611</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001260072655263581</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001260072655263581</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001269463582284928</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00150075375687253</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001260072655263581</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001387889472733908</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001872693809971364</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001528843405384198</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.003114526341833949</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.003114526341833951</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.001037129903219819</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.001571187723754934</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.001252014208560741</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.001252014208560741</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="D11" t="n">
+        <v>0.001571187723754936</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001252014208560742</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001252014208560742</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.001305784292150731</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.001568453982102122</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.001252014208560741</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.001464994887074982</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001854078758692988</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="H11" t="n">
+        <v>0.001568453982102123</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.001252014208560742</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.001464994887074985</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001854078758692996</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.001527852803597038</v>
       </c>
     </row>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,320 +2891,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0022953628188493</v>
+        <v>0.003082634581776003</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001806206675995394</v>
+        <v>0.001100212617902794</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009362671141319126</v>
+        <v>0.00167018037268035</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004638717644930779</v>
+        <v>0.001373335351320529</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004638717644930779</v>
+        <v>0.001373335351320529</v>
       </c>
       <c r="G2" t="n">
-        <v>0.009790515569171064</v>
+        <v>0.001418203623080907</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02706358641093288</v>
+        <v>0.001686722273587519</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004638717644930779</v>
+        <v>0.001373335351320529</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02671771821334062</v>
+        <v>0.001854001974030705</v>
       </c>
       <c r="K2" t="n">
-        <v>0.005305409492797768</v>
+        <v>0.001905986867082323</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02273987961328348</v>
+        <v>0.001835832794923011</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005445549919631986</v>
+        <v>0.003141205096216702</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004592496206228309</v>
+        <v>0.001127905851640449</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005445549919631986</v>
+        <v>0.001698425394820461</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005576403716071056</v>
+        <v>0.001402258964381075</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005576403716071056</v>
+        <v>0.001402258964381075</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005425071956086768</v>
+        <v>0.001442244168277712</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005445549919631986</v>
+        <v>0.001698425394820461</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005312738395232912</v>
+        <v>0.001402258964381075</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005445549919631986</v>
+        <v>0.001866995768899065</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005445549919631986</v>
+        <v>0.001942548684754012</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005445549919631986</v>
+        <v>0.001854768913233305</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001325042088928076</v>
+        <v>0.00229536281884929</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001296289512232375</v>
+        <v>0.001806206675995393</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001327724679698274</v>
+        <v>0.00936267114131913</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001221176581256184</v>
+        <v>0.004638717644930826</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001313782488822854</v>
+        <v>0.004638717644930826</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001322994292573555</v>
+        <v>0.009790515569171043</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002048697620225629</v>
+        <v>0.02706358641093289</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001984252737341994</v>
+        <v>0.004638717644930826</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001386859891684128</v>
+        <v>0.02671771821334063</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001313967924239289</v>
+        <v>0.005305409492797761</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001328899858824941</v>
+        <v>0.02273987961328347</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001055702661523209</v>
+        <v>0.0005445549919631989</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001054683039701811</v>
+        <v>0.0004592496206228213</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00105565498458461</v>
+        <v>0.0005445549919631989</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001055417721390959</v>
+        <v>0.0005576403716071052</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001055417721390959</v>
+        <v>0.0005576403716071053</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001053654865168688</v>
+        <v>0.0005425071956086785</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001055702661523209</v>
+        <v>0.0005445549919631989</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001042421509083302</v>
+        <v>0.0005312738395232915</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001055702661523209</v>
+        <v>0.0005445549919631989</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001055702661523209</v>
+        <v>0.0005445549919631989</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001055702661523209</v>
+        <v>0.0005445549919631989</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001489973541824264</v>
+        <v>0.001325042088928073</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002280506568286197</v>
+        <v>0.001296289512232439</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002430411032004239</v>
+        <v>0.001327724679698268</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002053873420881281</v>
+        <v>0.001221176581256189</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001509164351905485</v>
+        <v>0.001313782488822856</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002266848523441021</v>
+        <v>0.001322994292573556</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002268896319795138</v>
+        <v>0.002048697620225622</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002255615167355634</v>
+        <v>0.001984252737341995</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002269049400229263</v>
+        <v>0.001386859891684121</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001475504651341688</v>
+        <v>0.001313967924239282</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003082546293657103</v>
+        <v>0.001328899858824934</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002028786412423401</v>
+        <v>0.001055702661523205</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002515806921196446</v>
+        <v>0.001054683039701816</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00251682675712385</v>
+        <v>0.001055654984584599</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003066733155641055</v>
+        <v>0.001055417721390961</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002503545077721769</v>
+        <v>0.001055417721390961</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002514778746663322</v>
+        <v>0.001053654865168687</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002516826543017848</v>
+        <v>0.001055702661523205</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002503545390577937</v>
+        <v>0.001042421509083302</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002516826543017847</v>
+        <v>0.001055702661523205</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002234054264722911</v>
+        <v>0.001055702661523205</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002516826543017847</v>
+        <v>0.001055702661523205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003098487753687264</v>
+        <v>0.00148997354182426</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001099471853667181</v>
+        <v>0.002280506568286205</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00149452010093084</v>
+        <v>0.002430411032004243</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001308222657391523</v>
+        <v>0.002053873420881283</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001308222657391523</v>
+        <v>0.001509164351905485</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001234738446408814</v>
+        <v>0.002266848523441028</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001158248357871042</v>
+        <v>0.002268896319795142</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001308222657391523</v>
+        <v>0.002255615167355636</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001292818306763072</v>
+        <v>0.002269049400229267</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001832886177719391</v>
+        <v>0.00147550465134168</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001411749793996181</v>
+        <v>0.003082546293657108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.002028786412423413</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002515806921196454</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002516826757123858</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.003066733155641065</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002503545077721772</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002514778746663318</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002516826543017855</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002503545390577939</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002516826543017855</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.00223405426472291</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002516826543017855</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.003098487753687262</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001099471853667181</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.00149452010093084</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001308222657391524</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001308222657391524</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001234738446408815</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00115824835787104</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001308222657391524</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001292818306763075</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001832886177719396</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001411749793996181</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.003063198054793015</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.00108727505821118</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.001577402814152955</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.001330548531964355</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.001330548531964355</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.001323787858349058</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.001440940000333455</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.001330548531964355</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.001592749398963822</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001856090076907895</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="B11" t="n">
+        <v>0.003063198054793014</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001087275058211181</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.001577402814152956</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001330548531964357</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001330548531964357</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001323787858349059</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.001440940000333456</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.001330548531964357</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.001592749398963825</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0018560900769079</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.001634257683851955</v>
       </c>
     </row>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,320 +3367,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00142656902993934</v>
+        <v>0.003046980480386901</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001553886617342955</v>
+        <v>0.001083621809374542</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002095198327437071</v>
+        <v>0.001644582909818104</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003188964497113127</v>
+        <v>0.001360379282266559</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003188964497113127</v>
+        <v>0.001360379282266559</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00266509877985002</v>
+        <v>0.001390761536707938</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003402184628211935</v>
+        <v>0.001645744986688287</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003188964497113127</v>
+        <v>0.001360379282266559</v>
       </c>
       <c r="J2" t="n">
-        <v>0.009219380818927991</v>
+        <v>0.001833842889094622</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001829838045788945</v>
+        <v>0.001886158149430912</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004154688373875846</v>
+        <v>0.001578984116708679</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005181644144748775</v>
+        <v>0.003105811233081737</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004505888937986672</v>
+        <v>0.001111191321681716</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005181644144748775</v>
+        <v>0.001680395762428164</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005886490095354307</v>
+        <v>0.001390419059210143</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005886490095354307</v>
+        <v>0.001390419059210143</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005164444416674769</v>
+        <v>0.001421932242586693</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005181644144748775</v>
+        <v>0.001680395762428164</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005069970595917429</v>
+        <v>0.001390419059210143</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005181644144748775</v>
+        <v>0.001864689259482319</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005181644144748775</v>
+        <v>0.001926132992981053</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005181644144748775</v>
+        <v>0.001611864197678211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001263822983243038</v>
+        <v>0.001426569029939339</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00124673014943652</v>
+        <v>0.001553886617342952</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001882759125521007</v>
+        <v>0.002095198327437068</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001181608907829613</v>
+        <v>0.003188964497113128</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001259490853542443</v>
+        <v>0.003188964497113128</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001262103010435637</v>
+        <v>0.002665098779850058</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001915207208551609</v>
+        <v>0.003402184628211932</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001866615347504077</v>
+        <v>0.003188964497113128</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001882208490897408</v>
+        <v>0.009219380818927985</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001261076020902329</v>
+        <v>0.001829838045788943</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001260730168669836</v>
+        <v>0.004154688373875842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009776283896510034</v>
+        <v>0.0005181644144748768</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009769165179371092</v>
+        <v>0.0004505888937986666</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009775831993368916</v>
+        <v>0.0005181644144748767</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009824506638299259</v>
+        <v>0.0005886490095354316</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009824506638299259</v>
+        <v>0.0005886490095354318</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009759084168436047</v>
+        <v>0.0005164444416674757</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009776283896510034</v>
+        <v>0.0005181644144748768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009664610347678718</v>
+        <v>0.0005069970595917444</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009776283896510034</v>
+        <v>0.0005181644144748768</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009776283896510034</v>
+        <v>0.0005181644144748768</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009776283896510034</v>
+        <v>0.0005181644144748768</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001367951910726787</v>
+        <v>0.001263822983243036</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00208783515152504</v>
+        <v>0.001246730149436521</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002219283818771931</v>
+        <v>0.001882759125521005</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001882891205267865</v>
+        <v>0.001181608907829611</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001388701337206236</v>
+        <v>0.001259490853542443</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002071352503314096</v>
+        <v>0.001262103010435636</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002073072476121838</v>
+        <v>0.001915207208551606</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002061905121238362</v>
+        <v>0.00186661534750408</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002073211052267088</v>
+        <v>0.001882208490897408</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001354853934236645</v>
+        <v>0.001261076020902383</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002809629867671071</v>
+        <v>0.001260730168669835</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001675319817560083</v>
+        <v>0.0009776283896510032</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002066518053629428</v>
+        <v>0.0009769165179371075</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00206723020698674</v>
+        <v>0.0009775831993368905</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002508318761175399</v>
+        <v>0.0009824506638299259</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002056062555714607</v>
+        <v>0.0009824506638299259</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002065509952535927</v>
+        <v>0.0009759084168436025</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002067229925343324</v>
+        <v>0.0009776283896510032</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002056062570460193</v>
+        <v>0.0009664610347678695</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002067229925343324</v>
+        <v>0.0009776283896510032</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001840155788202851</v>
+        <v>0.0009776283896510032</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002067229925343324</v>
+        <v>0.0009776283896510032</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003080893018728329</v>
+        <v>0.001367951910726786</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001086480672234789</v>
+        <v>0.002087835151525041</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001641740777196003</v>
+        <v>0.002219283818771924</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001325506947614027</v>
+        <v>0.001882891205267866</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001325506947614027</v>
+        <v>0.001388701337206238</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001370923561656327</v>
+        <v>0.002071352503314093</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001618579994172915</v>
+        <v>0.002073072476121835</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001325506947614027</v>
+        <v>0.002061905121238362</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001663138323152336</v>
+        <v>0.002073211052267088</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001894102076021644</v>
+        <v>0.001354853934236641</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001535486956669389</v>
+        <v>0.002809629867671067</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001675319817560081</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002066518053629432</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002067230206986738</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002508318761175399</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002056062555714608</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002065509952535927</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002067229925343327</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002056062570460196</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002067229925343327</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.001840155788202855</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002067229925343327</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.003080893018728329</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001086480672234789</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001641740777196002</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001325506947614026</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001325506947614026</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001370923561656327</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001618579994172914</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001325506947614026</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001663138323152333</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001894102076021642</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001535486956669388</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.003035642613446465</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.001072378385128024</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.001626994768351343</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.001330844064627701</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.001330844064627701</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>0.003035642613446462</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001072378385128023</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.001626994768351342</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001330844064627699</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001330844064627699</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.001367552424329597</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.001617618615136985</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.001330844064627701</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.001742136570759756</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001871583980137912</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="H11" t="n">
+        <v>0.001617618615136984</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.001330844064627699</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.001742136570759755</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001871583980137906</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.001544232228649839</v>
       </c>
     </row>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001272671048087191</v>
+        <v>0.003000046640855439</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001504489438004689</v>
+        <v>0.001063309906323473</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001865272314112844</v>
+        <v>0.001628037285366946</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002206360593530624</v>
+        <v>0.001259298508376961</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002206360593530624</v>
+        <v>0.001259298508376962</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001832854843610416</v>
+        <v>0.00133036951174315</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00227153158694551</v>
+        <v>0.001628283108012761</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002206360593530624</v>
+        <v>0.001259298508376962</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00300913344478735</v>
+        <v>0.001525924509183351</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001368196355616862</v>
+        <v>0.001860559444945444</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001834435347385606</v>
+        <v>0.001541510589405859</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005082721716442563</v>
+        <v>0.003058426292486933</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004493174276809618</v>
+        <v>0.001090732810105916</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005082721716442563</v>
+        <v>0.001663978149488847</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000558709123968834</v>
+        <v>0.001289008386762089</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005587091239688341</v>
+        <v>0.001289008386762089</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005066415237220924</v>
+        <v>0.001361660798150901</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005082721716442563</v>
+        <v>0.001663978149488847</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004977232178697796</v>
+        <v>0.001289008386762089</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005082721716442563</v>
+        <v>0.001559024083612218</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005082721716442563</v>
+        <v>0.001900790551575557</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005082721716442563</v>
+        <v>0.001576326173851689</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001862801908050723</v>
+        <v>0.001272671048087208</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001241536308857192</v>
+        <v>0.00150448943800469</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001250822273255117</v>
+        <v>0.001865272314112859</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001170344724222022</v>
+        <v>0.002206360593530644</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001250221039470808</v>
+        <v>0.002206360593530644</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001861171260128561</v>
+        <v>0.001832854843610447</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001252366282337394</v>
+        <v>0.00227153158694553</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001852252954276237</v>
+        <v>0.002206360593530644</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001309086968268307</v>
+        <v>0.003009133444787359</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001255908043146675</v>
+        <v>0.001368196355616885</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001251184911614245</v>
+        <v>0.001834435347385609</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009540549283640264</v>
+        <v>0.0005082721716442733</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009533626686893623</v>
+        <v>0.0004493174276809566</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009540088195846485</v>
+        <v>0.0005082721716442733</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009563589291755681</v>
+        <v>0.0005587091239688341</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009563589291755681</v>
+        <v>0.0005587091239688343</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009524242804418567</v>
+        <v>0.0005066415237221073</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009540549283640264</v>
+        <v>0.0005082721716442733</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009435059745895402</v>
+        <v>0.0004977232178697804</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009540549283640264</v>
+        <v>0.0005082721716442733</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009540549283640264</v>
+        <v>0.0005082721716442733</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009540549283640264</v>
+        <v>0.0005082721716442733</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001335412697381461</v>
+        <v>0.001862801908050732</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002034506511816354</v>
+        <v>0.001241536308857204</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0021652388155424</v>
+        <v>0.001250822273255129</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001835346100547016</v>
+        <v>0.001170344724222031</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001354345272054469</v>
+        <v>0.001250221039470806</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002021090320283234</v>
+        <v>0.001861171260128567</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002022720968206401</v>
+        <v>0.0012523662823374</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002012172014430907</v>
+        <v>0.001852252954276238</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002022856043746069</v>
+        <v>0.001309086968268307</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001322645593405316</v>
+        <v>0.001255908043146678</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002740671928656719</v>
+        <v>0.001251184911614262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001538904196167072</v>
+        <v>0.000954054928364031</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00189364165134492</v>
+        <v>0.0009533626686893606</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001894334173023959</v>
+        <v>0.0009540088195846562</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002293943528781814</v>
+        <v>0.0009563589291755681</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001883784941305571</v>
+        <v>0.0009563589291755681</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001892703263097422</v>
+        <v>0.0009524242804418668</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001894333911019575</v>
+        <v>0.000954054928364031</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001883784957245098</v>
+        <v>0.0009435059745895375</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001894333911019575</v>
+        <v>0.000954054928364031</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001688396648552645</v>
+        <v>0.000954054928364031</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001894333911019575</v>
+        <v>0.000954054928364031</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003036952466198924</v>
+        <v>0.001335412697381462</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001067016536896037</v>
+        <v>0.002034506511816352</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001630746323504196</v>
+        <v>0.002165238815542403</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001247656417284948</v>
+        <v>0.001835346100547015</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001247656417284948</v>
+        <v>0.001354345272054469</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001330180178696245</v>
+        <v>0.002021090320283229</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001626321499504946</v>
+        <v>0.002022720968206404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001247656417284948</v>
+        <v>0.002012172014430906</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001501146130353985</v>
+        <v>0.002022856043746078</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001879789747578679</v>
+        <v>0.001322645593405324</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001548719660163809</v>
+        <v>0.002740671928656715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001538904196167078</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.001893641651344919</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.001894334173023953</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002293943528781814</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.001883784941305575</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001892703263097422</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.001894333911019589</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.001883784957245095</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.001894333911019589</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.001688396648552635</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.001894333911019589</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.003036952466198931</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001067016536896036</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001630746323504197</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001247656417284948</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001247656417284948</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001330180178696251</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001626321499504951</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001247656417284948</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001501146130353984</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001879789747578684</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.00154871966016381</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.002990275981461368</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0010525189264337</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.001612916698640386</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.001240483230483954</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.001240483230483954</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.001316045729568494</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.001611149212265461</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.001240483230483954</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>0.002990275981461371</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001052518926433698</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.00161291669864038</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001240483230483955</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001240483230483955</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001316045729568502</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.001611149212265465</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.001240483230483955</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.001499589856004763</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.001851004012201257</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.001528949537701127</v>
+      <c r="K11" t="n">
+        <v>0.001851004012201266</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001528949537701134</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001989668864084115</v>
+        <v>0.003055259704684347</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00165421478760185</v>
+        <v>0.001093632983212629</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003352436325151219</v>
+        <v>0.001655264985781212</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004242039362627834</v>
+        <v>0.001365993569278427</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004242039362627834</v>
+        <v>0.001365993569278427</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0050710009896756</v>
+        <v>0.001399826768212609</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02264136541858739</v>
+        <v>0.001674052342060883</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004242039362627834</v>
+        <v>0.001365993569278427</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006387593371240719</v>
+        <v>0.001807714089694589</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002968793521750268</v>
+        <v>0.001890983702025529</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01851446405359098</v>
+        <v>0.001824547125861701</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005373847077771923</v>
+        <v>0.003113796099883692</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000453494141052408</v>
+        <v>0.001121450851835783</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005373847077771923</v>
+        <v>0.001690072457528968</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005608458666992808</v>
+        <v>0.001395270715320418</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005608458666992808</v>
+        <v>0.001395270715320418</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005354929026662558</v>
+        <v>0.001428784324375742</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005373847077771923</v>
+        <v>0.001690072457528968</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005250921776133728</v>
+        <v>0.001395270715320418</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005373847077771923</v>
+        <v>0.001841836103409727</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005373847077771923</v>
+        <v>0.001929980226732656</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005373847077771923</v>
+        <v>0.00184752841109692</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001301848197388157</v>
+        <v>0.001989668864084114</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001279447417361456</v>
+        <v>0.001654214787601853</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001298430576870934</v>
+        <v>0.003352436325151224</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001206879990465831</v>
+        <v>0.004242039362627839</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00129258753283475</v>
+        <v>0.004242039362627839</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001299956392277212</v>
+        <v>0.005071000989675701</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002009940283754714</v>
+        <v>0.02264136541858737</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001289555667224336</v>
+        <v>0.004242039362627839</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001356102278114272</v>
+        <v>0.006387593371240741</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001291909705385692</v>
+        <v>0.002968793521750242</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001304444433188649</v>
+        <v>0.01851446405359099</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001031947501813707</v>
+        <v>0.0005373847077771962</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001031139944799111</v>
+        <v>0.0004534941410524114</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001031900357765485</v>
+        <v>0.0005373847077771962</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001034608635975757</v>
+        <v>0.0005608458666992802</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001034608635975757</v>
+        <v>0.0005608458666992819</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001030055696702746</v>
+        <v>0.0005354929026662394</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001031947501813707</v>
+        <v>0.0005373847077771962</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001019654971649891</v>
+        <v>0.0005250921776133741</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001031947501813707</v>
+        <v>0.0005373847077771962</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001031947501813707</v>
+        <v>0.0005373847077771962</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001031947501813707</v>
+        <v>0.0005373847077771962</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001453897005411121</v>
+        <v>0.001301848197388159</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002226259235413475</v>
+        <v>0.001279447417361465</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002369887183261079</v>
+        <v>0.001298430576870946</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002005743860452015</v>
+        <v>0.001206879990465821</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001474601984809173</v>
+        <v>0.00129258753283475</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002210679350765188</v>
+        <v>0.001299956392277203</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002212571155875337</v>
+        <v>0.002009940283754705</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002200278625712335</v>
+        <v>0.001289555667224335</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002212720256841704</v>
+        <v>0.001356102278114285</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001439804243583451</v>
+        <v>0.001291909705385656</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003005069745112906</v>
+        <v>0.001304444433188648</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001916070147012604</v>
+        <v>0.001031947501813714</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002373294427727712</v>
+        <v>0.001031139944799112</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002374102098424531</v>
+        <v>0.001031900357765495</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002890368251455794</v>
+        <v>0.001034608635975758</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002361809186748306</v>
+        <v>0.001034608635975758</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002372210179631352</v>
+        <v>0.001030055696702757</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002374101984742315</v>
+        <v>0.001031947501813714</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002361809454578491</v>
+        <v>0.00101965497164989</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002374101984742315</v>
+        <v>0.001031947501813714</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002108716586947007</v>
+        <v>0.001031947501813714</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002374101984742315</v>
+        <v>0.001031947501813714</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0030777900700896</v>
+        <v>0.00145389700541112</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001096216890038797</v>
+        <v>0.002226259235413477</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001624835413969982</v>
+        <v>0.002369887183261074</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001310101757923876</v>
+        <v>0.002005743860452019</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001310101757923876</v>
+        <v>0.001474601984809174</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001326920745661852</v>
+        <v>0.002210679350765203</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001239812793858535</v>
+        <v>0.002212571155875329</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001310101757923876</v>
+        <v>0.002200278625712337</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001713481909249921</v>
+        <v>0.002212720256841713</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001873860645366791</v>
+        <v>0.001439804243583446</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001488713541348293</v>
+        <v>0.003005069745112923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001916070147012602</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002373294427727713</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002374102098424543</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002890368251455799</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002361809186748308</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.00237221017963136</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002374101984742316</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002361809454578492</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002374101984742316</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002108716586947013</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002374101984742316</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.003077790070089601</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001096216890038799</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001624835413969981</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001310101757923875</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001310101757923875</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001326920745661854</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001239812793858537</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001310101757923875</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001713481909249918</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001873860645366795</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001488713541348293</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.003038876846383622</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.001082151450179136</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.001625581923063749</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B11" t="n">
+        <v>0.003038876846383626</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001082151450179137</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.001625581923063748</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.001327241422245636</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.001327241422245636</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.001353478515277829</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.001469182760198419</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.001353478515277827</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.001469182760198422</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.001327241422245636</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.001749312522311332</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001865449113661565</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.001661285216650932</v>
+      <c r="J11" t="n">
+        <v>0.00174931252231133</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001865449113661569</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001661285216650933</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001524705120260518</v>
+        <v>0.002848878820926524</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00161272975205266</v>
+        <v>0.001084869131481881</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002001222502615627</v>
+        <v>0.001645338312279892</v>
       </c>
       <c r="E2" t="n">
-        <v>0.003048136734288661</v>
+        <v>0.001363800904377265</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003048136734288661</v>
+        <v>0.001363800904377265</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002083255916133472</v>
+        <v>0.001374430819393795</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002474129315241044</v>
+        <v>0.001645638438595235</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003048136734288661</v>
+        <v>0.001363800904377265</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003529587174409709</v>
+        <v>0.001828258033283222</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001886615949083763</v>
+        <v>0.001891393365730853</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002008448644312226</v>
+        <v>0.001580264338228918</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000519377465685724</v>
+        <v>0.002904411605626214</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004504955006404718</v>
+        <v>0.001112355376542723</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000519377465685724</v>
+        <v>0.00168123900699675</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0006020879298062663</v>
+        <v>0.001394019594381718</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0006020879298062663</v>
+        <v>0.001394019594381718</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005176935956037459</v>
+        <v>0.00140597587193954</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000519377465685724</v>
+        <v>0.00168123900699675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005084366207859404</v>
+        <v>0.001394019594381718</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000519377465685724</v>
+        <v>0.001865421660667789</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000519377465685724</v>
+        <v>0.00193134916831365</v>
       </c>
       <c r="L3" t="n">
-        <v>0.000519377465685724</v>
+        <v>0.00161536018346371</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001880208060719207</v>
+        <v>0.001524705120260514</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001247786846619174</v>
+        <v>0.001612729752052672</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001261773330617103</v>
+        <v>0.002001222502615646</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001184423208807081</v>
+        <v>0.003048136734288679</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001260982830474868</v>
+        <v>0.003048136734288679</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001262699605984273</v>
+        <v>0.002083255916133636</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001916503182607728</v>
+        <v>0.002474129315241053</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001869267215819423</v>
+        <v>0.003048136734288679</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001317824356830224</v>
+        <v>0.003529587174409718</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001262540932643117</v>
+        <v>0.001886615949083772</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001260524922964624</v>
+        <v>0.002008448644312238</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009775627956521607</v>
+        <v>0.0005193774656857363</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009768934444054096</v>
+        <v>0.0004504955006404899</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009775180187146621</v>
+        <v>0.0005193774656857363</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009859697406751887</v>
+        <v>0.0006020879298062718</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009859697406751887</v>
+        <v>0.0006020879298062718</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009758789255701809</v>
+        <v>0.0005176935956037657</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009775627956521607</v>
+        <v>0.0005193774656857363</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009666219507523763</v>
+        <v>0.0005084366207859445</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009775627956521607</v>
+        <v>0.0005193774656857356</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009775627956521607</v>
+        <v>0.0005193774656857363</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009775627956521607</v>
+        <v>0.0005193774656857363</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001365441873708449</v>
+        <v>0.001880208060719216</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002087154423555933</v>
+        <v>0.001247786846619205</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00221505716089141</v>
+        <v>0.001261773330617113</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001882444596188152</v>
+        <v>0.001184423208807101</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001388375800649547</v>
+        <v>0.001260982830474888</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002067456767888934</v>
+        <v>0.001262699605984277</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002069140637970823</v>
+        <v>0.00191650318260776</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002058199793071128</v>
+        <v>0.001869267215819434</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002069278934654595</v>
+        <v>0.001317824356830233</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001352370307908132</v>
+        <v>0.001262540932643135</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002804212839312529</v>
+        <v>0.001260524922964632</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001667082721721333</v>
+        <v>0.000977562795652173</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002056120791058413</v>
+        <v>0.000976893444405415</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002056790419951991</v>
+        <v>0.0009775180187146762</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002495563648454864</v>
+        <v>0.000985969740675203</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002045849297276373</v>
+        <v>0.000985969740675203</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002055106272223189</v>
+        <v>0.0009758789255701969</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002056790142305165</v>
+        <v>0.000977562795652173</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002045849297405379</v>
+        <v>0.0009666219507523909</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002056790142305165</v>
+        <v>0.000977562795652173</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001566078865302441</v>
+        <v>0.000977562795652173</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002056790142305165</v>
+        <v>0.000977562795652173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002877167970514394</v>
+        <v>0.001365441873708458</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001086239210944976</v>
+        <v>0.002087154423555941</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001644853070997256</v>
+        <v>0.002215057160891429</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001332490321174119</v>
+        <v>0.001882444596188159</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001332490321174119</v>
+        <v>0.00138837580064956</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001368724561286139</v>
+        <v>0.002067456767888949</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001639370777626112</v>
+        <v>0.002069140637970824</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001332490321174119</v>
+        <v>0.002058199793071137</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001795644537564722</v>
+        <v>0.002069278934654607</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001897914903203674</v>
+        <v>0.001352370307908148</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001584229226403065</v>
+        <v>0.002804212839312539</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001667082721721367</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002056120791058427</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002056790419952013</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002495563648454887</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002045849297276392</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002055106272223203</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002056790142305181</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002045849297405397</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002056790142305181</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.001566078865302481</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002056790142305181</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.002877167970514401</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001086239210944977</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001644853070997259</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001332490321174119</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001332490321174119</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001368724561286141</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001639370777626104</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001332490321174119</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001795644537564722</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001897914903203666</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001584229226403064</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.002836482880130319</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.001072986192907625</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.001628782595445027</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B11" t="n">
+        <v>0.00283648288013033</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001072986192907624</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.00162878259544503</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.001335804888985647</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.001335804888985647</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.001357481354333611</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G11" t="n">
+        <v>0.001357481354333612</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.001626588260805463</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>0.001335804888985647</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.001796509219904829</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001876180668557137</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.001566099653557854</v>
+      <c r="J11" t="n">
+        <v>0.00179650921990483</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001876180668557138</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001566099653557852</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001351985440433208</v>
+        <v>0.002288729392077066</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001519534855004753</v>
+        <v>0.001063471621314897</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001808870791622344</v>
+        <v>0.001628868815473619</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002180721129158538</v>
+        <v>0.001261892004831579</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002180721129158538</v>
+        <v>0.001261892004831579</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001803384491319209</v>
+        <v>0.001269425208785534</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002209535247163102</v>
+        <v>0.001629115415057931</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002180721129158538</v>
+        <v>0.001261892004831579</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0029737855297031</v>
+        <v>0.001528859668659549</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00164543302086334</v>
+        <v>0.001863823577271347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00183821614735471</v>
+        <v>0.001543895213433911</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005093152630714564</v>
+        <v>0.002335678801086225</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004490719210745894</v>
+        <v>0.001090852956974034</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005093152630714564</v>
+        <v>0.001664862508814127</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005667003786756877</v>
+        <v>0.001291645613637825</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005667003786756879</v>
+        <v>0.001291645613637825</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005077261408004383</v>
+        <v>0.001299753988189627</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005093152630714564</v>
+        <v>0.001664862508814127</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004990403614343898</v>
+        <v>0.001291645613637825</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005093152630714564</v>
+        <v>0.00156201882069751</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005093152630714564</v>
+        <v>0.001903752624507854</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005093152630714564</v>
+        <v>0.001578717692433439</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001867723057667465</v>
+        <v>0.001351985440433205</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001244382705987862</v>
+        <v>0.001519534855004754</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001253621894354371</v>
+        <v>0.001808870791622345</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001174360187256443</v>
+        <v>0.002180721129158539</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001254014078265516</v>
+        <v>0.002180721129158539</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001257139831793137</v>
+        <v>0.001803384491319259</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001902114566602445</v>
+        <v>0.002209535247163105</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00124845405242709</v>
+        <v>0.002180721129158539</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001871951468273289</v>
+        <v>0.002973785529703105</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001259791736337682</v>
+        <v>0.001645433020863332</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001254241630889799</v>
+        <v>0.001838216147354713</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009544484692148485</v>
+        <v>0.0005093152630714521</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009537643503437221</v>
+        <v>0.0004490719210745913</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009544025926442755</v>
+        <v>0.0005093152630714521</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009590070891020929</v>
+        <v>0.0005667003786756875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009590070891020929</v>
+        <v>0.0005667003786756877</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009528593469438361</v>
+        <v>0.0005077261408004356</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009544484692148485</v>
+        <v>0.0005093152630714521</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000944173567577784</v>
+        <v>0.000499040361434389</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009544484692148485</v>
+        <v>0.0005093152630714521</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009544484692148485</v>
+        <v>0.0005093152630714521</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009544484692148485</v>
+        <v>0.0005093152630714521</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001333824096188589</v>
+        <v>0.001867723057667457</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002033881792289423</v>
+        <v>0.001244382705987862</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002162518808837323</v>
+        <v>0.001253621894354363</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001835043321118599</v>
+        <v>0.001174360187256441</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001354182384398518</v>
+        <v>0.001254014078265518</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002018606151598935</v>
+        <v>0.001257139831793137</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002020195273870785</v>
+        <v>0.00190211456660244</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002009920372232884</v>
+        <v>0.001248454052427093</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002020330165219213</v>
+        <v>0.001871951468273286</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001321074399201315</v>
+        <v>0.001259791736337682</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002737167362150783</v>
+        <v>0.001254241630889801</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001539017766680618</v>
+        <v>0.0009544484692148481</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00189382623285629</v>
+        <v>0.0009537643503437227</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001894510614637809</v>
+        <v>0.0009544025926442651</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002294466578953343</v>
+        <v>0.0009590070891020939</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001884235438659702</v>
+        <v>0.0009590070891020939</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001892921229456401</v>
+        <v>0.0009528593469438319</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001894510351727421</v>
+        <v>0.0009544484692148481</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001884235450090352</v>
+        <v>0.000944173567577786</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001894510351727421</v>
+        <v>0.0009544484692148481</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001680180038977159</v>
+        <v>0.0009544484692148481</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001894510351727421</v>
+        <v>0.0009544484692148481</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002312326340404222</v>
+        <v>0.001333824096188584</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001066783208211797</v>
+        <v>0.002033881792289422</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00163299991935012</v>
+        <v>0.002162518808837321</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001250912609171555</v>
+        <v>0.0018350433211186</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001250912609171555</v>
+        <v>0.001354182384398518</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001268965901388587</v>
+        <v>0.002018606151598931</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0016285335883309</v>
+        <v>0.002020195273870782</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001250912609171555</v>
+        <v>0.002009920372232884</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001504953008585484</v>
+        <v>0.002020330165219212</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00187600897609845</v>
+        <v>0.001321074399201316</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001551025225737428</v>
+        <v>0.002737167362150779</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001539017766680616</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.001893826232856295</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.001894510614637814</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002294466578953348</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.001884235438659705</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001892921229456403</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.001894510351727418</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.001884235450090358</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.001894510351727418</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.001680180038977154</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.001894510351727418</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.00231232634040422</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001066783208211798</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001632999919350118</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001250912609171556</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001250912609171556</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001268965901388588</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001628533588330895</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001250912609171556</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001504953008585481</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001876008976098447</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001551025225737429</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.002278103948046881</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.002278103948046878</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.001052519808922341</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.001614371235727453</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.001614371235727451</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.001243358357991042</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.001243358357991042</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G11" t="n">
         <v>0.001255416531175253</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.001612585640464657</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="H11" t="n">
+        <v>0.001612585640464656</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.001243358357991042</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.001502894542290626</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001851200128831301</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.001531295052836577</v>
+      <c r="J11" t="n">
+        <v>0.001502894542290623</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001851200128831303</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001531295052836573</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02149815209962302</v>
+        <v>0.001674691181977803</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008282537020936077</v>
+        <v>0.001635885407422877</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02589074065730742</v>
+        <v>0.001678952016049202</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008282537020936077</v>
+        <v>0.001635885407422877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008282537020936077</v>
+        <v>0.001635885407422877</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02657078687345928</v>
+        <v>0.001675352271379892</v>
       </c>
       <c r="H2" t="n">
-        <v>0.06494450836581515</v>
+        <v>0.001714925570046</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008282537020936077</v>
+        <v>0.001635885407422877</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03306729572857029</v>
+        <v>0.001684891669121089</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01167892897750555</v>
+        <v>0.001663231379164648</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02826199552498331</v>
+        <v>0.001678609877135867</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006232923342840853</v>
+        <v>0.001688780060091367</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005379345641720642</v>
+        <v>0.001664704355435596</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006232923342840853</v>
+        <v>0.001688780060091367</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005554365248662359</v>
+        <v>0.001664704355435596</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005554365248662358</v>
+        <v>0.001664704355435596</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006209520726537881</v>
+        <v>0.001684993666621412</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006232923342840853</v>
+        <v>0.001688780060091367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000608231450789868</v>
+        <v>0.001664704355435596</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006232923342840853</v>
+        <v>0.001688780060091367</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006232923342840853</v>
+        <v>0.001688780060091367</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006232923342840853</v>
+        <v>0.001688780060091367</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001456060795465422</v>
+        <v>0.02149815209962288</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00140290008151517</v>
+        <v>0.008282537020936103</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00147016784701364</v>
+        <v>0.02589074065730746</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001318767497277539</v>
+        <v>0.008282537020936103</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00143586428477855</v>
+        <v>0.008282537020936103</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001453720533835125</v>
+        <v>0.0265707868734592</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002288106599076347</v>
+        <v>0.06494450836581528</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0022238588433467</v>
+        <v>0.008282537020936103</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00152178235679446</v>
+        <v>0.03306729572857028</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001433841667055761</v>
+        <v>0.01167892897750553</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001485372512057263</v>
+        <v>0.02826199552498324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001186791284202811</v>
+        <v>0.0006232923342840866</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001171730400708598</v>
+        <v>0.0005379345641720638</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001186737091859443</v>
+        <v>0.0006232923342840866</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001170881276883857</v>
+        <v>0.0005554365248662358</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001170881276883857</v>
+        <v>0.0005554365248662358</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001184451022572517</v>
+        <v>0.000620952072653788</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001186791284202811</v>
+        <v>0.0006232923342840866</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001171730400708598</v>
+        <v>0.0006082314507898683</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001186791284202811</v>
+        <v>0.0006232923342840866</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001186791284202811</v>
+        <v>0.0006232923342840866</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001186791284202811</v>
+        <v>0.0006232923342840866</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001672987301730448</v>
+        <v>0.00145606079546542</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002510473601360208</v>
+        <v>0.001402900081515156</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002703012542432668</v>
+        <v>0.001470167847013639</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002277199531484589</v>
+        <v>0.001318767497277539</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001684494927659528</v>
+        <v>0.001435864284778549</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002523771389396271</v>
+        <v>0.001453720533835123</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002526111651026588</v>
+        <v>0.002288106599076347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002511050767532351</v>
+        <v>0.002223858843346698</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002526279314274554</v>
+        <v>0.001521782356794457</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001657140078957756</v>
+        <v>0.001433841667055766</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003417271370844159</v>
+        <v>0.001485372512057259</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002535299791519627</v>
+        <v>0.001186791284202816</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003130041101644077</v>
+        <v>0.0011717304007086</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003145102096107118</v>
+        <v>0.001186737091859442</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003833738853453662</v>
+        <v>0.00117088127688386</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003130040181606336</v>
+        <v>0.00117088127688386</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003142761723507993</v>
+        <v>0.001184451022572519</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003145101985138289</v>
+        <v>0.001186791284202816</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003130041101644077</v>
+        <v>0.0011717304007086</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003145101985138289</v>
+        <v>0.001186791284202816</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002791780245951538</v>
+        <v>0.001186791284202816</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003145101985138289</v>
+        <v>0.001186791284202816</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00119387913528624</v>
+        <v>0.001672987301730452</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001482715483268434</v>
+        <v>0.002510473601360205</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001104896441990719</v>
+        <v>0.002703012542432674</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001482715483268434</v>
+        <v>0.002277199531484592</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001482715483268434</v>
+        <v>0.00168449492765953</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001099770999563816</v>
+        <v>0.002523771389396278</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003761844845537594</v>
+        <v>0.00252611165102659</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001482715483268434</v>
+        <v>0.002511050767532354</v>
       </c>
       <c r="J8" t="n">
-        <v>0.000985702107988953</v>
+        <v>0.002526279314274554</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001434361312563881</v>
+        <v>0.001657140078957758</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001120639873079838</v>
+        <v>0.003417271370844159</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.002535299791519625</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.003130041101644075</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.003145102096107117</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.00383373885345366</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.003130040181606333</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.003142761723507989</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.003145101985138288</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.003130041101644075</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.003145101985138288</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002791780245951533</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.003145101985138288</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.00119387913528624</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001482715483268435</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001104896441990717</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001482715483268435</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001482715483268435</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001099770999563816</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0003761844845537571</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001482715483268435</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0009857021079889533</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.00143436131256388</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001120639873079837</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.0014495096840358</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.001553079890622696</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.001413283109086719</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.001553079890622696</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.001553079890622696</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.001409074092874705</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.001117690400182482</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.001553079890622696</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.001364988960338</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001547470038255199</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0007736674192469522</v>
+      <c r="B11" t="n">
+        <v>0.001449509684035801</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001553079890622695</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.001413283109086718</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001553079890622695</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001553079890622695</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001409074092874703</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.001117690400182481</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.001553079890622695</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.001364988960337998</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001547470038255198</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0007736674192469515</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01591916405163625</v>
+        <v>0.001663534116357803</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008297120456490139</v>
+        <v>0.001628468402530586</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02315697403724735</v>
+        <v>0.001672392120006754</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008297120456490139</v>
+        <v>0.001628468402530586</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008297120456490139</v>
+        <v>0.001628468402530586</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02289319673558917</v>
+        <v>0.001668128350990147</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05064779858968816</v>
+        <v>0.001698467361643253</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008297120456490139</v>
+        <v>0.001628468402530586</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02283627544235487</v>
+        <v>0.001670115719701765</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01014298175341151</v>
+        <v>0.001657164140198603</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03025152024391805</v>
+        <v>0.001677271373266413</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006019098873092898</v>
+        <v>0.001682871993387849</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005341727468398136</v>
+        <v>0.001656315435051444</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006019098873092892</v>
+        <v>0.001682871993387849</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005496664394554847</v>
+        <v>0.001656315435051444</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005496664394554848</v>
+        <v>0.001656315435051444</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005997429630406915</v>
+        <v>0.001679537846706709</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006019098873092892</v>
+        <v>0.001682871993387849</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005879705766757378</v>
+        <v>0.001656315435051444</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006019098873092892</v>
+        <v>0.001682871993387849</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006019098873092892</v>
+        <v>0.001682871993387849</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006019098873092892</v>
+        <v>0.001682871993387849</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001394866545979313</v>
+        <v>0.01591916405163629</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001350302509308048</v>
+        <v>0.008297120456490163</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001408638453182823</v>
+        <v>0.02315697403724737</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001269990119080488</v>
+        <v>0.008297120456490163</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001377227204699872</v>
+        <v>0.008297120456490163</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001392699621710712</v>
+        <v>0.02289319673558919</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002157457592732589</v>
+        <v>0.05064779858968824</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002105218004650966</v>
+        <v>0.008297120456490163</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001455807952072549</v>
+        <v>0.02283627544235485</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001381160640048985</v>
+        <v>0.01014298175341151</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001416875773046248</v>
+        <v>0.030251520243918</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001118180129201021</v>
+        <v>0.0006019098873092911</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001104240818567465</v>
+        <v>0.0005341727468398129</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00111812944195425</v>
+        <v>0.0006019098873092908</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001103268199870019</v>
+        <v>0.0005496664394554835</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001103268199870019</v>
+        <v>0.000549666439455485</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001116013204932416</v>
+        <v>0.0005997429630406882</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001118180129201021</v>
+        <v>0.0006019098873092908</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001104240818567465</v>
+        <v>0.0005879705766757363</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001118180129201021</v>
+        <v>0.0006019098873092908</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001118180129201021</v>
+        <v>0.0006019098873092908</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001118180129201021</v>
+        <v>0.0006019098873092908</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001560978992079419</v>
+        <v>0.001394866545979313</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002327365810753722</v>
+        <v>0.001350302509308047</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002503973017718609</v>
+        <v>0.001408638453182821</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002113821805273941</v>
+        <v>0.001269990119080488</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001571247474363063</v>
+        <v>0.001377227204699872</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002339852311024251</v>
+        <v>0.001392699621710715</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002342019235292942</v>
+        <v>0.002157457592732592</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002328079924659301</v>
+        <v>0.002105218004650964</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00234217273195361</v>
+        <v>0.001455807952072551</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001546470768585227</v>
+        <v>0.001381160640048984</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003157881078736878</v>
+        <v>0.001416875773046248</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002201469283219402</v>
+        <v>0.001118180129201016</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002704611182042564</v>
+        <v>0.001104240818567464</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002718550669045792</v>
+        <v>0.001118129441954249</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003301311198702172</v>
+        <v>0.001103268199870018</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002704610466364548</v>
+        <v>0.001103268199870018</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002716383568407513</v>
+        <v>0.001116013204932418</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002718550492676119</v>
+        <v>0.001118180129201016</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002704611182042564</v>
+        <v>0.001104240818567464</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002718550492676119</v>
+        <v>0.001118180129201016</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002418951683363484</v>
+        <v>0.001118180129201016</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002718550492676119</v>
+        <v>0.001118180129201016</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00129988969010946</v>
+        <v>0.001560978992079417</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001457148861458596</v>
+        <v>0.002327365810753721</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001114540895966733</v>
+        <v>0.00250397301771861</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001457148861458596</v>
+        <v>0.002113821805273937</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001457148861458596</v>
+        <v>0.001571247474363062</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001133081466123368</v>
+        <v>0.00233985231102425</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0005890388339091203</v>
+        <v>0.002342019235292944</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001457148861458596</v>
+        <v>0.0023280799246593</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001166075341068717</v>
+        <v>0.002342172731953607</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00143368244017019</v>
+        <v>0.001546470768585225</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001022297789074907</v>
+        <v>0.003157881078736877</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.002201469283219402</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002704611182042565</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002718550669045795</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.003301311198702174</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002704610466364548</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002716383568407512</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002718550492676119</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002704611182042565</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002718550492676119</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002418951683363479</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002718550492676119</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.001299889690109458</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001457148861458596</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001114540895966732</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001457148861458596</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001457148861458596</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001133081466123368</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00058903883390912</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001457148861458596</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001166075341068716</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001433682440170188</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001022297789074906</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.001489275947873954</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.001489275947873952</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.00153784697683963</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.001413799659516404</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.0014137996595164</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.00153784697683963</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.00153784697683963</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.001419488956371568</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.001200769788240982</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.001419488956371569</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.00120076978824098</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.00153784697683963</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.001434971595963346</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001543782099364581</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0008335364482485067</v>
+      <c r="J11" t="n">
+        <v>0.001434971595963345</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001543782099364578</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0008335364482485032</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01333721076049514</v>
+        <v>0.00158805777651617</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01038669751186686</v>
+        <v>0.001518379033104947</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01873899559904821</v>
+        <v>0.001594930436634665</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01038669751186686</v>
+        <v>0.001518379033104947</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01038669751186686</v>
+        <v>0.001518379033104947</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01938602615277383</v>
+        <v>0.001592674674745456</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03480583887154076</v>
+        <v>0.001610348895063343</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01038669751186686</v>
+        <v>0.001518379033104947</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01468716370953079</v>
+        <v>0.001588113486957712</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008434056881918658</v>
+        <v>0.001582642037794597</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02019859024568573</v>
+        <v>0.001659839320819657</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006050029236764858</v>
+        <v>0.001608892571338377</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005478557994428885</v>
+        <v>0.001541637673418276</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006050029236764858</v>
+        <v>0.001608892571338377</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005627310570238819</v>
+        <v>0.001541637673418276</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005627310570238815</v>
+        <v>0.001541637673418276</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006029916272008196</v>
+        <v>0.001606560723422184</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006050029236764858</v>
+        <v>0.001608892571338377</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005920428185778004</v>
+        <v>0.001541637673418276</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006050029236764857</v>
+        <v>0.001608892571338377</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006050029236764858</v>
+        <v>0.001608892571338377</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006050029236764858</v>
+        <v>0.001608892571338377</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001399482088615796</v>
+        <v>0.01333721076049512</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00136669695865833</v>
+        <v>0.01038669751186687</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001405854083514814</v>
+        <v>0.0187389955990482</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001285841404285679</v>
+        <v>0.01038669751186687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001385723561380704</v>
+        <v>0.01038669751186687</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002110198185807541</v>
+        <v>0.01938602615277377</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002147954247572856</v>
+        <v>0.03480583887154075</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001386521983517115</v>
+        <v>0.01038669751186687</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002120082505843285</v>
+        <v>0.01468716370953078</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001389232761694324</v>
+        <v>0.008434056881918678</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001423330047875091</v>
+        <v>0.02019859024568584</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001111878984760478</v>
+        <v>0.0006050029236764805</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001098918879661796</v>
+        <v>0.000547855799442888</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001111827995376271</v>
+        <v>0.0006050029236764803</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001097962380500509</v>
+        <v>0.0005627310570238809</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001097962380500509</v>
+        <v>0.0005627310570238809</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001109867688284816</v>
+        <v>0.0006029916272008193</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001111878984760478</v>
+        <v>0.0006050029236764803</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001098918879661796</v>
+        <v>0.0005920428185777996</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001111878984760478</v>
+        <v>0.0006050029236764803</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001111878984760478</v>
+        <v>0.0006050029236764803</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001111878984760478</v>
+        <v>0.0006050029236764803</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001541863531616025</v>
+        <v>0.001399482088615799</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002293130612426939</v>
+        <v>0.001366696958658314</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002465404620069537</v>
+        <v>0.001405854083514812</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00208399123429468</v>
+        <v>0.001285841404285681</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001552610289999278</v>
+        <v>0.001385723561380705</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002304780470878076</v>
+        <v>0.002110198185807541</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002306791767353874</v>
+        <v>0.002147954247572857</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002293831662255057</v>
+        <v>0.001386521983517104</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002306942097547134</v>
+        <v>0.002120082505843283</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001527654596932288</v>
+        <v>0.001389232761694328</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003105823271728974</v>
+        <v>0.001423330047875091</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002024029151100405</v>
+        <v>0.001111878984760481</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002477351888214174</v>
+        <v>0.001098918879661797</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002490312236641939</v>
+        <v>0.001111827995376272</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003015431980035723</v>
+        <v>0.001097962380500509</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002477351375202205</v>
+        <v>0.001097962380500509</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00248830069683719</v>
+        <v>0.001109867688284818</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002490311993312849</v>
+        <v>0.001111878984760481</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002477351888214174</v>
+        <v>0.001098918879661797</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002490311993312849</v>
+        <v>0.001111878984760481</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002220145985644992</v>
+        <v>0.001111878984760481</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002490311993312849</v>
+        <v>0.001111878984760481</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001280754772468252</v>
+        <v>0.001541863531616031</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001284215205048903</v>
+        <v>0.002293130612426939</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001136965486193984</v>
+        <v>0.002465404620069546</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001284215205048903</v>
+        <v>0.002083991234294679</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001284215205048903</v>
+        <v>0.001552610289999278</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001135109567325026</v>
+        <v>0.002304780470878076</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0008287631832858293</v>
+        <v>0.002306791767353879</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001284215205048903</v>
+        <v>0.002293831662255057</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0012822038633839</v>
+        <v>0.002306942097547135</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001394507936832937</v>
+        <v>0.00152765459693229</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0001951469077670645</v>
+        <v>0.00310582327172898</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.002024029151100408</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002477351888214174</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002490312236641943</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.003015431980035723</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002477351375202204</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002488300696837197</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002490311993312858</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002477351888214174</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002490311993312858</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002220145985644996</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002490311993312858</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.00128075477246825</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001284215205048903</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001136965486193982</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001284215205048903</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001284215205048903</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001135109567325026</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.000828763183285827</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001284215205048903</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001282203863383899</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001394507936832936</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.0001951469077670664</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.001438754032317147</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.001438754032317146</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.001401250989640149</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.001380202108951578</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.001380202108951579</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.001401250989640149</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.001401250989640149</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.00137816289629556</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G11" t="n">
+        <v>0.001378162896295559</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.001255387537374586</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>0.001401250989640149</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>0.001439469083743283</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.001485096345891328</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.0008389956086939772</v>
+      <c r="K11" t="n">
+        <v>0.001485096345891327</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0008389956086939774</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.005187343549293049</v>
+        <v>0.001590331211135595</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004613266222669468</v>
+        <v>0.00157548156326935</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008244263837527022</v>
+        <v>0.001594227970909304</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004613266222669468</v>
+        <v>0.00157548156326935</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004613266222669468</v>
+        <v>0.00157548156326935</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0100414379597328</v>
+        <v>0.001594147511440631</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02074308381249164</v>
+        <v>0.001607224698884799</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004613266222669468</v>
+        <v>0.00157548156326935</v>
       </c>
       <c r="J2" t="n">
-        <v>0.018745311086297</v>
+        <v>0.00160408203701967</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00783528903722547</v>
+        <v>0.001593566989237195</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02647942371375323</v>
+        <v>0.001598348623842082</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005722000571758495</v>
+        <v>0.001622198850255689</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004978319400739504</v>
+        <v>0.001607881344197981</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005722000571758495</v>
+        <v>0.001622198850255689</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005143444761470439</v>
+        <v>0.001607881344197981</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000514344476147044</v>
+        <v>0.001607881344197981</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00057030437761263</v>
+        <v>0.00162045227726324</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005722000571758495</v>
+        <v>0.001622198850255689</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000559971944406782</v>
+        <v>0.001607881344197981</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005722000571758495</v>
+        <v>0.001622198850255689</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005722000571758495</v>
+        <v>0.001622198850255689</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005722000571758495</v>
+        <v>0.001622198850255689</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00203491487567786</v>
+        <v>0.005187343549293018</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001330739001071057</v>
+        <v>0.00461326622266947</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00205078657730269</v>
+        <v>0.008244263837527013</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001248575374899554</v>
+        <v>0.00461326622266947</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00134802904098501</v>
+        <v>0.00461326622266947</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002033019196114641</v>
+        <v>0.0100414379597328</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001367174081077922</v>
+        <v>0.02074308381249164</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002022686762908791</v>
+        <v>0.00461326622266947</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002050234509639446</v>
+        <v>0.01874531108629704</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001357525242374157</v>
+        <v>0.007835289037225465</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001369449153563509</v>
+        <v>0.02647942371375317</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001062070771351092</v>
+        <v>0.000572200057175849</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001049842658582023</v>
+        <v>0.0004978319400739511</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001062017375740189</v>
+        <v>0.000572200057175849</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001049059397443735</v>
+        <v>0.0005143444761470446</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001049059397443735</v>
+        <v>0.0005143444761470446</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001060175091787872</v>
+        <v>0.0005703043776126304</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001062070771351092</v>
+        <v>0.0005722000571758495</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001049842658582023</v>
+        <v>0.0005599719444067814</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001062070771351092</v>
+        <v>0.000572200057175849</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001062070771351092</v>
+        <v>0.000572200057175849</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001062070771351092</v>
+        <v>0.000572200057175849</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001483839799684129</v>
+        <v>0.002034914875677854</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002221862889404726</v>
+        <v>0.001330739001071051</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002390306630215988</v>
+        <v>0.002050786577302695</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002016572959973728</v>
+        <v>0.001248575374899554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001494975055810887</v>
+        <v>0.001348029040985011</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002232730503208086</v>
+        <v>0.002033019196114638</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002234626182771299</v>
+        <v>0.001367174081077924</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002222398070002237</v>
+        <v>0.002022686762908785</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002234773733707455</v>
+        <v>0.002050234509639448</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001469893557171095</v>
+        <v>0.001357525242374157</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003018885339551053</v>
+        <v>0.001369449153563507</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002082437475195535</v>
+        <v>0.001062070771351093</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002562536809277169</v>
+        <v>0.001049842658582025</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002574765145254504</v>
+        <v>0.001062017375740192</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003130672044569732</v>
+        <v>0.001049059397443737</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00256253648837878</v>
+        <v>0.001049059397443737</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002572869242483016</v>
+        <v>0.001060175091787875</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002574764922046234</v>
+        <v>0.001062070771351093</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002562536809277169</v>
+        <v>0.001049842658582025</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002574764922046234</v>
+        <v>0.001062070771351093</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002289508559703222</v>
+        <v>0.001062070771351093</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002574764922046234</v>
+        <v>0.001062070771351093</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001513439493713035</v>
+        <v>0.001483839799684131</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001513137872892453</v>
+        <v>0.002221862889404725</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001431868938006562</v>
+        <v>0.002390306630215988</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001513137872892453</v>
+        <v>0.002016572959973729</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001513137872892453</v>
+        <v>0.00149497505581089</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001396204300876791</v>
+        <v>0.002232730503208088</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001168218181385847</v>
+        <v>0.002234626182771302</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001513137872892453</v>
+        <v>0.002222398070002237</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001228373366273789</v>
+        <v>0.002234773733707458</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001445813242937206</v>
+        <v>0.001469893557171099</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001093554357639187</v>
+        <v>0.003018885339551052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.002082437475195528</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002562536809277165</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002574765145254512</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.003130672044569728</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002562536488378773</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.00257286924248301</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002574764922046237</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002562536809277165</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002574764922046237</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002289508559703223</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002574764922046237</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.001513439493713036</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001513137872892455</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001431868938006563</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001513137872892455</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001513137872892455</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001396204300876792</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001168218181385847</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001513137872892455</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001228373366273788</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001445813242937208</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001093554357639187</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.001540845357313182</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.001532372981895805</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.00150762725429051</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.001532372981895805</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.001532372981895805</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="C11" t="n">
+        <v>0.001532372981895806</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.001507627254290511</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001532372981895806</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001532372981895806</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.001492113967548897</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>0.001400662047798471</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.001532372981895805</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.001424890186760557</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001513310975799708</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.00137022963277795</v>
+      <c r="I11" t="n">
+        <v>0.001532372981895806</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.001424890186760558</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001513310975799709</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001370229632777952</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,320 +7651,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004137940365520056</v>
+        <v>0.001580773077917834</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00577318798874486</v>
+        <v>0.001569735344244404</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004848120988364359</v>
+        <v>0.001581954364337412</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00577318798874486</v>
+        <v>0.001569735344244404</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00577318798874486</v>
+        <v>0.001569735344244404</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00649926264886888</v>
+        <v>0.00158299064691104</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003634294347394239</v>
+        <v>0.001579942781944388</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00577318798874486</v>
+        <v>0.001569735344244404</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01190527455733317</v>
+        <v>0.001589924589936588</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007124720356414618</v>
+        <v>0.001584790786498489</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004495340639666384</v>
+        <v>0.001580883533346259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005522906108056919</v>
+        <v>0.001613450039987075</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004981557323654759</v>
+        <v>0.001600021808561117</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005522906108056919</v>
+        <v>0.001613450039987075</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005123977484262901</v>
+        <v>0.001600021808561117</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005123977484262909</v>
+        <v>0.001600021808561117</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005506546682999256</v>
+        <v>0.001612576304661864</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005522906108056919</v>
+        <v>0.001613450039987075</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005417339262405146</v>
+        <v>0.001600021808561117</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005522906108056919</v>
+        <v>0.001613450039987075</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005522906108056919</v>
+        <v>0.001613450039987075</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005522906108056919</v>
+        <v>0.001613450039987075</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001915435718661182</v>
+        <v>0.004137940365520056</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001286204418358137</v>
+        <v>0.005773187988744853</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001306471111450375</v>
+        <v>0.004848120988364353</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001207548733553994</v>
+        <v>0.005773187988744853</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001295387423995578</v>
+        <v>0.005773187988744853</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001913799776155414</v>
+        <v>0.006499262648868814</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001945161264417999</v>
+        <v>0.003634294347394238</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001904879034096001</v>
+        <v>0.005773187988744853</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001363036131065581</v>
+        <v>0.01190527455733313</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001310090283737402</v>
+        <v>0.007124720356414613</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001302718143942571</v>
+        <v>0.004495340639666378</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009954001546044428</v>
+        <v>0.0005522906108056931</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000984843470039266</v>
+        <v>0.0004981557323654756</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009953498940284571</v>
+        <v>0.0005522906108056931</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009841642444921319</v>
+        <v>0.0005123977484262898</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009841642444921319</v>
+        <v>0.0005123977484262901</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009937642120986764</v>
+        <v>0.0005506546682999266</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009954001546044428</v>
+        <v>0.0005522906108056931</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000984843470039266</v>
+        <v>0.0005417339262405143</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009954001546044428</v>
+        <v>0.0005522906108056931</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009954001546044428</v>
+        <v>0.0005522906108056931</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009954001546044428</v>
+        <v>0.0005522906108056931</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001371803917156486</v>
+        <v>0.00191543571866118</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002038025480667429</v>
+        <v>0.001286204418358132</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002189465164513015</v>
+        <v>0.001306471111450374</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001852844361544809</v>
+        <v>0.001207548733553994</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001382339253678537</v>
+        <v>0.001295387423995578</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002047400621026658</v>
+        <v>0.001913799776155414</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002049036563532329</v>
+        <v>0.001945161264417997</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002038479878967247</v>
+        <v>0.001904879034096001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002049169659067681</v>
+        <v>0.00136303613106558</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00135922397306445</v>
+        <v>0.001310090283737401</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002756462691867825</v>
+        <v>0.001302718143942568</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001792506092287998</v>
+        <v>0.0009954001546044423</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00219306431271224</v>
+        <v>0.0009848434700392645</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002203621333037974</v>
+        <v>0.0009953498940284567</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00266748244149626</v>
+        <v>0.0009841642444921314</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002193064266270347</v>
+        <v>0.0009841642444921314</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002201985054771648</v>
+        <v>0.0009937642120986757</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002203620997277412</v>
+        <v>0.0009954001546044423</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00219306431271224</v>
+        <v>0.0009848434700392645</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002203620997277412</v>
+        <v>0.0009954001546044423</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001965419547974084</v>
+        <v>0.0009954001546044423</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002203620997277412</v>
+        <v>0.0009954001546044423</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001523912854065532</v>
+        <v>0.001371803917156486</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001463890166263027</v>
+        <v>0.002038025480667427</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001499216746221308</v>
+        <v>0.002189465164513014</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001463890166263027</v>
+        <v>0.001852844361544807</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001463890166263027</v>
+        <v>0.001382339253678535</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00145900414969745</v>
+        <v>0.002047400621026657</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001542706346285024</v>
+        <v>0.002049036563532326</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001463890166263027</v>
+        <v>0.002038479878967243</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001334331740674527</v>
+        <v>0.002049169659067677</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001439894061939715</v>
+        <v>0.001359223973064449</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001523020373382488</v>
+        <v>0.002756462691867824</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001792506092287996</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002193064312712229</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002203621333037965</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002667482441496252</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.00219306426627034</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002201985054771638</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002203620997277409</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002193064312712229</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002203620997277409</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.00196541954797408</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002203620997277409</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.001523912854065532</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001463890166263027</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001499216746221309</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001463890166263027</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001463890166263027</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001459004149697451</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001542706346285025</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001463890166263027</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001334331740674528</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001439894061939715</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001523020373382488</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>0.001540033372985449</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.001507795013172969</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.00152997785163408</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.001507795013172969</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.001507795013172969</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="C11" t="n">
+        <v>0.001507795013172968</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.001529977851634081</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001507795013172968</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001507795013172968</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.001513114826996811</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.001547754175863181</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.001507795013172969</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.001462924874252138</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.001505822263396853</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="H11" t="n">
+        <v>0.001547754175863182</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.001507795013172968</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.001462924874252139</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.001505822263396852</v>
+      </c>
+      <c r="L11" t="n">
         <v>0.001539737746858926</v>
       </c>
     </row>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00608913677361687</v>
+        <v>0.001518623151701658</v>
       </c>
       <c r="C2" t="n">
-        <v>0.006431420581326007</v>
+        <v>0.001457747301494414</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003681293075724239</v>
+        <v>0.001515711114040047</v>
       </c>
       <c r="E2" t="n">
-        <v>0.006431420581326007</v>
+        <v>0.001457747301494414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006431420581326007</v>
+        <v>0.001457747301494414</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005978763456169699</v>
+        <v>0.001517853176407214</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003376897052341075</v>
+        <v>0.001514957738858303</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006431420581326007</v>
+        <v>0.001457747301494414</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00984695904113346</v>
+        <v>0.001522704093768306</v>
       </c>
       <c r="K2" t="n">
-        <v>0.006140278825134366</v>
+        <v>0.001519086582336083</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005266655142565789</v>
+        <v>0.00151714167424323</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005545254802766191</v>
+        <v>0.001547841705356973</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005071065976565242</v>
+        <v>0.001485501129515958</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005545254802766192</v>
+        <v>0.001547841705356973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005209203880444529</v>
+        <v>0.001485501129515958</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000520920388044453</v>
+        <v>0.001485501129515958</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005528755562728775</v>
+        <v>0.001547218637058086</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005545254802766192</v>
+        <v>0.001547841705356973</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005438624263190383</v>
+        <v>0.001485501129515958</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005545254802766191</v>
+        <v>0.001547841705356973</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005545254802766192</v>
+        <v>0.001547841705356973</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005545254802766192</v>
+        <v>0.001547841705356973</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001316505395472502</v>
+        <v>0.006089136773616867</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001296786578075659</v>
+        <v>0.006431420581326009</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001308281970240844</v>
+        <v>0.003681293075724234</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001217453381181572</v>
+        <v>0.006431420581326009</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001303811452644097</v>
+        <v>0.006431420581326009</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00131485547146876</v>
+        <v>0.005978763456169742</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001954017510938204</v>
+        <v>0.003376897052341074</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00130584234151492</v>
+        <v>0.006431420581326009</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001370266468530422</v>
+        <v>0.009846959041133471</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001318547657693268</v>
+        <v>0.006140278825134375</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001314454838232773</v>
+        <v>0.00526665514256579</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009958343561052895</v>
+        <v>0.0005545254802766176</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009851713021477063</v>
+        <v>0.0005071065976565244</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009957838582419954</v>
+        <v>0.0005545254802766177</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009844818862824534</v>
+        <v>0.0005209203880444526</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009844818862824534</v>
+        <v>0.0005209203880444527</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009941844321015453</v>
+        <v>0.0005528755562728758</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009958343561052895</v>
+        <v>0.0005545254802766177</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009851713021477063</v>
+        <v>0.0005438624263190375</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009958343561052895</v>
+        <v>0.0005545254802766177</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009958343561052895</v>
+        <v>0.0005545254802766177</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009958343561052895</v>
+        <v>0.0005545254802766177</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001369151725952327</v>
+        <v>0.001316505395472503</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002031871808739754</v>
+        <v>0.001296786578075663</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002182725562383603</v>
+        <v>0.001308281970240844</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001847617158453844</v>
+        <v>0.001217453381181581</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001379467442973388</v>
+        <v>0.001303811452644096</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002041349026639381</v>
+        <v>0.001314855471468759</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002042998950643005</v>
+        <v>0.001954017510938201</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002032335896685541</v>
+        <v>0.00130584234151492</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002043131380850399</v>
+        <v>0.001370266468530418</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00135663466780577</v>
+        <v>0.001318547657693263</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002746888722948144</v>
+        <v>0.001314454838232771</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001683065014342441</v>
+        <v>0.0009958343561052877</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00205251036825252</v>
+        <v>0.0009851713021477057</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002063173729495789</v>
+        <v>0.0009957838582419936</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002491147638687201</v>
+        <v>0.0009844818862824541</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002052510327911341</v>
+        <v>0.0009844818862824541</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002061523498206358</v>
+        <v>0.0009941844321015448</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002063173422210099</v>
+        <v>0.0009958343561052877</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00205251036825252</v>
+        <v>0.0009851713021477057</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002063173422210099</v>
+        <v>0.0009958343561052877</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001834001974844166</v>
+        <v>0.0009958343561052877</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002063173422210099</v>
+        <v>0.0009958343561052877</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001407454262855078</v>
+        <v>0.001369151725952327</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001334246484216005</v>
+        <v>0.002031871808739751</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001468535487086764</v>
+        <v>0.0021827255623836</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001334246484216005</v>
+        <v>0.001847617158453843</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001334246484216005</v>
+        <v>0.001379467442973388</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001410585542019513</v>
+        <v>0.00204134902663938</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001485508092998582</v>
+        <v>0.002042998950642996</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001334246484216005</v>
+        <v>0.002032335896685545</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001323713362514495</v>
+        <v>0.002043131380850392</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001397907533939274</v>
+        <v>0.001356634667805769</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001490520306891593</v>
+        <v>0.00274688872294814</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001683065014342444</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.00205251036825252</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.00206317372949579</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002491147638687206</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002052510327911345</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002061523498206359</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002063173422210102</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.00205251036825252</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002063173422210098</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.001834001974844166</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002063173422210098</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.001407454262855077</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001334246484216006</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001468535487086764</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001334246484216006</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001334246484216006</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001410585542019513</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.00148550809299858</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001334246484216006</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001323713362514493</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001397907533939275</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.001490520306891593</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.001454746417975064</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.001454746417975062</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.001388925955862978</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D11" t="n">
         <v>0.001479626531993179</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>0.001388925955862978</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.001388925955862978</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.001455684682740824</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.001486595746589798</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.001455684682740822</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.001486595746589796</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.001388925955862978</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.00142072498352033</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>0.001420724983520328</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.001450866056529175</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.001488622477601316</v>
+      <c r="L11" t="n">
+        <v>0.001488622477601315</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0138111699655613</v>
+        <v>0.001647666386453372</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007159127332110423</v>
+        <v>0.001616401848355964</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02382311419293671</v>
+        <v>0.001659420444983844</v>
       </c>
       <c r="E2" t="n">
-        <v>0.007159127332110423</v>
+        <v>0.001616401848355964</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007159127332110423</v>
+        <v>0.001616401848355964</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0227716633941211</v>
+        <v>0.001653881025524675</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05838325797260724</v>
+        <v>0.001695130031223311</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007159127332110423</v>
+        <v>0.001616401848355964</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02234622276602953</v>
+        <v>0.001655335107533751</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01108606348175525</v>
+        <v>0.001644454713533119</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02052356817175122</v>
+        <v>0.001723248830364438</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0006100827189552195</v>
+        <v>0.001670179038849348</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0005263679082691731</v>
+        <v>0.001646273393428794</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0006100827189552194</v>
+        <v>0.001670179038849348</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005436830890058632</v>
+        <v>0.001646273393428794</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005436830890058612</v>
+        <v>0.001646273393428794</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0006078152841882661</v>
+        <v>0.001666726254064004</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0006100827189552195</v>
+        <v>0.001670179038849348</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005954848600564993</v>
+        <v>0.001646273393428794</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006100827189552194</v>
+        <v>0.001670179038849348</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0006100827189552194</v>
+        <v>0.001670179038849348</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006100827189552194</v>
+        <v>0.001670179038849348</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00143103040134797</v>
+        <v>0.01381116996556128</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001381201927471982</v>
+        <v>0.007159127332110376</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001447832013063927</v>
+        <v>0.02382311419293675</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001297899083021376</v>
+        <v>0.007159127332110376</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001411545636643903</v>
+        <v>0.007159127332110376</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002187308139397613</v>
+        <v>0.02277166339412115</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002244395206734254</v>
+        <v>0.05838325797260727</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002174977715265848</v>
+        <v>0.007159127332110376</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002207183296893006</v>
+        <v>0.02234622276602952</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001412975229415611</v>
+        <v>0.01108606348175526</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001456299566757834</v>
+        <v>0.02052356817175135</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001153586469458367</v>
+        <v>0.0006100827189552198</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001138988610559647</v>
+        <v>0.0005263679082691724</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001153532553970152</v>
+        <v>0.0006100827189552198</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001138114876032634</v>
+        <v>0.0005436830890058619</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001138114876032634</v>
+        <v>0.000543683089005862</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001151319034691411</v>
+        <v>0.0006078152841882653</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001153586469458367</v>
+        <v>0.0006100827189552198</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001138988610559647</v>
+        <v>0.0005954848600564981</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001153586469458367</v>
+        <v>0.0006100827189552198</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001153586469458367</v>
+        <v>0.0006100827189552198</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001153586469458367</v>
+        <v>0.0006100827189552198</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001623439288574884</v>
+        <v>0.001431030401347973</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002434525372325217</v>
+        <v>0.001381201927471979</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002621066186009287</v>
+        <v>0.001447832013063929</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002208593323070346</v>
+        <v>0.00129789908302137</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001634544492456734</v>
+        <v>0.001411545636643902</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002447462088340204</v>
+        <v>0.002187308139397611</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002449729523107245</v>
+        <v>0.002244395206734259</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002435131664208435</v>
+        <v>0.002174977715265844</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002449891912688176</v>
+        <v>0.002207183296893004</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001608090523260056</v>
+        <v>0.00141297522941561</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003312858766226881</v>
+        <v>0.001456299566757838</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002437538994546128</v>
+        <v>0.001153586469458368</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003007730262137942</v>
+        <v>0.001138988610559646</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003022328165099199</v>
+        <v>0.001153532553970153</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003682563440032241</v>
+        <v>0.001138114876032635</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003007729370636012</v>
+        <v>0.001138114876032635</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003020060686269697</v>
+        <v>0.001151319034691414</v>
       </c>
       <c r="H7" t="n">
-        <v>0.003022328121036669</v>
+        <v>0.001153586469458368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003007730262137942</v>
+        <v>0.001138988610559646</v>
       </c>
       <c r="J7" t="n">
-        <v>0.003022328121036669</v>
+        <v>0.001153586469458368</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002683499023037316</v>
+        <v>0.001153586469458368</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003022328121036669</v>
+        <v>0.001153586469458368</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001356097071595938</v>
+        <v>0.001623439288574883</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001490835920311272</v>
+        <v>0.00243452537232522</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001110041920085204</v>
+        <v>0.002621066186009296</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001490835920311272</v>
+        <v>0.002208593323070347</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001490835920311272</v>
+        <v>0.001634544492456735</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001152560015653367</v>
+        <v>0.002447462088340203</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0003863151390427943</v>
+        <v>0.002449729523107246</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001490835920311272</v>
+        <v>0.002435131664208439</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001199130670077777</v>
+        <v>0.00244989191268817</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001423688257160599</v>
+        <v>0.001608090523260056</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0001984465655914466</v>
+        <v>0.003312858766226885</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00243753899454613</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.00300773026213794</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.003022328165099202</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.003682563440032246</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.003007729370636016</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.003020060686269702</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00302232812103666</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.00300773026213794</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.00302232812103666</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002683499023037318</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.00302232812103666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.001356097071595936</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001490835920311271</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001110041920085203</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001490835920311271</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001490835920311271</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001152560015653367</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0003863151390427929</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001490835920311271</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001199130670077778</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001423688257160598</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.000198446565591449</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.001504758090433228</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.001504758090433229</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.001545677302737654</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.001404556270895074</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.001404556270895076</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.001545677302737654</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>0.001545677302737654</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.001419933748497257</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.001110967865379838</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.001419933748497255</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.001110967865379841</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.001545677302737654</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J11" t="n">
         <v>0.001441006598600604</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>0.001532300622345223</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.001466320447010409</v>
+      <c r="L11" t="n">
+        <v>0.00146632044701041</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,320 +9079,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002704252549387825</v>
+        <v>0.001600517720896571</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004982689781134017</v>
+        <v>0.001582481381557018</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01939514359039634</v>
+        <v>0.001622257843361492</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004982689781134017</v>
+        <v>0.001582481381557018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.004982689781134017</v>
+        <v>0.001582481381557018</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01312770962196828</v>
+        <v>0.001611103933647004</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008132751857594878</v>
+        <v>0.001606674496703601</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004982689781134017</v>
+        <v>0.001582481381557018</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01438860889692124</v>
+        <v>0.001613457924624694</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004895065595051514</v>
+        <v>0.001603365851747538</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05238967152271241</v>
+        <v>0.001603936124459444</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0005656620241668104</v>
+        <v>0.00163513497223298</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000503852998650307</v>
+        <v>0.001614004372427761</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005656620241668104</v>
+        <v>0.00163513497223298</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0005186630338866159</v>
+        <v>0.001614004372427761</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005186630338866157</v>
+        <v>0.001614004372427761</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0005637288655733968</v>
+        <v>0.001632845648363117</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005656620241668104</v>
+        <v>0.00163513497223298</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0005532112154755186</v>
+        <v>0.001614004372427761</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005656620241668104</v>
+        <v>0.00163513497223298</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005656620241668104</v>
+        <v>0.00163513497223298</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005656620241668104</v>
+        <v>0.00163513497223298</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001989323548507005</v>
+        <v>0.002704252549387823</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001296206547256519</v>
+        <v>0.004982689781134016</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001353897441203445</v>
+        <v>0.01939514359039631</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001217257831777483</v>
+        <v>0.004982689781134016</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001315193220616124</v>
+        <v>0.004982689781134016</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001987390389913592</v>
+        <v>0.01312770962196829</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00202215062977691</v>
+        <v>0.008132751857594886</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001976872739815714</v>
+        <v>0.004982689781134016</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001387803844482498</v>
+        <v>0.01438860889692124</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001320307389011499</v>
+        <v>0.004895065595051511</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001341315717995471</v>
+        <v>0.0523896715227123</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001035794655949663</v>
+        <v>0.0005656620241668102</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001023343847258372</v>
+        <v>0.000503852998650309</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001035744394629051</v>
+        <v>0.0005656620241668102</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001022520257903284</v>
+        <v>0.0005186630338866156</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001022520257903284</v>
+        <v>0.0005186630338866163</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001033861497356249</v>
+        <v>0.0005637288655733971</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001035794655949663</v>
+        <v>0.0005656620241668102</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001023343847258372</v>
+        <v>0.0005532112154755191</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001035794655949663</v>
+        <v>0.0005656620241668102</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001035794655949663</v>
+        <v>0.0005656620241668102</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001035794655949663</v>
+        <v>0.0005656620241668102</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001440984676371209</v>
+        <v>0.001989323548507005</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002146657892793976</v>
+        <v>0.001296206547256512</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00230872187120191</v>
+        <v>0.001353897441203445</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001950147358981308</v>
+        <v>0.001217257831777483</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001450854484610301</v>
+        <v>0.001315193220616125</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002157759856609074</v>
+        <v>0.00198739038991359</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002159693015202411</v>
+        <v>0.002022150629776914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002147242206511198</v>
+        <v>0.001976872739815714</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002159834261884065</v>
+        <v>0.001387803844482498</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001427634299999784</v>
+        <v>0.0013203073890115</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002910443972434321</v>
+        <v>0.001341315717995471</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00194996768452687</v>
+        <v>0.001035794655949662</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002391098603344386</v>
+        <v>0.001023343847258371</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002403549880506741</v>
+        <v>0.00103574439462905</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002914522528692459</v>
+        <v>0.001022520257903286</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0023910984479835</v>
+        <v>0.001022520257903286</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002401616253442256</v>
+        <v>0.001033861497356251</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002403549412035672</v>
+        <v>0.001035794655949662</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002391098603344386</v>
+        <v>0.001023343847258371</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002403549412035672</v>
+        <v>0.001035794655949662</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002140742574802051</v>
+        <v>0.001035794655949662</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002403549412035672</v>
+        <v>0.001035794655949662</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001582607819736304</v>
+        <v>0.001440984676371211</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001501201825584087</v>
+        <v>0.002146657892793983</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00112721403308247</v>
+        <v>0.002308721871201916</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001501201825584087</v>
+        <v>0.001950147358981315</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001501201825584087</v>
+        <v>0.001450854484610307</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001312034086737245</v>
+        <v>0.002157759856609081</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001457046182615193</v>
+        <v>0.002159693015202418</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001501201825584087</v>
+        <v>0.002147242206511202</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001313951618554891</v>
+        <v>0.002159834261884073</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001523035439549244</v>
+        <v>0.001427634299999789</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005130204653502499</v>
+        <v>0.002910443972434331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.001949967684526867</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.002391098603344381</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.002403549880506735</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002914522528692453</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.002391098447983494</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002401616253442258</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.002403549412035668</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.002391098603344381</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.002403549412035668</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002140742574802052</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002403549412035668</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.001582607819736305</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001501201825584088</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.001127214033082472</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.001501201825584088</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001501201825584088</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001312034086737248</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.001457046182615194</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.001501201825584088</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001313951618554891</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.001523035439549246</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0005130204653502518</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.001576617699116481</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.001531155863262759</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.001391152197400019</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.001531155863262759</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.001531155863262759</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>0.001576617699116484</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001531155863262761</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.001391152197400021</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001531155863262761</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001531155863262761</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.001465133650741447</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>0.001525643529892211</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.001531155863262759</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="I11" t="n">
+        <v>0.001531155863262761</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.00146731847515055</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>0.001552360207136422</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
         <v>0.001141831949404544</v>
       </c>
     </row>
